--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -13,6 +13,8 @@
     <sheet name="②前提" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="③FY2027月次推移" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="⑤利益ブリッジ" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="⑥ワイン仕入・在庫計画" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="⑦FY2027資金繰り表" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="276">
   <si>
     <r>
       <rPr>
@@ -3464,6 +3466,2248 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">22.4%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ワイン仕入・自社在庫計画（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ワイン仕入は「売上原価（出庫）＋在庫増減」がキャッシュアウト。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に現れない在庫積み増しが資金繰りの最大論点。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】自社在庫（簿価）の実績推移　単位：百万円</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">時点</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2024/12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/07</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自社在庫 簿価</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末→</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末の増加</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月のキャッシュアウト</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出典：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月度 取締役会資料「ワイン預かり残高推移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」（税抜・簿価）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仕入・在庫計画（税抜）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">月次ベース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期首在庫</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">620</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の在庫販売</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">420</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04-08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の増減は横ばいと仮定。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">在庫方針（月次 増減額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝在庫横ばい（仕入＝売上原価）。積み増す場合は月額を入力。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">スポット大口仕入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">野村ユニソン等のロット仕入。発生月に入力。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プリムール等 前払仕入</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引渡し前の前払。発生月に入力。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕入 合計（入庫）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上原価（出庫）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期末在庫</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※在庫方針を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（横ばい）にしても、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上期の実績ペース（月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+23.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）を続ける場合は年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">280</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円の追加資金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※スポット大口仕入・プリムール前払は、売上計上より先に支払が発生するため、資金繰り上は最も注意を要する項目。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に在庫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を販売（削減）し、その代金をみずほ銀行への融資返済</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に充当する前提。期首在庫はその後の残高。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）月次資金繰り表</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">単位：円（税込ベース）　青字＝入力セル／黄色＝要確認の前提／緑字＝他シートからのリンク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【前提】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期首現預金（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末 見込）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★要差替え。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末実績を暫定表示。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">着地の見込値を入力してください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上 回収サイト（か月）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">売掛金回転</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）より</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月と設定。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">仕入 支払サイト（か月）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">買掛金回転</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）より</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.77</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月と設定。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">長期借入金 約定返済（月額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★要差替え。長期借入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">423,623,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円−みずほ一括返済</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">223,623,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年均等返済と仮定した暫定値。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">短期借入金 純増減（月額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期借入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">162,440,980</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円は同額借換（継続）を前提。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【営業収入】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上入金（既存事業・税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経営指導料 入金（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">インセンティブ 入金（税込）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前期末売掛金 回収（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在庫販売）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に販売した在庫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（税抜）の代金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">220</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（税込）を、回収サイト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月後の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に入金と仮定。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業収入 計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【営業支出】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ワイン仕入 支払（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人件費（役員報酬・給与・雑給・法定福利）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他販管費（税込・減価償却除く）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上場関連コスト（税込）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支払利息</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税 納付</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確定分。在庫販売</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に係る仮受消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を含む（仕入時に仮払控除済のため純増）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">法人税等（均等割）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業支出 計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経常収支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【財務・投資収支】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">長期借入金 約定返済</t>
+  </si>
+  <si>
+    <t xml:space="preserve">短期借入金 純増減</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新規調達（借入・増資）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投資売買益 入金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">みずほ銀行 融資返済（在庫販売代金充当）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在庫販売代金の入金月に同額を一括返済する前提。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">財務・投資収支 計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当月収支</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前月繰越 現預金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翌月繰越 現預金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資金不足額（マイナス時）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通期列＝最大不足額（必要調達額の下限）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※売上・仕入とも回収／支払サイト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月。既存事業の売上は横ばい前提のため、月ズレの影響は通期では相殺されます。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ワイン仕入の支払は前月仕入額を当月に支払う前提（⑥シートで仕入月を入力すると、翌月に資金流出として反映されます）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※減価償却費（月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）は資金支出を伴わないため、営業支出から除外しています。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※消費税納付・法人税等は暫定値です。税理士確定額に差し替えてください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※期首現預金と長期借入返済額（黄色セル）は必ず実際の数値に差し替えてください。この</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つで結論が大きく変わります。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【感応度】どこまで耐えられるか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ケース</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期末 現預金残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期中 最低残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必要調達額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前提</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本（在庫横ばい・調達なし）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在庫を積み増さず、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の一時収益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円が予定どおり入金する前提</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. 2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の一時収益が入らない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インセンティブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（税込）＋投資売買益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円が未入金の場合</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在庫を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上期ペースで積増</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">末の実績ペース）で積み増した場合</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D. 2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の在庫販売</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円が不成立</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">220</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・返済</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・消費税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は相殺されるが、長期借入が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">223.6→423.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円のままとなり約定返済が月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に戻る</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">運転資金バッファ（月商</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最低残高をゼロに戻すだけでは足りないため、月商</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月分を上乗せして必要調達額を算定。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ケース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は在庫積み増しを継続した場合。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上の利益は変わらないが、資金は年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">308</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（税込）流出します。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ケース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が同時に起きた場合、必要調達額は両者の合計に近い水準となります。</t>
     </r>
   </si>
 </sst>
@@ -3471,13 +5715,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\¥#,##0;&quot;(¥&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3669,8 +5916,41 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3692,19 +5972,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFFDF6E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFDF6E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
-        <bgColor rgb="FFD9E2F3"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -3717,6 +5997,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE7E6E6"/>
         <bgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6E3"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -3761,7 +6053,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="68">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3986,6 +6278,54 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4014,13 +6354,13 @@
       <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF6D2E46"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E2F3"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -4030,13 +6370,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFD9E2F3"/>
       <rgbColor rgb="FFE7E6E6"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFDF6E3"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF8CBAD"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -4044,7 +6384,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -4056,6 +6396,374 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>月末 現預金残高の推移（ケースA：在庫横ばい・調達なし）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="6d2e46"/>
+            </a:solidFill>
+            <a:ln w="28080">
+              <a:solidFill>
+                <a:srgbClr val="6d2e46"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>⑦FY2027資金繰り表!$D$12:$O$12</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2026/10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2026/11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2026/12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2027/01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2027/02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2027/03</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2027/04</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2027/05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2027/06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027/07</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2027/08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2027/09</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>⑦FY2027資金繰り表!$D$41:$O$41</c:f>
+              <c:numCache>
+                <c:formatCode>\¥#,##0;"(¥"#,##0\);\-</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>41193416.1666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7533449.33333336</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4336587.50000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1139725.66666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2057136.16666665</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36746002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33549140.1666667</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>25352278.3333333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22155416.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18958554.6666667</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15761692.8333333</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12564831</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="27442361"/>
+        <c:axId val="94407825"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="27442361"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="94407825"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="94407825"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>円</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="\¥#,##0;&quot;(¥&quot;#,##0\);\-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="27442361"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1038600</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="266760" y="11430000"/>
+        <a:ext cx="8639640" cy="2735640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9610,4 +12318,2193 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:Q22"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="56" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="57" t="n">
+        <v>560</v>
+      </c>
+      <c r="D6" s="57" t="n">
+        <v>470</v>
+      </c>
+      <c r="E6" s="57" t="n">
+        <v>480</v>
+      </c>
+      <c r="F6" s="57" t="n">
+        <v>530</v>
+      </c>
+      <c r="G6" s="57" t="n">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="58" t="n">
+        <f aca="false">G6-E6</f>
+        <v>140</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E7" s="59" t="n">
+        <f aca="false">C7/6</f>
+        <v>23.3333333333333</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M11" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="N11" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="O11" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="P11" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>420000000</v>
+      </c>
+      <c r="Q12" s="43" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="34" t="n">
+        <f aca="false">SUM(D14:O14)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="34" t="n">
+        <f aca="false">SUM(D15:O15)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <f aca="false">D17+$C$13+D14+D15</f>
+        <v>15711570</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <f aca="false">E17+$C$13+E14+E15</f>
+        <v>15711570</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">F17+$C$13+F14+F15</f>
+        <v>15711570</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <f aca="false">G17+$C$13+G14+G15</f>
+        <v>15711570</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <f aca="false">H17+$C$13+H14+H15</f>
+        <v>15711570</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <f aca="false">I17+$C$13+I14+I15</f>
+        <v>15711570</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <f aca="false">J17+$C$13+J14+J15</f>
+        <v>15711570</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <f aca="false">K17+$C$13+K14+K15</f>
+        <v>15711570</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <f aca="false">L17+$C$13+L14+L15</f>
+        <v>15711570</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <f aca="false">M17+$C$13+M14+M15</f>
+        <v>15711570</v>
+      </c>
+      <c r="N16" s="12" t="n">
+        <f aca="false">N17+$C$13+N14+N15</f>
+        <v>15711570</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <f aca="false">O17+$C$13+O14+O15</f>
+        <v>15711570</v>
+      </c>
+      <c r="P16" s="34" t="n">
+        <f aca="false">SUM(D16:O16)</f>
+        <v>188538840</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D7</f>
+        <v>15711570</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E7</f>
+        <v>15711570</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F7</f>
+        <v>15711570</v>
+      </c>
+      <c r="G17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G7</f>
+        <v>15711570</v>
+      </c>
+      <c r="H17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H7</f>
+        <v>15711570</v>
+      </c>
+      <c r="I17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I7</f>
+        <v>15711570</v>
+      </c>
+      <c r="J17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J7</f>
+        <v>15711570</v>
+      </c>
+      <c r="K17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K7</f>
+        <v>15711570</v>
+      </c>
+      <c r="L17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L7</f>
+        <v>15711570</v>
+      </c>
+      <c r="M17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M7</f>
+        <v>15711570</v>
+      </c>
+      <c r="N17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N7</f>
+        <v>15711570</v>
+      </c>
+      <c r="O17" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O7</f>
+        <v>15711570</v>
+      </c>
+      <c r="P17" s="34" t="n">
+        <f aca="false">SUM(D17:O17)</f>
+        <v>188538840</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="60" t="n">
+        <f aca="false">$C$12+D16-D17</f>
+        <v>420000000</v>
+      </c>
+      <c r="E18" s="60" t="n">
+        <f aca="false">D18+E16-E17</f>
+        <v>420000000</v>
+      </c>
+      <c r="F18" s="60" t="n">
+        <f aca="false">E18+F16-F17</f>
+        <v>420000000</v>
+      </c>
+      <c r="G18" s="60" t="n">
+        <f aca="false">F18+G16-G17</f>
+        <v>420000000</v>
+      </c>
+      <c r="H18" s="60" t="n">
+        <f aca="false">G18+H16-H17</f>
+        <v>420000000</v>
+      </c>
+      <c r="I18" s="60" t="n">
+        <f aca="false">H18+I16-I17</f>
+        <v>420000000</v>
+      </c>
+      <c r="J18" s="60" t="n">
+        <f aca="false">I18+J16-J17</f>
+        <v>420000000</v>
+      </c>
+      <c r="K18" s="60" t="n">
+        <f aca="false">J18+K16-K17</f>
+        <v>420000000</v>
+      </c>
+      <c r="L18" s="60" t="n">
+        <f aca="false">K18+L16-L17</f>
+        <v>420000000</v>
+      </c>
+      <c r="M18" s="60" t="n">
+        <f aca="false">L18+M16-M17</f>
+        <v>420000000</v>
+      </c>
+      <c r="N18" s="60" t="n">
+        <f aca="false">M18+N16-N17</f>
+        <v>420000000</v>
+      </c>
+      <c r="O18" s="60" t="n">
+        <f aca="false">N18+O16-O17</f>
+        <v>420000000</v>
+      </c>
+      <c r="P18" s="61" t="n">
+        <f aca="false">O18</f>
+        <v>420000000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="30" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="43" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:Q59"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="4" style="0" width="12.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="38" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="45" t="n">
+        <v>24390278</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="62" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>2662179</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="O12" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="P12" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="64" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="E14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="F14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="G14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="H14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="I14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="J14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="K14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="L14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="M14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="N14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="O14" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="P14" s="34" t="n">
+        <f aca="false">SUM(D14:O14)</f>
+        <v>428054844.8</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!D9:D13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!E9:E13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="F15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!F9:F13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="G15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!G9:G13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="H15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!H9:H13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="I15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!I9:I13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="J15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!J9:J13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="K15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!K9:K13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="L15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!L9:L13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="M15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!M9:M13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="N15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!N9:N13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="O15" s="51" t="n">
+        <f aca="false">SUM(③FY2027月次推移!O9:O13)*(1+$C$6)</f>
+        <v>8479166.66666667</v>
+      </c>
+      <c r="P15" s="34" t="n">
+        <f aca="false">SUM(D15:O15)</f>
+        <v>101750000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I14*(1+$C$6)</f>
+        <v>22000000</v>
+      </c>
+      <c r="J16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O14*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="34" t="n">
+        <f aca="false">SUM(D16:O16)</f>
+        <v>22000000</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="45" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="E17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="34" t="n">
+        <f aca="false">SUM(D17:O17)</f>
+        <v>220000000</v>
+      </c>
+      <c r="Q17" s="43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">SUM(D14:D17)</f>
+        <v>264150403.733333</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">SUM(E14:E17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">SUM(F14:F17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <f aca="false">SUM(G14:G17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <f aca="false">SUM(H14:H17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <f aca="false">SUM(I14:I17)</f>
+        <v>66150403.7333333</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <f aca="false">SUM(J14:J17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <f aca="false">SUM(K14:K17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <f aca="false">SUM(L14:L17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <f aca="false">SUM(M14:M17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <f aca="false">SUM(N14:N17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <f aca="false">SUM(O14:O17)</f>
+        <v>44150403.7333333</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <f aca="false">SUM(D18:O18)</f>
+        <v>771804844.8</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="64" t="s">
+        <v>230</v>
+      </c>
+      <c r="D21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!D16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!D16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="F21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!E16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="G21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!F16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="H21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!G16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="I21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!H16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="J21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!I16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="K21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!J16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="L21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!K16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="M21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!L16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="N21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!M16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="O21" s="51" t="n">
+        <f aca="false">⑥ワイン仕入・在庫計画!N16*(1+$C$6)</f>
+        <v>17282727</v>
+      </c>
+      <c r="P21" s="34" t="n">
+        <f aca="false">SUM(D21:O21)</f>
+        <v>207392724</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="64" t="s">
+        <v>231</v>
+      </c>
+      <c r="D22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="E22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="F22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="G22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="H22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="I22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="J22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="K22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="L22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="M22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="N22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="O22" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
+        <v>6089866.33333333</v>
+      </c>
+      <c r="P22" s="34" t="n">
+        <f aca="false">SUM(D22:O22)</f>
+        <v>73078396</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="64" t="s">
+        <v>232</v>
+      </c>
+      <c r="D23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!D41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!E41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="F23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!F41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="G23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!G41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="H23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!H41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="I23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!I41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="J23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!J41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="K23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!K41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="L23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!L41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="M23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!M41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="N23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!N41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="O23" s="51" t="n">
+        <f aca="false">((③FY2027月次推移!O41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
+      </c>
+      <c r="P23" s="34" t="n">
+        <f aca="false">SUM(D23:O23)</f>
+        <v>201149918.8</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="64" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="E24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="G24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="H24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="I24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="J24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="K24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="L24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="M24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="N24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="O24" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O42*(1+$C$6)</f>
+        <v>3300000</v>
+      </c>
+      <c r="P24" s="34" t="n">
+        <f aca="false">SUM(D24:O24)</f>
+        <v>39600000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D48</f>
+        <v>1250000</v>
+      </c>
+      <c r="E25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E48</f>
+        <v>1250000</v>
+      </c>
+      <c r="F25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F48</f>
+        <v>1250000</v>
+      </c>
+      <c r="G25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G48</f>
+        <v>1250000</v>
+      </c>
+      <c r="H25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H48</f>
+        <v>1250000</v>
+      </c>
+      <c r="I25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I48</f>
+        <v>1250000</v>
+      </c>
+      <c r="J25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J48</f>
+        <v>1250000</v>
+      </c>
+      <c r="K25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K48</f>
+        <v>1250000</v>
+      </c>
+      <c r="L25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L48</f>
+        <v>1250000</v>
+      </c>
+      <c r="M25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M48</f>
+        <v>1250000</v>
+      </c>
+      <c r="N25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N48</f>
+        <v>1250000</v>
+      </c>
+      <c r="O25" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O48</f>
+        <v>1250000</v>
+      </c>
+      <c r="P25" s="34" t="n">
+        <f aca="false">SUM(D25:O25)</f>
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="45" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="45" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="L26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="34" t="n">
+        <f aca="false">SUM(D26:O26)</f>
+        <v>35000000</v>
+      </c>
+      <c r="Q26" s="43" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="45" t="n">
+        <v>463105</v>
+      </c>
+      <c r="F27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="34" t="n">
+        <f aca="false">SUM(D27:O27)</f>
+        <v>463105</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <f aca="false">SUM(D21:D27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <f aca="false">SUM(E21:E27)</f>
+        <v>75148191.5666667</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <f aca="false">SUM(F21:F27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <f aca="false">SUM(G21:G27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <f aca="false">SUM(H21:H27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <f aca="false">SUM(I21:I27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <f aca="false">SUM(J21:J27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <f aca="false">SUM(K21:K27)</f>
+        <v>49685086.5666667</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <f aca="false">SUM(L21:L27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <f aca="false">SUM(M21:M27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="N28" s="12" t="n">
+        <f aca="false">SUM(N21:N27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="O28" s="12" t="n">
+        <f aca="false">SUM(O21:O27)</f>
+        <v>44685086.5666667</v>
+      </c>
+      <c r="P28" s="12" t="n">
+        <f aca="false">SUM(D28:O28)</f>
+        <v>571684143.8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">D18-D28</f>
+        <v>219465317.166667</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <f aca="false">E18-E28</f>
+        <v>-30997787.8333333</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <f aca="false">F18-F28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <f aca="false">G18-G28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="H29" s="16" t="n">
+        <f aca="false">H18-H28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <f aca="false">I18-I28</f>
+        <v>21465317.1666667</v>
+      </c>
+      <c r="J29" s="16" t="n">
+        <f aca="false">J18-J28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <f aca="false">K18-K28</f>
+        <v>-5534682.83333334</v>
+      </c>
+      <c r="L29" s="16" t="n">
+        <f aca="false">L18-L28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <f aca="false">M18-M28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <f aca="false">N18-N28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <f aca="false">O18-O28</f>
+        <v>-534682.833333336</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <f aca="false">SUM(D29:O29)</f>
+        <v>200120701</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="64" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="E32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="F32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="G32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="H32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="I32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="J32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="K32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="L32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="M32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="N32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="O32" s="51" t="n">
+        <f aca="false">-$C$9</f>
+        <v>-2662179</v>
+      </c>
+      <c r="P32" s="34" t="n">
+        <f aca="false">SUM(D32:O32)</f>
+        <v>-31946148</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="64" t="s">
+        <v>242</v>
+      </c>
+      <c r="D33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="51" t="n">
+        <f aca="false">$C$10</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="34" t="n">
+        <f aca="false">SUM(D33:O33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="34" t="n">
+        <f aca="false">SUM(D34:O34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="64" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D47</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E47</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F47</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G47</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H47</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I47</f>
+        <v>20000000</v>
+      </c>
+      <c r="J35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J47</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K47</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L47</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M47</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N47</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O47</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="34" t="n">
+        <f aca="false">SUM(D35:O35)</f>
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="45" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="E36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="34" t="n">
+        <f aca="false">SUM(D36:O36)</f>
+        <v>-200000000</v>
+      </c>
+      <c r="Q36" s="30" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <f aca="false">SUM(D32:D36)</f>
+        <v>-202662179</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <f aca="false">SUM(E32:E36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <f aca="false">SUM(F32:F36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <f aca="false">SUM(G32:G36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <f aca="false">SUM(H32:H36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <f aca="false">SUM(I32:I36)</f>
+        <v>17337821</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <f aca="false">SUM(J32:J36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <f aca="false">SUM(K32:K36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <f aca="false">SUM(L32:L36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <f aca="false">SUM(M32:M36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <f aca="false">SUM(N32:N36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <f aca="false">SUM(O32:O36)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <f aca="false">SUM(D37:O37)</f>
+        <v>-211946148</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <f aca="false">D29+D37</f>
+        <v>16803138.1666667</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <f aca="false">E29+E37</f>
+        <v>-33659966.8333333</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <f aca="false">F29+F37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <f aca="false">G29+G37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <f aca="false">H29+H37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <f aca="false">I29+I37</f>
+        <v>38803138.1666667</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <f aca="false">J29+J37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <f aca="false">K29+K37</f>
+        <v>-8196861.83333334</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <f aca="false">L29+L37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <f aca="false">M29+M37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <f aca="false">N29+N37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="O39" s="12" t="n">
+        <f aca="false">O29+O37</f>
+        <v>-3196861.83333334</v>
+      </c>
+      <c r="P39" s="12" t="n">
+        <f aca="false">SUM(D39:O39)</f>
+        <v>-11825447</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <f aca="false">$C$5</f>
+        <v>24390278</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <f aca="false">D41</f>
+        <v>41193416.1666667</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <f aca="false">E41</f>
+        <v>7533449.33333336</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <f aca="false">F41</f>
+        <v>4336587.50000002</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <f aca="false">G41</f>
+        <v>1139725.66666669</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <f aca="false">H41</f>
+        <v>-2057136.16666665</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <f aca="false">I41</f>
+        <v>36746002</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <f aca="false">J41</f>
+        <v>33549140.1666667</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <f aca="false">K41</f>
+        <v>25352278.3333333</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <f aca="false">L41</f>
+        <v>22155416.5</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <f aca="false">M41</f>
+        <v>18958554.6666667</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <f aca="false">N41</f>
+        <v>15761692.8333333</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="19" t="n">
+        <f aca="false">D40+D39</f>
+        <v>41193416.1666667</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <f aca="false">E40+E39</f>
+        <v>7533449.33333336</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <f aca="false">F40+F39</f>
+        <v>4336587.50000002</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <f aca="false">G40+G39</f>
+        <v>1139725.66666669</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <f aca="false">H40+H39</f>
+        <v>-2057136.16666665</v>
+      </c>
+      <c r="I41" s="19" t="n">
+        <f aca="false">I40+I39</f>
+        <v>36746002</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <f aca="false">J40+J39</f>
+        <v>33549140.1666667</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <f aca="false">K40+K39</f>
+        <v>25352278.3333333</v>
+      </c>
+      <c r="L41" s="19" t="n">
+        <f aca="false">L40+L39</f>
+        <v>22155416.5</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <f aca="false">M40+M39</f>
+        <v>18958554.6666667</v>
+      </c>
+      <c r="N41" s="19" t="n">
+        <f aca="false">N40+N39</f>
+        <v>15761692.8333333</v>
+      </c>
+      <c r="O41" s="19" t="n">
+        <f aca="false">O40+O39</f>
+        <v>12564831</v>
+      </c>
+      <c r="P41" s="52" t="n">
+        <f aca="false">O41</f>
+        <v>12564831</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="65" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42" s="66" t="n">
+        <f aca="false">IF(D41&lt;0,D41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="66" t="n">
+        <f aca="false">IF(E41&lt;0,E41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="66" t="n">
+        <f aca="false">IF(F41&lt;0,F41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="66" t="n">
+        <f aca="false">IF(G41&lt;0,G41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="66" t="n">
+        <f aca="false">IF(H41&lt;0,H41,0)</f>
+        <v>-2057136.16666665</v>
+      </c>
+      <c r="I42" s="66" t="n">
+        <f aca="false">IF(I41&lt;0,I41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="66" t="n">
+        <f aca="false">IF(J41&lt;0,J41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="66" t="n">
+        <f aca="false">IF(K41&lt;0,K41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="66" t="n">
+        <f aca="false">IF(L41&lt;0,L41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="66" t="n">
+        <f aca="false">IF(M41&lt;0,M41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="66" t="n">
+        <f aca="false">IF(N41&lt;0,N41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O42" s="66" t="n">
+        <f aca="false">IF(O41&lt;0,O41,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P42" s="66" t="n">
+        <f aca="false">MIN(D42:O42)</f>
+        <v>-2057136.16666665</v>
+      </c>
+      <c r="Q42" s="30" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="30" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="39" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="40"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+      <c r="Q50" s="40"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" s="34" t="n">
+        <f aca="false">O41</f>
+        <v>12564831</v>
+      </c>
+      <c r="D52" s="34" t="n">
+        <f aca="false">MIN(D41:O41)</f>
+        <v>-2057136.16666665</v>
+      </c>
+      <c r="E52" s="24" t="n">
+        <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$56,MAX(0,-D52+$C$56))</f>
+        <v>37728373.2333333</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="C53" s="66" t="n">
+        <f aca="false">C52-(P16+P35)</f>
+        <v>-29435169</v>
+      </c>
+      <c r="D53" s="66" t="n">
+        <f aca="false">D52-(P16+P35)</f>
+        <v>-44057136.1666667</v>
+      </c>
+      <c r="E53" s="24" t="n">
+        <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$56,MAX(0,-D53+$C$56))</f>
+        <v>79728373.2333333</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="C54" s="66" t="n">
+        <f aca="false">C52-23333333*(1+$C$6)*12</f>
+        <v>-295435164.6</v>
+      </c>
+      <c r="D54" s="66" t="n">
+        <f aca="false">D52-23333333*(1+$C$6)*12</f>
+        <v>-310057131.766667</v>
+      </c>
+      <c r="E54" s="24" t="n">
+        <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$56,MAX(0,-D54+$C$56))</f>
+        <v>345728368.833333</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="67" t="s">
+        <v>270</v>
+      </c>
+      <c r="C55" s="66" t="n">
+        <f aca="false">C52-(5043131-$C$9)*12</f>
+        <v>-16006593</v>
+      </c>
+      <c r="D55" s="66" t="n">
+        <f aca="false">D52-(5043131-$C$9)*12</f>
+        <v>-30628560.1666667</v>
+      </c>
+      <c r="E55" s="24" t="n">
+        <f aca="false">IF(C55&lt;0,-MIN(C55,D55)+$C$56,MAX(0,-D55+$C$56))</f>
+        <v>66299797.2333333</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C56" s="51" t="n">
+        <f aca="false">③FY2027月次推移!$C$6*(1+$C$6)</f>
+        <v>35671237.0666667</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="30" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="277">
   <si>
     <r>
       <rPr>
@@ -299,8 +299,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">損益分岐
-（営業利益</t>
+      <t xml:space="preserve">営業利益
+</t>
     </r>
     <r>
       <rPr>
@@ -311,7 +311,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -321,7 +321,1260 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）</t>
+      <t xml:space="preserve">億円</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">コメント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存事業 売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上総利益（既存事業）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＋上乗せ案件（営業収益）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万＋インセンティブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">＋追加で必要な粗利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標達成に必要な粗利の上積み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上総利益 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">販管費 小計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04-06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績の月平均</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">上場関連コスト</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は計上しない方針</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">販管費 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業利益</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は目標営業利益を固定して逆算</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外収益（投資売買益）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経常利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法人税等</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">繰越欠損金 約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">252</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円により実質非課税</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">当期純利益</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">字回復に必要な追加売上】</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">追加売上</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新規顧客売上計画
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,066</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に対する比率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円に必要な追加売上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【判定】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：撤退後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">99.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。上乗せなしでは黒字化しない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せ案件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を計上すると営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円で黒字化する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円には、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">からさらに粗利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">87.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円の上積みが必要。追加売上は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6,888</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　これは新規顧客売上計画（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,066</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にあたる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※上場関連コストは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は計上しない前提（②前提シートで年額を入力すれば再計算されます）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※上乗せ案件のうち約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円はグループ内取引。銀行は正常化調整で控除する可能性が高い。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">見込には</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単月に売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">232.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（通期の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を織り込み。粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のため営業利益寄与は＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円のみ。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）月次　実績／見込</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青字＝実績（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">まで）　灰字斜体＝見込（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降・同一値が並ぶプラグ）　出典：事業計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">202608</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（銀行様）全社シート</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">飲食事業の撤退により、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降が撤退後の実力値。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/10-2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には撤退店舗の費用が含まれる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通期</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">①10-3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月
+平均</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">②4-6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月
+平均</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差 ②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-①</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上原価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上総利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【販売費及び一般管理費 内訳】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">役員報酬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">従業員給与</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雑給</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法定福利費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">広告宣伝費・販売促進費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">発送配達費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支払手数料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地代家賃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通信交通費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水道光熱費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接待交際費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保険料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">研修採用費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備品消耗品費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">管理諸費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">清掃費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">業務委託費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会議費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雑費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">租税公課</t>
+  </si>
+  <si>
+    <t xml:space="preserve">諸会費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">減価償却費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">倉庫＆保管・移設代</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※「差 ②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」がマイナスの科目＝飲食撤退および固定費削減により減少した費用。合計で月▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.58</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（年▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">103</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月期）利益予測モデル　－　前提条件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青字＝入力セル／黄色＝主要前提／黒字＝計算式　単位：円（税別）　作成日 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/08/21</t>
     </r>
   </si>
   <si>
@@ -330,1303 +1583,43 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D. </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益
-</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】ベース：飲食撤退後の実力値（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">コメント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存事業 売上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存事業 売上総利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">＋上乗せ案件（営業収益）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万＋インセンティブ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">＋追加で必要な粗利</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の達成に必要な粗利の上積み</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">売上総利益 合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販管費 小計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04-06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実績の月平均</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×12</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">上場関連コスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">販管費 合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外収益（投資売買益）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外費用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">経常利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法人税等</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">繰越欠損金 約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">252</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円により実質非課税</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">当期純利益</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">字回復に必要な追加売上】</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">追加売上</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新規顧客売上計画
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,066</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円に対する比率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">損益分岐（営業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）に必要な追加売上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円に必要な追加売上</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【判定】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：撤退後の実力値を横ばいで延ばすだけでは営業利益▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">135.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円。上乗せなしでは黒字化しない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：上乗せ案件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を全額計上しても、上場関連コスト</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">36</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を計上すると営業利益は▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">23.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：損益分岐までの距離は追加売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4,473</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円。新規顧客売上計画（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,066</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で到達する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：営業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円には追加売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,872</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円。同計画の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で到達する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※上乗せ案件のうち約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円はグループ内取引。銀行は正常化調整で控除する可能性が高い。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">見込には</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単月に売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">232.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（通期の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を織り込み。粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のため営業利益寄与は＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円のみ。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月）月次　実績／見込</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">青字＝実績（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">まで）　灰字斜体＝見込（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/07</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以降・同一値が並ぶプラグ）　出典：事業計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">202608</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（銀行様）全社シート</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飲食事業の撤退により、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以降が撤退後の実力値。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025/10-2026/03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には撤退店舗の費用が含まれる。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通期</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">①10-3</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月
-平均</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">②4-6</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月
-平均</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">差 ②</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-①</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">売上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上原価</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上総利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【販売費及び一般管理費 内訳】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">役員報酬</t>
-  </si>
-  <si>
-    <t xml:space="preserve">従業員給与</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雑給</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法定福利費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">広告宣伝費・販売促進費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">発送配達費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">支払手数料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">地代家賃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通信交通費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水道光熱費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接待交際費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保険料</t>
-  </si>
-  <si>
-    <t xml:space="preserve">研修採用費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備品消耗品費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">管理諸費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">清掃費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">業務委託費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会議費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雑費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">租税公課</t>
-  </si>
-  <si>
-    <t xml:space="preserve">諸会費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">減価償却費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">倉庫＆保管・移設代</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※「差 ②</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-①</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」がマイナスの科目＝飲食撤退および固定費削減により減少した費用。合計で月▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.58</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（年▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">103</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月期）利益予測モデル　－　前提条件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">青字＝入力セル／黄色＝主要前提／黒字＝計算式　単位：円（税別）　作成日 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/08/21</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04-06 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1635,7 +1628,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【</t>
+      <t xml:space="preserve">実績</t>
     </r>
     <r>
       <rPr>
@@ -1646,7 +1639,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -1656,85 +1649,85 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">】ベース：飲食撤退後の実力値（</t>
-    </r>
+      <t xml:space="preserve">か月平均）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月次平均</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以前は飲食撤退店舗の売上・費用を含むため基準から除外（貴社ご指摘）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">販管費</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上総利益率</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04-06 </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実績</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】上乗せ案件（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月平均）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月次平均</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以前は飲食撤退店舗の売上・費用を含むため基準から除外（貴社ご指摘）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">販管費</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売上総利益率</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09-2027/08</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1743,555 +1736,1087 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【</t>
-    </r>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金額</t>
+  </si>
+  <si>
+    <t xml:space="preserve">損益計上区分</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Value table</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業収益（原価なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Prime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Thierry Marx</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ito</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Aqua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hokkaido</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インセンティブ　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius2 shot</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業収益（成功報酬・一時）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投資売買益　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Cruiser shot</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外収益（一時）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※期間表記は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09-2027/08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。決算期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026/10-2027/09)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月ズレるため全額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">帰属で試算。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　うち 営業収益</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※うち約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円はグループ内取引（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Value table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Prime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　うち 営業外収益</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">】上乗せ案件（</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/09-2027/08</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】その他前提</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">上場関連コスト（年額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は計上しない方針のため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。計上する場合は年額を入力。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外費用（支払利息等・年額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事業計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画値</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">インセンティブ 計上月（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投資売買益 計上月（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">目標営業利益</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の目標</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新規顧客売上 計画額（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">事業計画のワイン投資 新規顧客計画 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">均等割のみ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">繰越欠損金 約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">252</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025▲127.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026▲124.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。資本金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円の中小法人は所得の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">控除可。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2027</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）月次推移表　【保守シナリオ】撤退後実力値の横ばい ＋ 上乗せ案件</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132.5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列＝月次ベース（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04-06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績平均、④シートから自動リンク）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列以降は同額で横ばい。緑字＝他シートからのリンク</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">区分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金額</t>
-  </si>
-  <si>
-    <t xml:space="preserve">損益計上区分</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Value table</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業収益（原価なし）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Prime</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Thierry Marx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ito</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Aqua</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Hokkaido</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">インセンティブ　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius2 shot</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業収益（成功報酬・一時）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投資売買益　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cruiser shot</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外収益（一時）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※期間表記は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/09-2027/08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。決算期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2026/10-2027/09)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月ズレるため全額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">帰属で試算。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">　うち 営業収益</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※うち約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円はグループ内取引（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Value table</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Prime</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">　うち 営業外収益</t>
-  </si>
-  <si>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月次ベース
+</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(26/4-6</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">】その他前提</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">上場関連コスト（年額）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事業計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画値。計上しない場合は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外費用（支払利息等・年額）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事業計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画値</t>
-    </r>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通期合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【収益】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　売上原価</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存事業 売上総利益</t>
   </si>
   <si>
     <r>
@@ -2300,7 +2825,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">インセンティブ 計上月（</t>
+      <t xml:space="preserve">＋経営指導料 </t>
     </r>
     <r>
       <rPr>
@@ -2309,15 +2834,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
+      <t xml:space="preserve">Value table</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
+      <t xml:space="preserve">＋経営指導料 </t>
     </r>
     <r>
       <rPr>
@@ -2326,11 +2853,225 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">Prime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋経営指導料 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋経営指導料 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Thierry Marx</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋経営指導料 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ito</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Aqua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hokkaido</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋インセンティブ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius2 shot</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【販売費及び一般管理費】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【損益】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外費用（支払利息等）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経常利益 累計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※既存事業の売上・粗利・販管費は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/04-06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績の月平均を横ばい。成長・季節変動は織り込んでいない保守前提。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※経営指導料は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">12</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月按分。インセンティブ・投資売買益は②前提で指定した月に一括計上。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 → FY2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益ブリッジ（保守シナリオ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2338,814 +3079,202 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投資売買益 計上月（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">目標営業利益</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">シナリオ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の目標</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新規顧客売上 計画額（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">事業計画のワイン投資 新規顧客計画 合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">均等割のみ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">繰越欠損金 約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">252</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2025▲127.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026▲124.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。資本金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円の中小法人は所得の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">控除可。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-2027</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月）月次推移表　【保守シナリオ】撤退後実力値の横ばい ＋ 上乗せ案件</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132.5</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列＝月次ベース（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04-06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実績平均、④シートから自動リンク）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列以降は同額で横ばい。緑字＝他シートからのリンク</t>
-    </r>
+    <t xml:space="preserve">単位：円（税別）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">増減</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月次ベース
-</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(26/4-6</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益（見込）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">現行計画の今期着地見込</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 既存事業 粗利の減少</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025/11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の大口を含む。撤退後実力値ベースでは減少</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">② 販管費の削減</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">飲食撤退＋固定費削減。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月平均比で月▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.58</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">③ 上乗せ案件（営業収益）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 上場関連コスト</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画値</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平均</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2027 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027/09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通期合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【収益】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　売上原価</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋経営指導料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Value table</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋経営指導料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Prime</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋経営指導料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋経営指導料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Thierry Marx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋経営指導料 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ito</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Aqua</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Hokkaido</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋インセンティブ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius2 shot</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【販売費及び一般管理費】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">【損益】</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外費用（支払利息等）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">経常利益 累計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※既存事業の売上・粗利・販管費は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/04-06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実績の月平均を横ばい。成長・季節変動は織り込んでいない保守前提。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※経営指導料は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月按分。インセンティブ・投資売買益は②前提で指定した月に一括計上。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 → FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益ブリッジ（保守シナリオ</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">単位：円（税別）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">増減</t>
-  </si>
-  <si>
-    <t xml:space="preserve">累計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">内容</t>
-  </si>
-  <si>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益（保守シナリオ</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -3154,7 +3283,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">FY2026 </t>
+      <t xml:space="preserve">B</t>
     </r>
     <r>
       <rPr>
@@ -3163,221 +3292,67 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">営業利益（見込）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">現行計画の今期着地見込</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 既存事業 粗利の減少</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025/11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の大口を含む。撤退後実力値ベースでは減少</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">② 販管費の削減</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飲食撤退＋固定費削減。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月平均比で月▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8.58</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">③ 上乗せ案件（営業収益）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ 上場関連コスト</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画値</t>
-    </r>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">①〜④の合計</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【営業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円に必要な追加売上】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業利益 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益（保守シナリオ</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">①〜④の合計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">損益分岐（営業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円</t>
     </r>
   </si>
   <si>
@@ -3407,65 +3382,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4.2%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22.4%</t>
+      <t xml:space="preserve">百万円に対する比率</t>
     </r>
   </si>
   <si>
@@ -6053,7 +5970,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6094,7 +6011,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6275,6 +6192,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6535,40 +6456,40 @@
                 <c:formatCode>\¥#,##0;"(¥"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>41193416.1666667</c:v>
+                  <c:v>44493416.1666667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7533449.33333336</c:v>
+                  <c:v>14133449.3333334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4336587.50000002</c:v>
+                  <c:v>14236587.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1139725.66666669</c:v>
+                  <c:v>14339725.6666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-2057136.16666665</c:v>
+                  <c:v>14442863.8333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36746002</c:v>
+                  <c:v>56546002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>33549140.1666667</c:v>
+                  <c:v>56649140.1666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25352278.3333333</c:v>
+                  <c:v>51752278.3333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22155416.5</c:v>
+                  <c:v>51855416.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18958554.6666667</c:v>
+                  <c:v>51958554.6666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15761692.8333333</c:v>
+                  <c:v>52061692.8333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12564831</c:v>
+                  <c:v>52164831</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6583,11 +6504,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="27442361"/>
-        <c:axId val="94407825"/>
+        <c:axId val="71173310"/>
+        <c:axId val="17219586"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27442361"/>
+        <c:axId val="71173310"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6619,7 +6540,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94407825"/>
+        <c:crossAx val="17219586"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6627,7 +6548,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94407825"/>
+        <c:axId val="17219586"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6703,7 +6624,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27442361"/>
+        <c:crossAx val="71173310"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6946,13 +6867,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:H34"/>
+  <dimension ref="B1:G35"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6986,16 +6907,13 @@
       <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>708205820</v>
@@ -7010,17 +6928,13 @@
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">E6+F9/②前提!$C$9</f>
-        <v>433872391.379295</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <f aca="false">E6+G9/②前提!$C$9</f>
-        <v>627858945.685991</v>
-      </c>
-      <c r="H6" s="3"/>
+        <v>558023786.135581</v>
+      </c>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>229139405</v>
@@ -7037,15 +6951,11 @@
         <f aca="false">E7</f>
         <v>200601928</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <f aca="false">E7</f>
-        <v>200601928</v>
-      </c>
-      <c r="H7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -7061,36 +6971,28 @@
         <f aca="false">②前提!$C$21</f>
         <v>112500000</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <f aca="false">②前提!$C$21</f>
-        <v>112500000</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
+      <c r="G8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="8" t="n">
-        <f aca="false">-E14</f>
-        <v>23059136</v>
-      </c>
-      <c r="G9" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <f aca="false">②前提!$C$29-E14</f>
-        <v>123059136</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>15</v>
+        <v>87059136</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>229139405</v>
@@ -7105,17 +7007,13 @@
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">F7+F8+F9</f>
-        <v>336161064</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <f aca="false">G7+G8+G9</f>
-        <v>436161064</v>
-      </c>
-      <c r="H10" s="13"/>
+        <v>400161064</v>
+      </c>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>343932836</v>
@@ -7132,38 +7030,32 @@
         <f aca="false">E11</f>
         <v>300161064</v>
       </c>
-      <c r="G11" s="8" t="n">
-        <f aca="false">E11</f>
-        <v>300161064</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>18</v>
+      <c r="G11" s="14" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
         <f aca="false">②前提!$C$25</f>
-        <v>36000000</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
         <f aca="false">②前提!$C$25</f>
-        <v>36000000</v>
+        <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">②前提!$C$25</f>
-        <v>36000000</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <f aca="false">②前提!$C$25</f>
-        <v>36000000</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
@@ -7174,21 +7066,17 @@
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">D11+D12</f>
-        <v>336161064</v>
+        <v>300161064</v>
       </c>
       <c r="E13" s="12" t="n">
         <f aca="false">E11+E12</f>
-        <v>336161064</v>
+        <v>300161064</v>
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">F11+F12</f>
-        <v>336161064</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <f aca="false">G11+G12</f>
-        <v>336161064</v>
-      </c>
-      <c r="H13" s="13"/>
+        <v>300161064</v>
+      </c>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="15" t="s">
@@ -7199,25 +7087,23 @@
       </c>
       <c r="D14" s="16" t="n">
         <f aca="false">D10-D13</f>
-        <v>-135559136</v>
+        <v>-99559136</v>
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">E10-E13</f>
-        <v>-23059136</v>
+        <v>12940864</v>
       </c>
       <c r="F14" s="16" t="n">
-        <f aca="false">F10-F13</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <f aca="false">G10-G13</f>
+        <f aca="false">②前提!$C$29</f>
         <v>100000000</v>
       </c>
-      <c r="H14" s="17"/>
+      <c r="G14" s="17" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -7233,15 +7119,11 @@
         <f aca="false">②前提!$C$22</f>
         <v>20000000</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <f aca="false">②前提!$C$22</f>
-        <v>20000000</v>
-      </c>
-      <c r="H15" s="3"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>10000000</v>
@@ -7258,40 +7140,32 @@
         <f aca="false">②前提!$C$26</f>
         <v>15000000</v>
       </c>
-      <c r="G16" s="8" t="n">
-        <f aca="false">②前提!$C$26</f>
-        <v>15000000</v>
-      </c>
-      <c r="H16" s="3"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="19" t="n">
         <v>-124793431</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">D14+D15-D16</f>
-        <v>-150559136</v>
+        <v>-114559136</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E14+E15-E16</f>
-        <v>-18059136</v>
+        <v>17940864</v>
       </c>
       <c r="F17" s="19" t="n">
         <f aca="false">F14+F15-F16</f>
-        <v>5000000</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <f aca="false">G14+G15-G16</f>
         <v>105000000</v>
       </c>
-      <c r="H17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -7305,75 +7179,55 @@
       <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>26</v>
+      <c r="G18" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>-124793431</v>
       </c>
       <c r="D19" s="12" t="n">
         <f aca="false">D17-D18</f>
-        <v>-150559136</v>
+        <v>-114559136</v>
       </c>
       <c r="E19" s="12" t="n">
         <f aca="false">E17-E18</f>
-        <v>-18059136</v>
+        <v>17940864</v>
       </c>
       <c r="F19" s="12" t="n">
         <f aca="false">F17-F18</f>
-        <v>5000000</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <f aca="false">G17-G18</f>
         <v>105000000</v>
       </c>
-      <c r="H19" s="13"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">F9/②前提!$C$9</f>
-        <v>44731623.379295</v>
+        <v>168883018.135581</v>
       </c>
       <c r="D23" s="25" t="n">
         <f aca="false">C23/②前提!$C$30</f>
-        <v>0.0419621232451172</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <f aca="false">G9/②前提!$C$9</f>
-        <v>238718177.685991</v>
-      </c>
-      <c r="D24" s="25" t="n">
-        <f aca="false">C24/②前提!$C$30</f>
-        <v>0.223938252988735</v>
+        <v>0.158426846281033</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7383,7 +7237,6 @@
       <c r="E26" s="26"/>
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="27" t="s">
@@ -7394,7 +7247,6 @@
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="26" t="s">
@@ -7405,7 +7257,6 @@
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="26" t="s">
@@ -7416,7 +7267,6 @@
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="26" t="s">
@@ -7427,18 +7277,16 @@
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
       <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="26"/>
@@ -7447,7 +7295,6 @@
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="28" t="s">
@@ -7458,30 +7305,39 @@
       <c r="E33" s="28"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B34:H34"/>
+  <mergeCells count="10">
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7510,17 +7366,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7528,57 +7384,57 @@
         <v>3</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L5" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M5" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N5" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P5" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q5" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R5" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>32789307</v>
@@ -7635,7 +7491,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>18502877</v>
@@ -7692,7 +7548,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="34" t="n">
         <v>14286430</v>
@@ -7749,12 +7605,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>1450000</v>
@@ -7811,7 +7667,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>5733907</v>
@@ -7868,7 +7724,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2678253</v>
@@ -7925,7 +7781,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>932201</v>
@@ -7982,7 +7838,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>53900</v>
@@ -8039,7 +7895,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>234134</v>
@@ -8096,7 +7952,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2786025</v>
@@ -8153,7 +8009,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4193310</v>
@@ -8210,7 +8066,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>298477</v>
@@ -8267,7 +8123,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>956603</v>
@@ -8324,7 +8180,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>385679</v>
@@ -8381,7 +8237,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>163840</v>
@@ -8438,7 +8294,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0</v>
@@ -8495,7 +8351,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>208971</v>
@@ -8552,7 +8408,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>732759</v>
@@ -8609,7 +8465,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>216380</v>
@@ -8666,7 +8522,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>31310</v>
@@ -8723,7 +8579,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>64335</v>
@@ -8780,7 +8636,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10000</v>
@@ -8837,7 +8693,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>0</v>
@@ -8894,7 +8750,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>10091</v>
@@ -8951,7 +8807,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>3815699</v>
@@ -9008,7 +8864,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>419018</v>
@@ -9191,7 +9047,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -9221,17 +9077,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -9241,27 +9097,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I6:K6)</f>
         <v>32428397.3333333</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I8:K8)</f>
@@ -9270,7 +9126,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I34:K34)</f>
@@ -9279,7 +9135,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="44" t="n">
         <f aca="false">C7/C6</f>
@@ -9288,7 +9144,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
@@ -9298,120 +9154,120 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="45" t="n">
         <v>60000000</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="45" t="n">
         <v>2500000</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" s="45" t="n">
         <v>20000000</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="45" t="n">
         <v>20000000</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="46" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="34" t="n">
         <f aca="false">SUM(C13:C19)</f>
         <v>132500000</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" s="8" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>112500000</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="8" t="n">
         <f aca="false">C19</f>
@@ -9420,7 +9276,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="40"/>
@@ -9430,79 +9286,79 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" s="45" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>0</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" s="45" t="n">
         <v>15000000</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" s="47" t="n">
         <v>6</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C28" s="47" t="n">
         <v>6</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C29" s="45" t="n">
         <v>100000000</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C30" s="45" t="n">
         <v>1066000000</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C31" s="48" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="49" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -9533,12 +9389,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9546,51 +9402,51 @@
         <v>3</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O4" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="50"/>
@@ -9609,7 +9465,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="51" t="n">
         <f aca="false">②前提!$C$6</f>
@@ -9670,7 +9526,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="51" t="n">
         <f aca="false">C6-C8</f>
@@ -9731,7 +9587,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="C8" s="51" t="n">
         <f aca="false">②前提!$C$7</f>
@@ -9792,7 +9648,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C9" s="51" t="n">
         <f aca="false">②前提!$C$13/12</f>
@@ -9853,7 +9709,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="51" t="n">
         <f aca="false">②前提!$C$14/12</f>
@@ -9914,7 +9770,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C11" s="51" t="n">
         <f aca="false">②前提!$C$15/12</f>
@@ -9975,7 +9831,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="51" t="n">
         <f aca="false">②前提!$C$16/12</f>
@@ -10036,7 +9892,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C13" s="51" t="n">
         <f aca="false">②前提!$C$17/12</f>
@@ -10097,7 +9953,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$27,②前提!$C$18,0)</f>
@@ -10154,7 +10010,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">C8+SUM(C9:C13)</f>
@@ -10215,7 +10071,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="50"/>
@@ -10234,7 +10090,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)</f>
@@ -10295,7 +10151,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I12:K12)</f>
@@ -10356,7 +10212,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I13:K13)</f>
@@ -10417,7 +10273,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I14:K14)</f>
@@ -10478,7 +10334,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I15:K15)</f>
@@ -10539,7 +10395,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I16:K16)</f>
@@ -10600,7 +10456,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I17:K17)</f>
@@ -10661,7 +10517,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I18:K18)</f>
@@ -10722,7 +10578,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I19:K19)</f>
@@ -10783,7 +10639,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I20:K20)</f>
@@ -10844,7 +10700,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I21:K21)</f>
@@ -10905,7 +10761,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I22:K22)</f>
@@ -10966,7 +10822,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I23:K23)</f>
@@ -11027,7 +10883,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C31" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I24:K24)</f>
@@ -11088,7 +10944,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I25:K25)</f>
@@ -11149,7 +11005,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I26:K26)</f>
@@ -11210,7 +11066,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I27:K27)</f>
@@ -11271,7 +11127,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I28:K28)</f>
@@ -11332,7 +11188,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I29:K29)</f>
@@ -11393,7 +11249,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I30:K30)</f>
@@ -11454,7 +11310,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I31:K31)</f>
@@ -11515,7 +11371,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I32:K32)</f>
@@ -11576,7 +11432,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I33:K33)</f>
@@ -11637,7 +11493,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="12" t="n">
         <f aca="false">SUM(C18:C40)</f>
@@ -11698,63 +11554,63 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C42" s="51" t="n">
         <f aca="false">②前提!$C$25/12</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="D42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="J42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="K42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="M42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="N42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="O42" s="8" t="n">
         <f aca="false">$C$42</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="P42" s="34" t="n">
         <f aca="false">SUM(D42:O42)</f>
-        <v>36000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11763,64 +11619,64 @@
       </c>
       <c r="C43" s="12" t="n">
         <f aca="false">C41+C42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="D43" s="12" t="n">
         <f aca="false">D41+D42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="E43" s="12" t="n">
         <f aca="false">E41+E42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="F43" s="12" t="n">
         <f aca="false">F41+F42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="G43" s="12" t="n">
         <f aca="false">G41+G42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="H43" s="12" t="n">
         <f aca="false">H41+H42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="I43" s="12" t="n">
         <f aca="false">I41+I42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="J43" s="12" t="n">
         <f aca="false">J41+J42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="K43" s="12" t="n">
         <f aca="false">K41+K42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="L43" s="12" t="n">
         <f aca="false">L41+L42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="M43" s="12" t="n">
         <f aca="false">M41+M42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="N43" s="12" t="n">
         <f aca="false">N41+N42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="O43" s="12" t="n">
         <f aca="false">O41+O42</f>
-        <v>28013422</v>
+        <v>25013422</v>
       </c>
       <c r="P43" s="12" t="n">
         <f aca="false">SUM(D43:O43)</f>
-        <v>336161064</v>
+        <v>300161064</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C45" s="50"/>
       <c r="D45" s="50"/>
@@ -11843,64 +11699,64 @@
       </c>
       <c r="C46" s="16" t="n">
         <f aca="false">C15-C43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="D46" s="16" t="n">
         <f aca="false">D15-D43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="E46" s="16" t="n">
         <f aca="false">E15-E43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="F46" s="16" t="n">
         <f aca="false">F15-F43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="G46" s="16" t="n">
         <f aca="false">G15-G43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="H46" s="16" t="n">
         <f aca="false">H15-H43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="I46" s="16" t="n">
         <f aca="false">I15-I43</f>
-        <v>16411738.6666667</v>
+        <v>19411738.6666667</v>
       </c>
       <c r="J46" s="16" t="n">
         <f aca="false">J15-J43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="K46" s="16" t="n">
         <f aca="false">K15-K43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="L46" s="16" t="n">
         <f aca="false">L15-L43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="M46" s="16" t="n">
         <f aca="false">M15-M43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="N46" s="16" t="n">
         <f aca="false">N15-N43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="O46" s="16" t="n">
         <f aca="false">O15-O43</f>
-        <v>-3588261.33333333</v>
+        <v>-588261.333333332</v>
       </c>
       <c r="P46" s="16" t="n">
         <f aca="false">SUM(D46:O46)</f>
-        <v>-23059136</v>
+        <v>12940864</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D47" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$28,②前提!$C$19,0)</f>
@@ -11957,7 +11813,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C48" s="51" t="n">
         <f aca="false">②前提!$C$26/12</f>
@@ -12018,126 +11874,126 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C49" s="19" t="n">
         <f aca="false">C46+C47-C48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="D49" s="19" t="n">
         <f aca="false">D46+D47-D48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="E49" s="19" t="n">
         <f aca="false">E46+E47-E48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="F49" s="19" t="n">
         <f aca="false">F46+F47-F48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="G49" s="19" t="n">
         <f aca="false">G46+G47-G48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="H49" s="19" t="n">
         <f aca="false">H46+H47-H48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="I49" s="19" t="n">
         <f aca="false">I46+I47-I48</f>
-        <v>35161738.6666667</v>
+        <v>38161738.6666667</v>
       </c>
       <c r="J49" s="19" t="n">
         <f aca="false">J46+J47-J48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="K49" s="19" t="n">
         <f aca="false">K46+K47-K48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="L49" s="19" t="n">
         <f aca="false">L46+L47-L48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="M49" s="19" t="n">
         <f aca="false">M46+M47-M48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="N49" s="19" t="n">
         <f aca="false">N46+N47-N48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="O49" s="19" t="n">
         <f aca="false">O46+O47-O48</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="P49" s="19" t="n">
         <f aca="false">SUM(D49:O49)</f>
-        <v>-18059136</v>
+        <v>17940864</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D50" s="52" t="n">
         <f aca="false">D49</f>
-        <v>-4838261.33333333</v>
+        <v>-1838261.33333333</v>
       </c>
       <c r="E50" s="52" t="n">
         <f aca="false">D50+E49</f>
-        <v>-9676522.66666666</v>
+        <v>-3676522.66666666</v>
       </c>
       <c r="F50" s="52" t="n">
         <f aca="false">E50+F49</f>
-        <v>-14514784</v>
+        <v>-5514784</v>
       </c>
       <c r="G50" s="52" t="n">
         <f aca="false">F50+G49</f>
-        <v>-19353045.3333333</v>
+        <v>-7353045.33333333</v>
       </c>
       <c r="H50" s="52" t="n">
         <f aca="false">G50+H49</f>
-        <v>-24191306.6666667</v>
+        <v>-9191306.66666666</v>
       </c>
       <c r="I50" s="52" t="n">
         <f aca="false">H50+I49</f>
-        <v>10970432</v>
+        <v>28970432</v>
       </c>
       <c r="J50" s="52" t="n">
         <f aca="false">I50+J49</f>
-        <v>6132170.66666667</v>
+        <v>27132170.6666667</v>
       </c>
       <c r="K50" s="52" t="n">
         <f aca="false">J50+K49</f>
-        <v>1293909.33333334</v>
+        <v>25293909.3333333</v>
       </c>
       <c r="L50" s="52" t="n">
         <f aca="false">K50+L49</f>
-        <v>-3544351.99999999</v>
+        <v>23455648</v>
       </c>
       <c r="M50" s="52" t="n">
         <f aca="false">L50+M49</f>
-        <v>-8382613.33333333</v>
+        <v>21617386.6666667</v>
       </c>
       <c r="N50" s="52" t="n">
         <f aca="false">M50+N49</f>
-        <v>-13220874.6666667</v>
+        <v>19779125.3333333</v>
       </c>
       <c r="O50" s="52" t="n">
         <f aca="false">N50+O49</f>
-        <v>-18059136</v>
+        <v>17940864</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -12156,7 +12012,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:E14"/>
+  <dimension ref="B1:F13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -12167,31 +12023,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C5" s="54" t="n">
         <v>-114793431</v>
@@ -12201,12 +12057,12 @@
         <v>-114793431</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">②前提!$C$7*12-229139405</f>
@@ -12217,12 +12073,12 @@
         <v>-143330908</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">343932836-②前提!$C$8*12</f>
@@ -12233,12 +12089,12 @@
         <v>-99559136</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">②前提!$C$21</f>
@@ -12249,64 +12105,56 @@
         <v>12940864</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C9" s="8" t="n">
         <f aca="false">-②前提!$C$25</f>
-        <v>-36000000</v>
+        <v>-0</v>
       </c>
       <c r="D9" s="34" t="n">
         <f aca="false">D8+C9</f>
-        <v>-23059136</v>
+        <v>12940864</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">D9</f>
-        <v>-23059136</v>
+        <v>12940864</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C13" s="24" t="n">
         <f aca="false">①サマリー!C23</f>
-        <v>44731623.379295</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <f aca="false">①サマリー!C24</f>
-        <v>238718177.685991</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>177</v>
+        <v>168883018.135581</v>
+      </c>
+      <c r="E13" s="56" t="n">
+        <f aca="false">①サマリー!D23</f>
+        <v>0.158426846281033</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -12337,18 +12185,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="56" t="s">
-        <v>178</v>
+      <c r="B1" s="57" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -12359,71 +12207,71 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="57" t="n">
+        <v>188</v>
+      </c>
+      <c r="C6" s="58" t="n">
         <v>560</v>
       </c>
-      <c r="D6" s="57" t="n">
+      <c r="D6" s="58" t="n">
         <v>470</v>
       </c>
-      <c r="E6" s="57" t="n">
+      <c r="E6" s="58" t="n">
         <v>480</v>
       </c>
-      <c r="F6" s="57" t="n">
+      <c r="F6" s="58" t="n">
         <v>530</v>
       </c>
-      <c r="G6" s="57" t="n">
+      <c r="G6" s="58" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="58" t="n">
+        <v>189</v>
+      </c>
+      <c r="C7" s="59" t="n">
         <f aca="false">G6-E6</f>
         <v>140</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="59" t="n">
+        <v>190</v>
+      </c>
+      <c r="E7" s="60" t="n">
         <f aca="false">C7/6</f>
         <v>23.3333333333333</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C10" s="40"/>
       <c r="D10" s="40"/>
@@ -12446,73 +12294,73 @@
         <v>3</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O11" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P11" s="41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C12" s="45" t="n">
         <v>420000000</v>
       </c>
       <c r="Q12" s="43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C13" s="45" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D14" s="45" t="n">
         <v>0</v>
@@ -12555,12 +12403,12 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D15" s="45" t="n">
         <v>0</v>
@@ -12603,12 +12451,12 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D16" s="12" t="n">
         <f aca="false">D17+$C$13+D14+D15</f>
@@ -12665,7 +12513,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">③FY2027月次推移!D7</f>
@@ -12722,74 +12570,74 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="60" t="n">
+        <v>205</v>
+      </c>
+      <c r="D18" s="61" t="n">
         <f aca="false">$C$12+D16-D17</f>
         <v>420000000</v>
       </c>
-      <c r="E18" s="60" t="n">
+      <c r="E18" s="61" t="n">
         <f aca="false">D18+E16-E17</f>
         <v>420000000</v>
       </c>
-      <c r="F18" s="60" t="n">
+      <c r="F18" s="61" t="n">
         <f aca="false">E18+F16-F17</f>
         <v>420000000</v>
       </c>
-      <c r="G18" s="60" t="n">
+      <c r="G18" s="61" t="n">
         <f aca="false">F18+G16-G17</f>
         <v>420000000</v>
       </c>
-      <c r="H18" s="60" t="n">
+      <c r="H18" s="61" t="n">
         <f aca="false">G18+H16-H17</f>
         <v>420000000</v>
       </c>
-      <c r="I18" s="60" t="n">
+      <c r="I18" s="61" t="n">
         <f aca="false">H18+I16-I17</f>
         <v>420000000</v>
       </c>
-      <c r="J18" s="60" t="n">
+      <c r="J18" s="61" t="n">
         <f aca="false">I18+J16-J17</f>
         <v>420000000</v>
       </c>
-      <c r="K18" s="60" t="n">
+      <c r="K18" s="61" t="n">
         <f aca="false">J18+K16-K17</f>
         <v>420000000</v>
       </c>
-      <c r="L18" s="60" t="n">
+      <c r="L18" s="61" t="n">
         <f aca="false">K18+L16-L17</f>
         <v>420000000</v>
       </c>
-      <c r="M18" s="60" t="n">
+      <c r="M18" s="61" t="n">
         <f aca="false">L18+M16-M17</f>
         <v>420000000</v>
       </c>
-      <c r="N18" s="60" t="n">
+      <c r="N18" s="61" t="n">
         <f aca="false">M18+N16-N17</f>
         <v>420000000</v>
       </c>
-      <c r="O18" s="60" t="n">
+      <c r="O18" s="61" t="n">
         <f aca="false">N18+O16-O17</f>
         <v>420000000</v>
       </c>
-      <c r="P18" s="61" t="n">
+      <c r="P18" s="62" t="n">
         <f aca="false">O18</f>
         <v>420000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -12821,17 +12669,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -12851,66 +12699,66 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C5" s="45" t="n">
         <v>24390278</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="62" t="n">
+        <v>214</v>
+      </c>
+      <c r="C6" s="63" t="n">
         <v>0.1</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="63" t="n">
+        <v>215</v>
+      </c>
+      <c r="C7" s="64" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="63" t="n">
+        <v>217</v>
+      </c>
+      <c r="C8" s="64" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C9" s="45" t="n">
         <v>2662179</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12918,51 +12766,51 @@
         <v>3</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L12" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O12" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P12" s="41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="36" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="50"/>
@@ -12980,8 +12828,8 @@
       <c r="P13" s="50"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="64" t="s">
-        <v>223</v>
+      <c r="B14" s="65" t="s">
+        <v>224</v>
       </c>
       <c r="D14" s="51" t="n">
         <f aca="false">③FY2027月次推移!D6*(1+$C$6)</f>
@@ -13037,8 +12885,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="64" t="s">
-        <v>224</v>
+      <c r="B15" s="65" t="s">
+        <v>225</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!D9:D13)*(1+$C$6)</f>
@@ -13094,8 +12942,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="64" t="s">
-        <v>225</v>
+      <c r="B16" s="65" t="s">
+        <v>226</v>
       </c>
       <c r="D16" s="51" t="n">
         <f aca="false">③FY2027月次推移!D14*(1+$C$6)</f>
@@ -13152,7 +13000,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D17" s="45" t="n">
         <v>220000000</v>
@@ -13195,12 +13043,12 @@
         <v>220000000</v>
       </c>
       <c r="Q17" s="43" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D18" s="12" t="n">
         <f aca="false">SUM(D14:D17)</f>
@@ -13257,7 +13105,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="36" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="50"/>
@@ -13275,8 +13123,8 @@
       <c r="P20" s="50"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="64" t="s">
-        <v>230</v>
+      <c r="B21" s="65" t="s">
+        <v>231</v>
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D16*(1+$C$6)</f>
@@ -13332,8 +13180,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="64" t="s">
-        <v>231</v>
+      <c r="B22" s="65" t="s">
+        <v>232</v>
       </c>
       <c r="D22" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
@@ -13389,8 +13237,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="64" t="s">
-        <v>232</v>
+      <c r="B23" s="65" t="s">
+        <v>233</v>
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">((③FY2027月次推移!D41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
@@ -13446,65 +13294,65 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="64" t="s">
-        <v>233</v>
+      <c r="B24" s="65" t="s">
+        <v>234</v>
       </c>
       <c r="D24" s="51" t="n">
         <f aca="false">③FY2027月次推移!D42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="E24" s="51" t="n">
         <f aca="false">③FY2027月次推移!E42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="F24" s="51" t="n">
         <f aca="false">③FY2027月次推移!F42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="G24" s="51" t="n">
         <f aca="false">③FY2027月次推移!G42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="51" t="n">
         <f aca="false">③FY2027月次推移!H42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="I24" s="51" t="n">
         <f aca="false">③FY2027月次推移!I42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="J24" s="51" t="n">
         <f aca="false">③FY2027月次推移!J42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="K24" s="51" t="n">
         <f aca="false">③FY2027月次推移!K42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="L24" s="51" t="n">
         <f aca="false">③FY2027月次推移!L42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="M24" s="51" t="n">
         <f aca="false">③FY2027月次推移!M42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="N24" s="51" t="n">
         <f aca="false">③FY2027月次推移!N42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="O24" s="51" t="n">
         <f aca="false">③FY2027月次推移!O42*(1+$C$6)</f>
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="P24" s="34" t="n">
         <f aca="false">SUM(D24:O24)</f>
-        <v>39600000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="64" t="s">
-        <v>234</v>
+      <c r="B25" s="65" t="s">
+        <v>235</v>
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">③FY2027月次推移!D48</f>
@@ -13561,7 +13409,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D26" s="45" t="n">
         <v>0</v>
@@ -13604,12 +13452,12 @@
         <v>35000000</v>
       </c>
       <c r="Q26" s="43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D27" s="45" t="n">
         <v>0</v>
@@ -13654,121 +13502,121 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D28" s="12" t="n">
         <f aca="false">SUM(D21:D27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="E28" s="12" t="n">
         <f aca="false">SUM(E21:E27)</f>
-        <v>75148191.5666667</v>
+        <v>71848191.5666667</v>
       </c>
       <c r="F28" s="12" t="n">
         <f aca="false">SUM(F21:F27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="G28" s="12" t="n">
         <f aca="false">SUM(G21:G27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="H28" s="12" t="n">
         <f aca="false">SUM(H21:H27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="I28" s="12" t="n">
         <f aca="false">SUM(I21:I27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="J28" s="12" t="n">
         <f aca="false">SUM(J21:J27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="K28" s="12" t="n">
         <f aca="false">SUM(K21:K27)</f>
-        <v>49685086.5666667</v>
+        <v>46385086.5666667</v>
       </c>
       <c r="L28" s="12" t="n">
         <f aca="false">SUM(L21:L27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="M28" s="12" t="n">
         <f aca="false">SUM(M21:M27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="N28" s="12" t="n">
         <f aca="false">SUM(N21:N27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="O28" s="12" t="n">
         <f aca="false">SUM(O21:O27)</f>
-        <v>44685086.5666667</v>
+        <v>41385086.5666667</v>
       </c>
       <c r="P28" s="12" t="n">
         <f aca="false">SUM(D28:O28)</f>
-        <v>571684143.8</v>
+        <v>532084143.8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D29" s="16" t="n">
         <f aca="false">D18-D28</f>
-        <v>219465317.166667</v>
+        <v>222765317.166667</v>
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">E18-E28</f>
-        <v>-30997787.8333333</v>
+        <v>-27697787.8333333</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">F18-F28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">G18-G28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="H29" s="16" t="n">
         <f aca="false">H18-H28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="I29" s="16" t="n">
         <f aca="false">I18-I28</f>
-        <v>21465317.1666667</v>
+        <v>24765317.1666667</v>
       </c>
       <c r="J29" s="16" t="n">
         <f aca="false">J18-J28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="K29" s="16" t="n">
         <f aca="false">K18-K28</f>
-        <v>-5534682.83333334</v>
+        <v>-2234682.83333334</v>
       </c>
       <c r="L29" s="16" t="n">
         <f aca="false">L18-L28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="M29" s="16" t="n">
         <f aca="false">M18-M28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="N29" s="16" t="n">
         <f aca="false">N18-N28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="O29" s="16" t="n">
         <f aca="false">O18-O28</f>
-        <v>-534682.833333336</v>
+        <v>2765317.16666666</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">SUM(D29:O29)</f>
-        <v>200120701</v>
+        <v>239720701</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -13786,8 +13634,8 @@
       <c r="P31" s="50"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="64" t="s">
-        <v>241</v>
+      <c r="B32" s="65" t="s">
+        <v>242</v>
       </c>
       <c r="D32" s="51" t="n">
         <f aca="false">-$C$9</f>
@@ -13843,8 +13691,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="64" t="s">
-        <v>242</v>
+      <c r="B33" s="65" t="s">
+        <v>243</v>
       </c>
       <c r="D33" s="51" t="n">
         <f aca="false">$C$10</f>
@@ -13901,7 +13749,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D34" s="45" t="n">
         <v>0</v>
@@ -13945,8 +13793,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="64" t="s">
-        <v>244</v>
+      <c r="B35" s="65" t="s">
+        <v>245</v>
       </c>
       <c r="D35" s="51" t="n">
         <f aca="false">③FY2027月次推移!D47</f>
@@ -14003,7 +13851,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D36" s="45" t="n">
         <v>-200000000</v>
@@ -14046,12 +13894,12 @@
         <v>-200000000</v>
       </c>
       <c r="Q36" s="30" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D37" s="12" t="n">
         <f aca="false">SUM(D32:D36)</f>
@@ -14108,64 +13956,64 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D39" s="12" t="n">
         <f aca="false">D29+D37</f>
-        <v>16803138.1666667</v>
+        <v>20103138.1666667</v>
       </c>
       <c r="E39" s="12" t="n">
         <f aca="false">E29+E37</f>
-        <v>-33659966.8333333</v>
+        <v>-30359966.8333333</v>
       </c>
       <c r="F39" s="12" t="n">
         <f aca="false">F29+F37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="G39" s="12" t="n">
         <f aca="false">G29+G37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="H39" s="12" t="n">
         <f aca="false">H29+H37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="I39" s="12" t="n">
         <f aca="false">I29+I37</f>
-        <v>38803138.1666667</v>
+        <v>42103138.1666667</v>
       </c>
       <c r="J39" s="12" t="n">
         <f aca="false">J29+J37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="K39" s="12" t="n">
         <f aca="false">K29+K37</f>
-        <v>-8196861.83333334</v>
+        <v>-4896861.83333334</v>
       </c>
       <c r="L39" s="12" t="n">
         <f aca="false">L29+L37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="M39" s="12" t="n">
         <f aca="false">M29+M37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="N39" s="12" t="n">
         <f aca="false">N29+N37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="O39" s="12" t="n">
         <f aca="false">O29+O37</f>
-        <v>-3196861.83333334</v>
+        <v>103138.166666664</v>
       </c>
       <c r="P39" s="12" t="n">
         <f aca="false">SUM(D39:O39)</f>
-        <v>-11825447</v>
+        <v>27774553</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D40" s="8" t="n">
         <f aca="false">$C$5</f>
@@ -14173,194 +14021,194 @@
       </c>
       <c r="E40" s="8" t="n">
         <f aca="false">D41</f>
-        <v>41193416.1666667</v>
+        <v>44493416.1666667</v>
       </c>
       <c r="F40" s="8" t="n">
         <f aca="false">E41</f>
-        <v>7533449.33333336</v>
+        <v>14133449.3333334</v>
       </c>
       <c r="G40" s="8" t="n">
         <f aca="false">F41</f>
-        <v>4336587.50000002</v>
+        <v>14236587.5</v>
       </c>
       <c r="H40" s="8" t="n">
         <f aca="false">G41</f>
-        <v>1139725.66666669</v>
+        <v>14339725.6666667</v>
       </c>
       <c r="I40" s="8" t="n">
         <f aca="false">H41</f>
-        <v>-2057136.16666665</v>
+        <v>14442863.8333334</v>
       </c>
       <c r="J40" s="8" t="n">
         <f aca="false">I41</f>
-        <v>36746002</v>
+        <v>56546002</v>
       </c>
       <c r="K40" s="8" t="n">
         <f aca="false">J41</f>
-        <v>33549140.1666667</v>
+        <v>56649140.1666667</v>
       </c>
       <c r="L40" s="8" t="n">
         <f aca="false">K41</f>
-        <v>25352278.3333333</v>
+        <v>51752278.3333333</v>
       </c>
       <c r="M40" s="8" t="n">
         <f aca="false">L41</f>
-        <v>22155416.5</v>
+        <v>51855416.5</v>
       </c>
       <c r="N40" s="8" t="n">
         <f aca="false">M41</f>
-        <v>18958554.6666667</v>
+        <v>51958554.6666667</v>
       </c>
       <c r="O40" s="8" t="n">
         <f aca="false">N41</f>
-        <v>15761692.8333333</v>
+        <v>52061692.8333333</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D41" s="19" t="n">
         <f aca="false">D40+D39</f>
-        <v>41193416.1666667</v>
+        <v>44493416.1666667</v>
       </c>
       <c r="E41" s="19" t="n">
         <f aca="false">E40+E39</f>
-        <v>7533449.33333336</v>
+        <v>14133449.3333334</v>
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">F40+F39</f>
-        <v>4336587.50000002</v>
+        <v>14236587.5</v>
       </c>
       <c r="G41" s="19" t="n">
         <f aca="false">G40+G39</f>
-        <v>1139725.66666669</v>
+        <v>14339725.6666667</v>
       </c>
       <c r="H41" s="19" t="n">
         <f aca="false">H40+H39</f>
-        <v>-2057136.16666665</v>
+        <v>14442863.8333334</v>
       </c>
       <c r="I41" s="19" t="n">
         <f aca="false">I40+I39</f>
-        <v>36746002</v>
+        <v>56546002</v>
       </c>
       <c r="J41" s="19" t="n">
         <f aca="false">J40+J39</f>
-        <v>33549140.1666667</v>
+        <v>56649140.1666667</v>
       </c>
       <c r="K41" s="19" t="n">
         <f aca="false">K40+K39</f>
-        <v>25352278.3333333</v>
+        <v>51752278.3333333</v>
       </c>
       <c r="L41" s="19" t="n">
         <f aca="false">L40+L39</f>
-        <v>22155416.5</v>
+        <v>51855416.5</v>
       </c>
       <c r="M41" s="19" t="n">
         <f aca="false">M40+M39</f>
-        <v>18958554.6666667</v>
+        <v>51958554.6666667</v>
       </c>
       <c r="N41" s="19" t="n">
         <f aca="false">N40+N39</f>
-        <v>15761692.8333333</v>
+        <v>52061692.8333333</v>
       </c>
       <c r="O41" s="19" t="n">
         <f aca="false">O40+O39</f>
-        <v>12564831</v>
+        <v>52164831</v>
       </c>
       <c r="P41" s="52" t="n">
         <f aca="false">O41</f>
-        <v>12564831</v>
+        <v>52164831</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="65" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="66" t="n">
+      <c r="B42" s="66" t="s">
+        <v>252</v>
+      </c>
+      <c r="D42" s="67" t="n">
         <f aca="false">IF(D41&lt;0,D41,0)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="66" t="n">
+      <c r="E42" s="67" t="n">
         <f aca="false">IF(E41&lt;0,E41,0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="66" t="n">
+      <c r="F42" s="67" t="n">
         <f aca="false">IF(F41&lt;0,F41,0)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="66" t="n">
+      <c r="G42" s="67" t="n">
         <f aca="false">IF(G41&lt;0,G41,0)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="66" t="n">
+      <c r="H42" s="67" t="n">
         <f aca="false">IF(H41&lt;0,H41,0)</f>
-        <v>-2057136.16666665</v>
-      </c>
-      <c r="I42" s="66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="67" t="n">
         <f aca="false">IF(I41&lt;0,I41,0)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="66" t="n">
+      <c r="J42" s="67" t="n">
         <f aca="false">IF(J41&lt;0,J41,0)</f>
         <v>0</v>
       </c>
-      <c r="K42" s="66" t="n">
+      <c r="K42" s="67" t="n">
         <f aca="false">IF(K41&lt;0,K41,0)</f>
         <v>0</v>
       </c>
-      <c r="L42" s="66" t="n">
+      <c r="L42" s="67" t="n">
         <f aca="false">IF(L41&lt;0,L41,0)</f>
         <v>0</v>
       </c>
-      <c r="M42" s="66" t="n">
+      <c r="M42" s="67" t="n">
         <f aca="false">IF(M41&lt;0,M41,0)</f>
         <v>0</v>
       </c>
-      <c r="N42" s="66" t="n">
+      <c r="N42" s="67" t="n">
         <f aca="false">IF(N41&lt;0,N41,0)</f>
         <v>0</v>
       </c>
-      <c r="O42" s="66" t="n">
+      <c r="O42" s="67" t="n">
         <f aca="false">IF(O41&lt;0,O41,0)</f>
         <v>0</v>
       </c>
-      <c r="P42" s="66" t="n">
+      <c r="P42" s="67" t="n">
         <f aca="false">MIN(D42:O42)</f>
-        <v>-2057136.16666665</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="30" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="30" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="39" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C50" s="40"/>
       <c r="D50" s="40"/>
@@ -14380,121 +14228,121 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="53" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C52" s="34" t="n">
         <f aca="false">O41</f>
-        <v>12564831</v>
+        <v>52164831</v>
       </c>
       <c r="D52" s="34" t="n">
         <f aca="false">MIN(D41:O41)</f>
-        <v>-2057136.16666665</v>
+        <v>14133449.3333334</v>
       </c>
       <c r="E52" s="24" t="n">
         <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$56,MAX(0,-D52+$C$56))</f>
-        <v>37728373.2333333</v>
+        <v>21537787.7333333</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="67" t="s">
-        <v>266</v>
-      </c>
-      <c r="C53" s="66" t="n">
+      <c r="B53" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="67" t="n">
         <f aca="false">C52-(P16+P35)</f>
-        <v>-29435169</v>
-      </c>
-      <c r="D53" s="66" t="n">
+        <v>10164831</v>
+      </c>
+      <c r="D53" s="67" t="n">
         <f aca="false">D52-(P16+P35)</f>
-        <v>-44057136.1666667</v>
+        <v>-27866550.6666666</v>
       </c>
       <c r="E53" s="24" t="n">
         <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$56,MAX(0,-D53+$C$56))</f>
-        <v>79728373.2333333</v>
+        <v>63537787.7333333</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="67" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" s="66" t="n">
+      <c r="B54" s="68" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54" s="67" t="n">
         <f aca="false">C52-23333333*(1+$C$6)*12</f>
-        <v>-295435164.6</v>
-      </c>
-      <c r="D54" s="66" t="n">
+        <v>-255835164.6</v>
+      </c>
+      <c r="D54" s="67" t="n">
         <f aca="false">D52-23333333*(1+$C$6)*12</f>
-        <v>-310057131.766667</v>
+        <v>-293866546.266667</v>
       </c>
       <c r="E54" s="24" t="n">
         <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$56,MAX(0,-D54+$C$56))</f>
-        <v>345728368.833333</v>
+        <v>329537783.333333</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="67" t="s">
-        <v>270</v>
-      </c>
-      <c r="C55" s="66" t="n">
+      <c r="B55" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55" s="67" t="n">
         <f aca="false">C52-(5043131-$C$9)*12</f>
-        <v>-16006593</v>
-      </c>
-      <c r="D55" s="66" t="n">
+        <v>23593407</v>
+      </c>
+      <c r="D55" s="67" t="n">
         <f aca="false">D52-(5043131-$C$9)*12</f>
-        <v>-30628560.1666667</v>
+        <v>-14437974.6666666</v>
       </c>
       <c r="E55" s="24" t="n">
         <f aca="false">IF(C55&lt;0,-MIN(C55,D55)+$C$56,MAX(0,-D55+$C$56))</f>
-        <v>66299797.2333333</v>
+        <v>50109211.7333333</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C56" s="51" t="n">
         <f aca="false">③FY2027月次推移!$C$6*(1+$C$6)</f>
         <v>35671237.0666667</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="30" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="277">
   <si>
     <r>
       <rPr>
@@ -299,7 +299,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">営業利益
+      <t xml:space="preserve">経常利益
 </t>
     </r>
     <r>
@@ -363,7 +363,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万＋インセンティブ</t>
+      <t xml:space="preserve">＋インセンティブ</t>
     </r>
     <r>
       <rPr>
@@ -382,20 +382,57 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万</t>
+      <t xml:space="preserve">＋クルーザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">＋追加で必要な粗利</t>
   </si>
   <si>
-    <t xml:space="preserve">目標達成に必要な粗利の上積み</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経常利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円の達成に必要な粗利の上積み</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">売上総利益 合計</t>
   </si>
   <si>
-    <t xml:space="preserve">販管費 小計</t>
+    <t xml:space="preserve">販管費</t>
   </si>
   <si>
     <r>
@@ -429,36 +466,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">上場関連コスト</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は計上しない方針</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">販管費 合計</t>
-  </si>
-  <si>
     <t xml:space="preserve">営業利益</t>
   </si>
   <si>
+    <t xml:space="preserve">営業外収益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クルーザー事業利益は営業収益に計上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">営業外費用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">経常利益</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -476,17 +498,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は目標営業利益を固定して逆算</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外収益（投資売買益）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外費用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">経常利益</t>
+      <t xml:space="preserve">は目標経常利益を固定して逆算</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">法人税等</t>
@@ -532,7 +545,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【</t>
+      <t xml:space="preserve">【経常利益</t>
     </r>
     <r>
       <rPr>
@@ -542,7 +555,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">V</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -551,7 +564,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">字回復に必要な追加売上】</t>
+      <t xml:space="preserve">億円に必要な追加売上】</t>
     </r>
   </si>
   <si>
@@ -595,7 +608,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">営業利益</t>
+      <t xml:space="preserve">経常利益</t>
     </r>
     <r>
       <rPr>
@@ -651,10 +664,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円。上乗せなしでは黒字化しない。</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">百万円・経常利益▲</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -662,6 +673,25 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">114.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">B</t>
     </r>
     <r>
@@ -687,7 +717,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円を計上すると営業利益＋</t>
+      <t xml:space="preserve">百万円を全額営業収益に計上すると営業利益＋</t>
     </r>
     <r>
       <rPr>
@@ -696,7 +726,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">12.9</t>
+      <t xml:space="preserve">32.9</t>
     </r>
     <r>
       <rPr>
@@ -740,7 +770,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：営業利益</t>
+      <t xml:space="preserve">：経常利益</t>
     </r>
     <r>
       <rPr>
@@ -783,7 +813,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">87.1</t>
+      <t xml:space="preserve">82.1</t>
     </r>
     <r>
       <rPr>
@@ -817,7 +847,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">6,888</t>
+      <t xml:space="preserve">5,918</t>
     </r>
     <r>
       <rPr>
@@ -861,7 +891,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15.8%</t>
+      <t xml:space="preserve">14.9%</t>
     </r>
     <r>
       <rPr>
@@ -879,6 +909,101 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">※クルーザー事業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円は投資損益ではなく事業利益のため、営業収益に計上（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">※上場関連コストは</t>
     </r>
     <r>
@@ -896,7 +1021,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は計上しない前提（②前提シートで年額を入力すれば再計算されます）。</t>
+      <t xml:space="preserve">は計上しない方針のため、項目自体を削除。</t>
     </r>
   </si>
   <si>
@@ -924,110 +1049,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">百万円はグループ内取引。銀行は正常化調整で控除する可能性が高い。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">※FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">見込には</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026/09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">単月に売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">232.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（通期の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を織り込み。粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">のため営業利益寄与は＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円のみ。</t>
     </r>
   </si>
   <si>
@@ -1430,6 +1451,9 @@
     <t xml:space="preserve">倉庫＆保管・移設代</t>
   </si>
   <si>
+    <t xml:space="preserve">販管費 合計</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1680,9 +1704,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">販管費</t>
-  </si>
-  <si>
     <t xml:space="preserve">売上総利益率</t>
   </si>
   <si>
@@ -1768,7 +1789,31 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">営業収益（原価なし）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業収益（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月按分）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1909,20 +1954,106 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">投資売買益　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cruiser shot</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外収益（一時）</t>
+      <t xml:space="preserve">クルーザー事業利益　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業収益（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クルーザー事業利益　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">営業収益（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -2129,6 +2260,36 @@
   <si>
     <r>
       <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クルーザー事業利益は投資損益ではなく事業利益のため、全額を営業収益に計上。営業外収益は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFC00000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
@@ -2160,9 +2321,18 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">上場関連コスト（年額）</t>
-  </si>
-  <si>
+    <t xml:space="preserve">営業外費用（支払利息等・年額）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事業計画</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -2180,58 +2350,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は計上しない方針のため</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。計上する場合は年額を入力。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">営業外費用（支払利息等・年額）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事業計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">計画値</t>
     </r>
   </si>
@@ -2345,7 +2463,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">投資売買益 計上月（</t>
+      <t xml:space="preserve">クルーザー事業利益 </t>
     </r>
     <r>
       <rPr>
@@ -2362,11 +2480,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">回目 計上月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">クルーザー事業利益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目 計上月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -2375,15 +2523,54 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">目標営業利益</t>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月（期末までに計上）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">目標経常利益</t>
   </si>
   <si>
     <r>
@@ -2403,16 +2590,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の目標</t>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の目標。営業利益ではなく経常利益で設定。</t>
     </r>
   </si>
   <si>
@@ -2967,6 +3154,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">＋クルーザー事業利益</t>
+  </si>
+  <si>
     <t xml:space="preserve">【販売費及び一般管理費】</t>
   </si>
   <si>
@@ -3035,7 +3225,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">か月按分。インセンティブ・投資売買益は②前提で指定した月に一括計上。</t>
+      <t xml:space="preserve">か月按分。インセンティブとクルーザー事業利益は②前提で指定した月に計上（クルーザーは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に各</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円）。</t>
     </r>
   </si>
   <si>
@@ -3232,27 +3479,62 @@
     <t xml:space="preserve">③ 上乗せ案件（営業収益）</t>
   </si>
   <si>
-    <t xml:space="preserve">④ 上場関連コスト</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画値</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋インセンティブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋クルーザー事業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
     </r>
   </si>
   <si>
@@ -3296,46 +3578,16 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">①〜④の合計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【営業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="12"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円に必要な追加売上】</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">営業利益 </t>
+    <t xml:space="preserve">①〜③の合計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経常利益 </t>
     </r>
     <r>
       <rPr>
@@ -4806,6 +5058,68 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">クルーザー事業利益 入金（税込）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027/09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に各</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。課税取引として税込入金と仮定。</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">営業収入 計</t>
   </si>
   <si>
@@ -4821,9 +5135,6 @@
     <t xml:space="preserve">その他販管費（税込・減価償却除く）</t>
   </si>
   <si>
-    <t xml:space="preserve">上場関連コスト（税込）</t>
-  </si>
-  <si>
     <t xml:space="preserve">支払利息</t>
   </si>
   <si>
@@ -4917,7 +5228,7 @@
     <t xml:space="preserve">経常収支</t>
   </si>
   <si>
-    <t xml:space="preserve">【財務・投資収支】</t>
+    <t xml:space="preserve">【財務収支】</t>
   </si>
   <si>
     <t xml:space="preserve">長期借入金 約定返済</t>
@@ -4929,16 +5240,13 @@
     <t xml:space="preserve">新規調達（借入・増資）</t>
   </si>
   <si>
-    <t xml:space="preserve">投資売買益 入金</t>
-  </si>
-  <si>
     <t xml:space="preserve">みずほ銀行 融資返済（在庫販売代金充当）</t>
   </si>
   <si>
     <t xml:space="preserve">在庫販売代金の入金月に同額を一括返済する前提。</t>
   </si>
   <si>
-    <t xml:space="preserve">財務・投資収支 計</t>
+    <t xml:space="preserve">財務収支 計</t>
   </si>
   <si>
     <t xml:space="preserve">当月収支</t>
@@ -5185,26 +5493,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円（税込）＋投資売買益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円が未入金の場合</t>
+      <t xml:space="preserve">百万円＋クルーザー事業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（いずれも税込）が未入金の場合</t>
     </r>
   </si>
   <si>
@@ -6451,7 +6759,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>⑦FY2027資金繰り表!$D$41:$O$41</c:f>
+              <c:f>⑦FY2027資金繰り表!$D$40:$O$40</c:f>
               <c:numCache>
                 <c:formatCode>\¥#,##0;"(¥"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
@@ -6471,25 +6779,25 @@
                   <c:v>14442863.8333334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>56546002</c:v>
+                  <c:v>47546002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>56649140.1666667</c:v>
+                  <c:v>47649140.1666667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51752278.3333333</c:v>
+                  <c:v>42752278.3333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>51855416.5</c:v>
+                  <c:v>42855416.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>51958554.6666667</c:v>
+                  <c:v>42958554.6666667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>52061692.8333333</c:v>
+                  <c:v>43061692.8333333</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>52164831</c:v>
+                  <c:v>54164831</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6504,11 +6812,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="71173310"/>
-        <c:axId val="17219586"/>
+        <c:axId val="92135058"/>
+        <c:axId val="69764832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="71173310"/>
+        <c:axId val="92135058"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6540,7 +6848,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17219586"/>
+        <c:crossAx val="69764832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6548,7 +6856,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="17219586"/>
+        <c:axId val="69764832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6624,7 +6932,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71173310"/>
+        <c:crossAx val="92135058"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6658,14 +6966,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>134640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1038600</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>12600</xdr:rowOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -6673,7 +6981,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="266760" y="11430000"/>
+        <a:off x="266760" y="11239560"/>
         <a:ext cx="8639640" cy="2735640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6928,7 +7236,7 @@
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">E6+F9/②前提!$C$9</f>
-        <v>558023786.135581</v>
+        <v>548324458.420246</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -6964,12 +7272,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="8" t="n">
-        <f aca="false">②前提!$C$21</f>
-        <v>112500000</v>
+        <f aca="false">②前提!$C$22</f>
+        <v>132500000</v>
       </c>
       <c r="F8" s="8" t="n">
-        <f aca="false">②前提!$C$21</f>
-        <v>112500000</v>
+        <f aca="false">②前提!$C$22</f>
+        <v>132500000</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>12</v>
@@ -6983,8 +7291,8 @@
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="n">
-        <f aca="false">②前提!$C$29-E14</f>
-        <v>87059136</v>
+        <f aca="false">②前提!$C$30+F14-F13+F11-F7-F8</f>
+        <v>82059136</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>14</v>
@@ -7003,11 +7311,11 @@
       </c>
       <c r="E10" s="12" t="n">
         <f aca="false">E7+E8</f>
-        <v>313101928</v>
+        <v>333101928</v>
       </c>
       <c r="F10" s="12" t="n">
         <f aca="false">F7+F8+F9</f>
-        <v>400161064</v>
+        <v>415161064</v>
       </c>
       <c r="G10" s="13"/>
     </row>
@@ -7035,199 +7343,155 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <f aca="false">②前提!$C$25</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <f aca="false">②前提!$C$25</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <f aca="false">②前提!$C$25</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="s">
+      <c r="C12" s="16" t="n">
+        <v>-114793431</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">D10-D11</f>
+        <v>-99559136</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">E10-E11</f>
+        <v>32940864</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">F10-F11</f>
+        <v>115000000</v>
+      </c>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>343932836</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <f aca="false">D11+D12</f>
-        <v>300161064</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <f aca="false">E11+E12</f>
-        <v>300161064</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <f aca="false">F11+F12</f>
-        <v>300161064</v>
-      </c>
-      <c r="G13" s="13"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>-114793431</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <f aca="false">D10-D13</f>
-        <v>-99559136</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <f aca="false">E10-E13</f>
-        <v>12940864</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <f aca="false">②前提!$C$29</f>
+      <c r="C14" s="7" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <f aca="false">②前提!$C$26</f>
+        <v>15000000</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <f aca="false">②前提!$C$26</f>
+        <v>15000000</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <f aca="false">②前提!$C$26</f>
+        <v>15000000</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>-124793431</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <f aca="false">D12+D13-D14</f>
+        <v>-114559136</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <f aca="false">E12+E13-E14</f>
+        <v>17940864</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <f aca="false">F12+F13-F14</f>
         <v>100000000</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="G15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <f aca="false">②前提!$C$22</f>
-        <v>20000000</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <f aca="false">②前提!$C$22</f>
-        <v>20000000</v>
-      </c>
-      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
-        <f aca="false">②前提!$C$26</f>
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <f aca="false">②前提!$C$26</f>
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <f aca="false">②前提!$C$26</f>
-        <v>15000000</v>
-      </c>
-      <c r="G16" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="19" t="n">
+      <c r="B17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>-124793431</v>
       </c>
-      <c r="D17" s="19" t="n">
-        <f aca="false">D14+D15-D16</f>
+      <c r="D17" s="12" t="n">
+        <f aca="false">D15-D16</f>
         <v>-114559136</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <f aca="false">E14+E15-E16</f>
+      <c r="E17" s="12" t="n">
+        <f aca="false">E15-E16</f>
         <v>17940864</v>
       </c>
-      <c r="F17" s="19" t="n">
-        <f aca="false">F14+F15-F16</f>
-        <v>105000000</v>
-      </c>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>-124793431</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <f aca="false">D17-D18</f>
-        <v>-114559136</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <f aca="false">E17-E18</f>
-        <v>17940864</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <f aca="false">F17-F18</f>
-        <v>105000000</v>
-      </c>
-      <c r="G19" s="13"/>
+      <c r="F17" s="12" t="n">
+        <f aca="false">F15-F16</f>
+        <v>100000000</v>
+      </c>
+      <c r="G17" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">F9/②前提!$C$9</f>
-        <v>168883018.135581</v>
+        <v>159183690.420246</v>
       </c>
       <c r="D23" s="25" t="n">
-        <f aca="false">C23/②前提!$C$30</f>
-        <v>0.158426846281033</v>
+        <f aca="false">C23/②前提!$C$31</f>
+        <v>0.149328039793852</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7240,7 +7504,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27" s="27"/>
       <c r="D27" s="27"/>
@@ -7250,7 +7514,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26"/>
@@ -7260,7 +7524,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26"/>
@@ -7270,7 +7534,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26"/>
@@ -7280,7 +7544,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -7298,7 +7562,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -7308,7 +7572,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
@@ -7317,14 +7581,14 @@
       <c r="G34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
+      <c r="B35" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7366,17 +7630,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7384,57 +7648,57 @@
         <v>3</v>
       </c>
       <c r="C5" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="F5" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="G5" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="H5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="I5" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="J5" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="K5" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="31" t="s">
+      <c r="L5" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="31" t="s">
+      <c r="M5" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="31" t="s">
+      <c r="N5" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="31" t="s">
+      <c r="O5" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="31" t="s">
+      <c r="P5" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="Q5" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="P5" s="32" t="s">
+      <c r="R5" s="23" t="s">
         <v>57</v>
-      </c>
-      <c r="Q5" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>32789307</v>
@@ -7491,7 +7755,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>18502877</v>
@@ -7548,7 +7812,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C8" s="34" t="n">
         <v>14286430</v>
@@ -7605,12 +7869,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>1450000</v>
@@ -7667,7 +7931,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>5733907</v>
@@ -7724,7 +7988,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2678253</v>
@@ -7781,7 +8045,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>932201</v>
@@ -7838,7 +8102,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>53900</v>
@@ -7895,7 +8159,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>234134</v>
@@ -7952,7 +8216,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2786025</v>
@@ -8009,7 +8273,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4193310</v>
@@ -8066,7 +8330,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>298477</v>
@@ -8123,7 +8387,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>956603</v>
@@ -8180,7 +8444,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>385679</v>
@@ -8237,7 +8501,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>163840</v>
@@ -8294,7 +8558,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0</v>
@@ -8351,7 +8615,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>208971</v>
@@ -8408,7 +8672,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>732759</v>
@@ -8465,7 +8729,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>216380</v>
@@ -8522,7 +8786,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>31310</v>
@@ -8579,7 +8843,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>64335</v>
@@ -8636,7 +8900,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10000</v>
@@ -8693,7 +8957,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>0</v>
@@ -8750,7 +9014,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>10091</v>
@@ -8807,7 +9071,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>3815699</v>
@@ -8864,7 +9128,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>419018</v>
@@ -8921,7 +9185,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="37" t="s">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">SUM(C11:C33)</f>
@@ -8990,7 +9254,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C35" s="16" t="n">
         <f aca="false">C8-C34</f>
@@ -9047,7 +9311,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -9066,7 +9330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G31"/>
+  <dimension ref="B1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9077,17 +9341,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -9097,27 +9361,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="41" t="s">
         <v>91</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I6:K6)</f>
         <v>32428397.3333333</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I8:K8)</f>
@@ -9126,7 +9390,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="C8" s="42" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I34:K34)</f>
@@ -9135,7 +9399,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" s="44" t="n">
         <f aca="false">C7/C6</f>
@@ -9144,7 +9408,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
@@ -9154,211 +9418,224 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" s="45" t="n">
         <v>60000000</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C15" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" s="45" t="n">
         <v>2500000</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C17" s="45" t="n">
         <v>10000000</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" s="45" t="n">
         <v>20000000</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="45" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="45" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="C20" s="45" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="46" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="34" t="n">
-        <f aca="false">SUM(C13:C19)</f>
+      <c r="C21" s="34" t="n">
+        <f aca="false">SUM(C13:C20)</f>
         <v>132500000</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F21" s="30" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <f aca="false">SUM(C13:C18)</f>
-        <v>112500000</v>
-      </c>
-      <c r="F21" s="30" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <f aca="false">SUM(C13:C20)</f>
+        <v>132500000</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="8" t="n">
-        <f aca="false">C19</f>
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="39" t="s">
+      <c r="C23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>117</v>
-      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C26" s="45" t="n">
         <v>15000000</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" s="47" t="n">
         <v>6</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C28" s="47" t="n">
         <v>6</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>123</v>
-      </c>
-      <c r="C29" s="45" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="45" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C30" s="45" t="n">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="45" t="n">
         <v>1066000000</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="48" t="s">
+      <c r="F31" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="49" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="48" t="s">
         <v>128</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -9377,7 +9654,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:P53"/>
+  <dimension ref="B1:P52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9389,12 +9666,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9402,51 +9679,51 @@
         <v>3</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H4" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J4" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O4" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="50"/>
@@ -9526,7 +9803,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="51" t="n">
         <f aca="false">C6-C8</f>
@@ -9587,7 +9864,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="51" t="n">
         <f aca="false">②前提!$C$7</f>
@@ -9648,7 +9925,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C9" s="51" t="n">
         <f aca="false">②前提!$C$13/12</f>
@@ -9709,7 +9986,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C10" s="51" t="n">
         <f aca="false">②前提!$C$14/12</f>
@@ -9770,7 +10047,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="51" t="n">
         <f aca="false">②前提!$C$15/12</f>
@@ -9831,7 +10108,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="51" t="n">
         <f aca="false">②前提!$C$16/12</f>
@@ -9892,7 +10169,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="51" t="n">
         <f aca="false">②前提!$C$17/12</f>
@@ -9953,7 +10230,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$27,②前提!$C$18,0)</f>
@@ -10009,1991 +10286,1926 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <f aca="false">IF(1=②前提!$C$28,②前提!$C$19,0)+IF(1=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <f aca="false">IF(2=②前提!$C$28,②前提!$C$19,0)+IF(2=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <f aca="false">IF(3=②前提!$C$28,②前提!$C$19,0)+IF(3=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <f aca="false">IF(4=②前提!$C$28,②前提!$C$19,0)+IF(4=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <f aca="false">IF(5=②前提!$C$28,②前提!$C$19,0)+IF(5=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <f aca="false">IF(6=②前提!$C$28,②前提!$C$19,0)+IF(6=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>10000000</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <f aca="false">IF(7=②前提!$C$28,②前提!$C$19,0)+IF(7=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <f aca="false">IF(8=②前提!$C$28,②前提!$C$19,0)+IF(8=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <f aca="false">IF(9=②前提!$C$28,②前提!$C$19,0)+IF(9=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <f aca="false">IF(10=②前提!$C$28,②前提!$C$19,0)+IF(10=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <f aca="false">IF(11=②前提!$C$28,②前提!$C$19,0)+IF(11=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <f aca="false">IF(12=②前提!$C$28,②前提!$C$19,0)+IF(12=②前提!$C$29,②前提!$C$20,0)</f>
+        <v>10000000</v>
+      </c>
+      <c r="P15" s="34" t="n">
+        <f aca="false">SUM(D15:O15)</f>
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C16" s="12" t="n">
         <f aca="false">C8+SUM(C9:C13)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <f aca="false">D8+SUM(D9:D14)</f>
+      <c r="D16" s="12" t="n">
+        <f aca="false">D8+SUM(D9:D15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="E15" s="12" t="n">
-        <f aca="false">E8+SUM(E9:E14)</f>
+      <c r="E16" s="12" t="n">
+        <f aca="false">E8+SUM(E9:E15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <f aca="false">F8+SUM(F9:F14)</f>
+      <c r="F16" s="12" t="n">
+        <f aca="false">F8+SUM(F9:F15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <f aca="false">G8+SUM(G9:G14)</f>
+      <c r="G16" s="12" t="n">
+        <f aca="false">G8+SUM(G9:G15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="H15" s="12" t="n">
-        <f aca="false">H8+SUM(H9:H14)</f>
+      <c r="H16" s="12" t="n">
+        <f aca="false">H8+SUM(H9:H15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <f aca="false">I8+SUM(I9:I14)</f>
-        <v>44425160.6666667</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <f aca="false">J8+SUM(J9:J14)</f>
+      <c r="I16" s="12" t="n">
+        <f aca="false">I8+SUM(I9:I15)</f>
+        <v>54425160.6666667</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <f aca="false">J8+SUM(J9:J15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="K15" s="12" t="n">
-        <f aca="false">K8+SUM(K9:K14)</f>
+      <c r="K16" s="12" t="n">
+        <f aca="false">K8+SUM(K9:K15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="L15" s="12" t="n">
-        <f aca="false">L8+SUM(L9:L14)</f>
+      <c r="L16" s="12" t="n">
+        <f aca="false">L8+SUM(L9:L15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="M15" s="12" t="n">
-        <f aca="false">M8+SUM(M9:M14)</f>
+      <c r="M16" s="12" t="n">
+        <f aca="false">M8+SUM(M9:M15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="N15" s="12" t="n">
-        <f aca="false">N8+SUM(N9:N14)</f>
+      <c r="N16" s="12" t="n">
+        <f aca="false">N8+SUM(N9:N15)</f>
         <v>24425160.6666667</v>
       </c>
-      <c r="O15" s="12" t="n">
-        <f aca="false">O8+SUM(O9:O14)</f>
-        <v>24425160.6666667</v>
-      </c>
-      <c r="P15" s="12" t="n">
-        <f aca="false">SUM(D15:O15)</f>
-        <v>313101928</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50"/>
+      <c r="O16" s="12" t="n">
+        <f aca="false">O8+SUM(O9:O15)</f>
+        <v>34425160.6666667</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <f aca="false">SUM(D16:O16)</f>
+        <v>333101928</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="51" t="n">
+      <c r="B18" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)</f>
         <v>2104000</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="D19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="E18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="E19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="F19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="G19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="H19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="I18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="I19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="J19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="K19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="L19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="M19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="N18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="N19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="O18" s="8" t="n">
-        <f aca="false">$C$18</f>
+      <c r="O19" s="8" t="n">
+        <f aca="false">$C$19</f>
         <v>2104000</v>
       </c>
-      <c r="P18" s="34" t="n">
-        <f aca="false">SUM(D18:O18)</f>
+      <c r="P19" s="34" t="n">
+        <f aca="false">SUM(D19:O19)</f>
         <v>25248000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="51" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I12:K12)</f>
         <v>2844602</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="D20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="E19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="E20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="F19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="F20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="G20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="H20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="I19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="I20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="J20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="K20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="L20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="M20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="N20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="O19" s="8" t="n">
-        <f aca="false">$C$19</f>
+      <c r="O20" s="8" t="n">
+        <f aca="false">$C$20</f>
         <v>2844602</v>
       </c>
-      <c r="P19" s="34" t="n">
-        <f aca="false">SUM(D19:O19)</f>
+      <c r="P20" s="34" t="n">
+        <f aca="false">SUM(D20:O20)</f>
         <v>34135224</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="51" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I13:K13)</f>
         <v>198075</v>
       </c>
-      <c r="D20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="D21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="E21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="F20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="F21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="G21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="H21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="I21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="J21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="K20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="K21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="L21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="M21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="N20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="N21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="O20" s="8" t="n">
-        <f aca="false">$C$20</f>
+      <c r="O21" s="8" t="n">
+        <f aca="false">$C$21</f>
         <v>198075</v>
       </c>
-      <c r="P20" s="34" t="n">
-        <f aca="false">SUM(D20:O20)</f>
+      <c r="P21" s="34" t="n">
+        <f aca="false">SUM(D21:O21)</f>
         <v>2376900</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="51" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>943189.333333333</v>
       </c>
-      <c r="D21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="D22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="E21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="E22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="F22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="G22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="H22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="I21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="I22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="J21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="J22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="K22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="L22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="M22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="N22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="O21" s="8" t="n">
-        <f aca="false">$C$21</f>
+      <c r="O22" s="8" t="n">
+        <f aca="false">$C$22</f>
         <v>943189.333333333</v>
       </c>
-      <c r="P21" s="34" t="n">
-        <f aca="false">SUM(D21:O21)</f>
+      <c r="P22" s="34" t="n">
+        <f aca="false">SUM(D22:O22)</f>
         <v>11318272</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" s="51" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I15:K15)</f>
         <v>520742.333333333</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="D23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="E23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="F23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="G23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="H22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="H23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="I22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="I23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="J22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="J23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="K23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="L22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="L23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="M23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="N22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="N23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="O22" s="8" t="n">
-        <f aca="false">$C$22</f>
+      <c r="O23" s="8" t="n">
+        <f aca="false">$C$23</f>
         <v>520742.333333333</v>
       </c>
-      <c r="P22" s="34" t="n">
-        <f aca="false">SUM(D22:O22)</f>
+      <c r="P23" s="34" t="n">
+        <f aca="false">SUM(D23:O23)</f>
         <v>6248908</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="51" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I16:K16)</f>
         <v>986309.666666667</v>
       </c>
-      <c r="D23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="D24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="E23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="E24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="F23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="F24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="G23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="G24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="H23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="H24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="I23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="I24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="J23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="J24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="K23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="K24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="L23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="L24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="M23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="M24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="N23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="N24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="O23" s="8" t="n">
-        <f aca="false">$C$23</f>
+      <c r="O24" s="8" t="n">
+        <f aca="false">$C$24</f>
         <v>986309.666666667</v>
       </c>
-      <c r="P23" s="34" t="n">
-        <f aca="false">SUM(D23:O23)</f>
+      <c r="P24" s="34" t="n">
+        <f aca="false">SUM(D24:O24)</f>
         <v>11835716</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="51" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I17:K17)</f>
         <v>3258950</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="D25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="E24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="E25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="F25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="G25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="H25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="I24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="I25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="J25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="K25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="L24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="L25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="M24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="M25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="N24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="N25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="O24" s="8" t="n">
-        <f aca="false">$C$24</f>
+      <c r="O25" s="8" t="n">
+        <f aca="false">$C$25</f>
         <v>3258950</v>
       </c>
-      <c r="P24" s="34" t="n">
-        <f aca="false">SUM(D24:O24)</f>
+      <c r="P25" s="34" t="n">
+        <f aca="false">SUM(D25:O25)</f>
         <v>39107400</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="51" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I18:K18)</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="D25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="D26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="E25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="E26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="F26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="G26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="H26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="I25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="I26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="J26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="K25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="K26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="L25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="L26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="M26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="N26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="O25" s="8" t="n">
-        <f aca="false">$C$25</f>
+      <c r="O26" s="8" t="n">
+        <f aca="false">$C$26</f>
         <v>3721702.66666667</v>
       </c>
-      <c r="P25" s="34" t="n">
-        <f aca="false">SUM(D25:O25)</f>
+      <c r="P26" s="34" t="n">
+        <f aca="false">SUM(D26:O26)</f>
         <v>44660432</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="51" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I19:K19)</f>
         <v>400027.333333333</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="D27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="E26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="E27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="F27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="G27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="H27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="I26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="I27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="J26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="J27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="K27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="L27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="M26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="M27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="N26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="N27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="O26" s="8" t="n">
-        <f aca="false">$C$26</f>
+      <c r="O27" s="8" t="n">
+        <f aca="false">$C$27</f>
         <v>400027.333333333</v>
       </c>
-      <c r="P26" s="34" t="n">
-        <f aca="false">SUM(D26:O26)</f>
+      <c r="P27" s="34" t="n">
+        <f aca="false">SUM(D27:O27)</f>
         <v>4800328</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="51" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I20:K20)</f>
         <v>687496.333333333</v>
       </c>
-      <c r="D27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="D28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="E27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="E28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="F28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="G28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="H28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="I27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="I28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="J28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="K27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="K28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="L28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="M27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="M28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="N27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="N28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="O27" s="8" t="n">
-        <f aca="false">$C$27</f>
+      <c r="O28" s="8" t="n">
+        <f aca="false">$C$28</f>
         <v>687496.333333333</v>
       </c>
-      <c r="P27" s="34" t="n">
-        <f aca="false">SUM(D27:O27)</f>
+      <c r="P28" s="34" t="n">
+        <f aca="false">SUM(D28:O28)</f>
         <v>8249956</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="51" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I21:K21)</f>
         <v>154132.333333333</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="D29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="E28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="E29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="F28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="F29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="G29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="H28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="H29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="I28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="I29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="J28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="J29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="K28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="K29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="L28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="L29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="M28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="M29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="N29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="O28" s="8" t="n">
-        <f aca="false">$C$28</f>
+      <c r="O29" s="8" t="n">
+        <f aca="false">$C$29</f>
         <v>154132.333333333</v>
       </c>
-      <c r="P28" s="34" t="n">
-        <f aca="false">SUM(D28:O28)</f>
+      <c r="P29" s="34" t="n">
+        <f aca="false">SUM(D29:O29)</f>
         <v>1849588</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="51" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I22:K22)</f>
         <v>122950.333333333</v>
       </c>
-      <c r="D29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="J29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="K29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <f aca="false">$C$29</f>
-        <v>122950.333333333</v>
-      </c>
-      <c r="P29" s="34" t="n">
-        <f aca="false">SUM(D29:O29)</f>
-        <v>1475404</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="51" t="n">
-        <f aca="false">AVERAGE(④FY2026月次実績!I23:K23)</f>
-        <v>0</v>
-      </c>
       <c r="D30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="E30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="F30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="G30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="H30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="I30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="J30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="K30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="L30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="M30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="N30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="O30" s="8" t="n">
         <f aca="false">$C$30</f>
-        <v>0</v>
+        <v>122950.333333333</v>
       </c>
       <c r="P30" s="34" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>0</v>
+        <v>1475404</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C31" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I23:K23)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <f aca="false">$C$31</f>
+        <v>0</v>
+      </c>
+      <c r="P31" s="34" t="n">
+        <f aca="false">SUM(D31:O31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I24:K24)</f>
         <v>246493.666666667</v>
       </c>
-      <c r="D31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="D32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="E31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="E32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="F32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="G32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="H32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="I32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="J31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="J32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="K32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="L31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="L32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="M32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="N31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="N32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="O31" s="8" t="n">
-        <f aca="false">$C$31</f>
+      <c r="O32" s="8" t="n">
+        <f aca="false">$C$32</f>
         <v>246493.666666667</v>
       </c>
-      <c r="P31" s="34" t="n">
-        <f aca="false">SUM(D31:O31)</f>
+      <c r="P32" s="34" t="n">
+        <f aca="false">SUM(D32:O32)</f>
         <v>2957924</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="51" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I25:K25)</f>
         <v>1213002</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="K32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <f aca="false">$C$32</f>
-        <v>1213002</v>
-      </c>
-      <c r="P32" s="34" t="n">
-        <f aca="false">SUM(D32:O32)</f>
-        <v>14556024</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="51" t="n">
-        <f aca="false">AVERAGE(④FY2026月次実績!I26:K26)</f>
-        <v>0</v>
-      </c>
       <c r="D33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="E33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="F33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="G33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="H33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="I33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="J33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="M33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="N33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="O33" s="8" t="n">
         <f aca="false">$C$33</f>
-        <v>0</v>
+        <v>1213002</v>
       </c>
       <c r="P33" s="34" t="n">
         <f aca="false">SUM(D33:O33)</f>
-        <v>0</v>
+        <v>14556024</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C34" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I26:K26)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <f aca="false">$C$34</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="34" t="n">
+        <f aca="false">SUM(D34:O34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I27:K27)</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="D34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="D35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="E34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="E35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="F35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="G34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="G35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="H35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="I34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="I35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="J34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="J35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="K35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="L34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="L35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="M35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="N35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="O34" s="8" t="n">
-        <f aca="false">$C$34</f>
+      <c r="O35" s="8" t="n">
+        <f aca="false">$C$35</f>
         <v>3250243.33333333</v>
       </c>
-      <c r="P34" s="34" t="n">
-        <f aca="false">SUM(D34:O34)</f>
+      <c r="P35" s="34" t="n">
+        <f aca="false">SUM(D35:O35)</f>
         <v>39002920</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C35" s="51" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I28:K28)</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="D35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="D36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="E35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="E36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="F35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="F36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="G35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="G36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="H36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="I36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="J35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="J36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="K35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="K36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="L35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="L36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="M36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="N36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="O35" s="8" t="n">
-        <f aca="false">$C$35</f>
+      <c r="O36" s="8" t="n">
+        <f aca="false">$C$36</f>
         <v>49855.6666666667</v>
       </c>
-      <c r="P35" s="34" t="n">
-        <f aca="false">SUM(D35:O35)</f>
+      <c r="P36" s="34" t="n">
+        <f aca="false">SUM(D36:O36)</f>
         <v>598268</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="51" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I29:K29)</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="D36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="D37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="E36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="E37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="F37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="G36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="G37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="H37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="I36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="I37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="J36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="J37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="K36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="K37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="L37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="M36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="M37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="N37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="O36" s="8" t="n">
-        <f aca="false">$C$36</f>
+      <c r="O37" s="8" t="n">
+        <f aca="false">$C$37</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="P36" s="34" t="n">
-        <f aca="false">SUM(D36:O36)</f>
+      <c r="P37" s="34" t="n">
+        <f aca="false">SUM(D37:O37)</f>
         <v>80000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="51" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C38" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I30:K30)</f>
         <v>394626.666666667</v>
       </c>
-      <c r="D37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="G37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="H37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="K37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <f aca="false">$C$37</f>
-        <v>394626.666666667</v>
-      </c>
-      <c r="P37" s="34" t="n">
-        <f aca="false">SUM(D37:O37)</f>
-        <v>4735520</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="51" t="n">
-        <f aca="false">AVERAGE(④FY2026月次実績!I31:K31)</f>
-        <v>0</v>
-      </c>
       <c r="D38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="E38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="F38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="G38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="H38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="I38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="J38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="O38" s="8" t="n">
         <f aca="false">$C$38</f>
-        <v>0</v>
+        <v>394626.666666667</v>
       </c>
       <c r="P38" s="34" t="n">
         <f aca="false">SUM(D38:O38)</f>
-        <v>0</v>
+        <v>4735520</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C39" s="51" t="n">
+        <f aca="false">AVERAGE(④FY2026月次実績!I31:K31)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <f aca="false">$C$39</f>
+        <v>0</v>
+      </c>
+      <c r="P39" s="34" t="n">
+        <f aca="false">SUM(D39:O39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I32:K32)</f>
         <v>3637873</v>
       </c>
-      <c r="D39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="D40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="E39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="E40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="F40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="G40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="H40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="I39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="I40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="J39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="J40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="K39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="K40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="L40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="M40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="N39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="N40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="O39" s="8" t="n">
-        <f aca="false">$C$39</f>
+      <c r="O40" s="8" t="n">
+        <f aca="false">$C$40</f>
         <v>3637873</v>
       </c>
-      <c r="P39" s="34" t="n">
-        <f aca="false">SUM(D39:O39)</f>
+      <c r="P40" s="34" t="n">
+        <f aca="false">SUM(D40:O40)</f>
         <v>43654476</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="51" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C41" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I33:K33)</f>
         <v>272483.666666667</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="D41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="E41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="F41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="G41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="H41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="I41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="J40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="J41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="K41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="L40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="L41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="M40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="M41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="N41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="O40" s="8" t="n">
-        <f aca="false">$C$40</f>
+      <c r="O41" s="8" t="n">
+        <f aca="false">$C$41</f>
         <v>272483.666666667</v>
       </c>
-      <c r="P40" s="34" t="n">
-        <f aca="false">SUM(D40:O40)</f>
+      <c r="P41" s="34" t="n">
+        <f aca="false">SUM(D41:O41)</f>
         <v>3269804</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="12" t="n">
-        <f aca="false">SUM(C18:C40)</f>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <f aca="false">SUM(C19:C41)</f>
         <v>25013422</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <f aca="false">SUM(D18:D40)</f>
+      <c r="D42" s="12" t="n">
+        <f aca="false">SUM(D19:D41)</f>
         <v>25013422</v>
       </c>
-      <c r="E41" s="12" t="n">
-        <f aca="false">SUM(E18:E40)</f>
+      <c r="E42" s="12" t="n">
+        <f aca="false">SUM(E19:E41)</f>
         <v>25013422</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <f aca="false">SUM(F18:F40)</f>
+      <c r="F42" s="12" t="n">
+        <f aca="false">SUM(F19:F41)</f>
         <v>25013422</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <f aca="false">SUM(G18:G40)</f>
+      <c r="G42" s="12" t="n">
+        <f aca="false">SUM(G19:G41)</f>
         <v>25013422</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <f aca="false">SUM(H18:H40)</f>
+      <c r="H42" s="12" t="n">
+        <f aca="false">SUM(H19:H41)</f>
         <v>25013422</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <f aca="false">SUM(I18:I40)</f>
+      <c r="I42" s="12" t="n">
+        <f aca="false">SUM(I19:I41)</f>
         <v>25013422</v>
       </c>
-      <c r="J41" s="12" t="n">
-        <f aca="false">SUM(J18:J40)</f>
+      <c r="J42" s="12" t="n">
+        <f aca="false">SUM(J19:J41)</f>
         <v>25013422</v>
       </c>
-      <c r="K41" s="12" t="n">
-        <f aca="false">SUM(K18:K40)</f>
+      <c r="K42" s="12" t="n">
+        <f aca="false">SUM(K19:K41)</f>
         <v>25013422</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <f aca="false">SUM(L18:L40)</f>
+      <c r="L42" s="12" t="n">
+        <f aca="false">SUM(L19:L41)</f>
         <v>25013422</v>
       </c>
-      <c r="M41" s="12" t="n">
-        <f aca="false">SUM(M18:M40)</f>
+      <c r="M42" s="12" t="n">
+        <f aca="false">SUM(M19:M41)</f>
         <v>25013422</v>
       </c>
-      <c r="N41" s="12" t="n">
-        <f aca="false">SUM(N18:N40)</f>
+      <c r="N42" s="12" t="n">
+        <f aca="false">SUM(N19:N41)</f>
         <v>25013422</v>
       </c>
-      <c r="O41" s="12" t="n">
-        <f aca="false">SUM(O18:O40)</f>
+      <c r="O42" s="12" t="n">
+        <f aca="false">SUM(O19:O41)</f>
         <v>25013422</v>
       </c>
-      <c r="P41" s="12" t="n">
-        <f aca="false">SUM(D41:O41)</f>
+      <c r="P42" s="12" t="n">
+        <f aca="false">SUM(D42:O42)</f>
         <v>300161064</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="51" t="n">
-        <f aca="false">②前提!$C$25/12</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="O42" s="8" t="n">
-        <f aca="false">$C$42</f>
-        <v>0</v>
-      </c>
-      <c r="P42" s="34" t="n">
-        <f aca="false">SUM(D42:O42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C43" s="12" t="n">
-        <f aca="false">C41+C42</f>
-        <v>25013422</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <f aca="false">D41+D42</f>
-        <v>25013422</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <f aca="false">E41+E42</f>
-        <v>25013422</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <f aca="false">F41+F42</f>
-        <v>25013422</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <f aca="false">G41+G42</f>
-        <v>25013422</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <f aca="false">H41+H42</f>
-        <v>25013422</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <f aca="false">I41+I42</f>
-        <v>25013422</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <f aca="false">J41+J42</f>
-        <v>25013422</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <f aca="false">K41+K42</f>
-        <v>25013422</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <f aca="false">L41+L42</f>
-        <v>25013422</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <f aca="false">M41+M42</f>
-        <v>25013422</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <f aca="false">N41+N42</f>
-        <v>25013422</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <f aca="false">O41+O42</f>
-        <v>25013422</v>
-      </c>
-      <c r="P43" s="12" t="n">
-        <f aca="false">SUM(D43:O43)</f>
-        <v>300161064</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
+      <c r="C45" s="16" t="n">
+        <f aca="false">C16-C42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <f aca="false">D16-D42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <f aca="false">E16-E42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <f aca="false">F16-F42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <f aca="false">G16-G42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="H45" s="16" t="n">
+        <f aca="false">H16-H42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="I45" s="16" t="n">
+        <f aca="false">I16-I42</f>
+        <v>29411738.6666667</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <f aca="false">J16-J42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="K45" s="16" t="n">
+        <f aca="false">K16-K42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="L45" s="16" t="n">
+        <f aca="false">L16-L42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="M45" s="16" t="n">
+        <f aca="false">M16-M42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="N45" s="16" t="n">
+        <f aca="false">N16-N42</f>
+        <v>-588261.333333332</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <f aca="false">O16-O42</f>
+        <v>9411738.66666666</v>
+      </c>
+      <c r="P45" s="16" t="n">
+        <f aca="false">SUM(D45:O45)</f>
+        <v>32940864</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <f aca="false">C15-C43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <f aca="false">D15-D43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <f aca="false">E15-E43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <f aca="false">F15-F43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="G46" s="16" t="n">
-        <f aca="false">G15-G43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <f aca="false">H15-H43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="I46" s="16" t="n">
-        <f aca="false">I15-I43</f>
-        <v>19411738.6666667</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <f aca="false">J15-J43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="K46" s="16" t="n">
-        <f aca="false">K15-K43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="L46" s="16" t="n">
-        <f aca="false">L15-L43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <f aca="false">M15-M43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="N46" s="16" t="n">
-        <f aca="false">N15-N43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="O46" s="16" t="n">
-        <f aca="false">O15-O43</f>
-        <v>-588261.333333332</v>
-      </c>
-      <c r="P46" s="16" t="n">
+      <c r="B46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P46" s="34" t="n">
         <f aca="false">SUM(D46:O46)</f>
-        <v>12940864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>23</v>
+        <v>158</v>
+      </c>
+      <c r="C47" s="51" t="n">
+        <f aca="false">②前提!$C$26/12</f>
+        <v>1250000</v>
       </c>
       <c r="D47" s="8" t="n">
-        <f aca="false">IF(1=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="E47" s="8" t="n">
-        <f aca="false">IF(2=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="F47" s="8" t="n">
-        <f aca="false">IF(3=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="G47" s="8" t="n">
-        <f aca="false">IF(4=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="H47" s="8" t="n">
-        <f aca="false">IF(5=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="I47" s="8" t="n">
-        <f aca="false">IF(6=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>20000000</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="J47" s="8" t="n">
-        <f aca="false">IF(7=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="K47" s="8" t="n">
-        <f aca="false">IF(8=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="L47" s="8" t="n">
-        <f aca="false">IF(9=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="M47" s="8" t="n">
-        <f aca="false">IF(10=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="N47" s="8" t="n">
-        <f aca="false">IF(11=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="O47" s="8" t="n">
-        <f aca="false">IF(12=②前提!$C$28,②前提!$C$19,0)</f>
-        <v>0</v>
+        <f aca="false">$C$47</f>
+        <v>1250000</v>
       </c>
       <c r="P47" s="34" t="n">
         <f aca="false">SUM(D47:O47)</f>
-        <v>20000000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C48" s="51" t="n">
-        <f aca="false">②前提!$C$26/12</f>
-        <v>1250000</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="F48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="G48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="H48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="I48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="J48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="K48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="L48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="N48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="O48" s="8" t="n">
-        <f aca="false">$C$48</f>
-        <v>1250000</v>
-      </c>
-      <c r="P48" s="34" t="n">
+      <c r="B48" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="19" t="n">
+        <f aca="false">C45+C46-C47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="D48" s="19" t="n">
+        <f aca="false">D45+D46-D47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <f aca="false">E45+E46-E47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <f aca="false">F45+F46-F47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="G48" s="19" t="n">
+        <f aca="false">G45+G46-G47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <f aca="false">H45+H46-H47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="I48" s="19" t="n">
+        <f aca="false">I45+I46-I47</f>
+        <v>28161738.6666667</v>
+      </c>
+      <c r="J48" s="19" t="n">
+        <f aca="false">J45+J46-J47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="K48" s="19" t="n">
+        <f aca="false">K45+K46-K47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="L48" s="19" t="n">
+        <f aca="false">L45+L46-L47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <f aca="false">M45+M46-M47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="N48" s="19" t="n">
+        <f aca="false">N45+N46-N47</f>
+        <v>-1838261.33333333</v>
+      </c>
+      <c r="O48" s="19" t="n">
+        <f aca="false">O45+O46-O47</f>
+        <v>8161738.66666666</v>
+      </c>
+      <c r="P48" s="19" t="n">
         <f aca="false">SUM(D48:O48)</f>
-        <v>15000000</v>
+        <v>17940864</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="19" t="n">
-        <f aca="false">C46+C47-C48</f>
+      <c r="B49" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="52" t="n">
+        <f aca="false">D48</f>
         <v>-1838261.33333333</v>
       </c>
-      <c r="D49" s="19" t="n">
-        <f aca="false">D46+D47-D48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="E49" s="19" t="n">
-        <f aca="false">E46+E47-E48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="F49" s="19" t="n">
-        <f aca="false">F46+F47-F48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="G49" s="19" t="n">
-        <f aca="false">G46+G47-G48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="H49" s="19" t="n">
-        <f aca="false">H46+H47-H48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="I49" s="19" t="n">
-        <f aca="false">I46+I47-I48</f>
-        <v>38161738.6666667</v>
-      </c>
-      <c r="J49" s="19" t="n">
-        <f aca="false">J46+J47-J48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="K49" s="19" t="n">
-        <f aca="false">K46+K47-K48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="L49" s="19" t="n">
-        <f aca="false">L46+L47-L48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="M49" s="19" t="n">
-        <f aca="false">M46+M47-M48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="N49" s="19" t="n">
-        <f aca="false">N46+N47-N48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="O49" s="19" t="n">
-        <f aca="false">O46+O47-O48</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="P49" s="19" t="n">
-        <f aca="false">SUM(D49:O49)</f>
+      <c r="E49" s="52" t="n">
+        <f aca="false">D49+E48</f>
+        <v>-3676522.66666666</v>
+      </c>
+      <c r="F49" s="52" t="n">
+        <f aca="false">E49+F48</f>
+        <v>-5514784</v>
+      </c>
+      <c r="G49" s="52" t="n">
+        <f aca="false">F49+G48</f>
+        <v>-7353045.33333333</v>
+      </c>
+      <c r="H49" s="52" t="n">
+        <f aca="false">G49+H48</f>
+        <v>-9191306.66666666</v>
+      </c>
+      <c r="I49" s="52" t="n">
+        <f aca="false">H49+I48</f>
+        <v>18970432</v>
+      </c>
+      <c r="J49" s="52" t="n">
+        <f aca="false">I49+J48</f>
+        <v>17132170.6666667</v>
+      </c>
+      <c r="K49" s="52" t="n">
+        <f aca="false">J49+K48</f>
+        <v>15293909.3333333</v>
+      </c>
+      <c r="L49" s="52" t="n">
+        <f aca="false">K49+L48</f>
+        <v>13455648</v>
+      </c>
+      <c r="M49" s="52" t="n">
+        <f aca="false">L49+M48</f>
+        <v>11617386.6666667</v>
+      </c>
+      <c r="N49" s="52" t="n">
+        <f aca="false">M49+N48</f>
+        <v>9779125.33333334</v>
+      </c>
+      <c r="O49" s="52" t="n">
+        <f aca="false">N49+O48</f>
         <v>17940864</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="D50" s="52" t="n">
-        <f aca="false">D49</f>
-        <v>-1838261.33333333</v>
-      </c>
-      <c r="E50" s="52" t="n">
-        <f aca="false">D50+E49</f>
-        <v>-3676522.66666666</v>
-      </c>
-      <c r="F50" s="52" t="n">
-        <f aca="false">E50+F49</f>
-        <v>-5514784</v>
-      </c>
-      <c r="G50" s="52" t="n">
-        <f aca="false">F50+G49</f>
-        <v>-7353045.33333333</v>
-      </c>
-      <c r="H50" s="52" t="n">
-        <f aca="false">G50+H49</f>
-        <v>-9191306.66666666</v>
-      </c>
-      <c r="I50" s="52" t="n">
-        <f aca="false">H50+I49</f>
-        <v>28970432</v>
-      </c>
-      <c r="J50" s="52" t="n">
-        <f aca="false">I50+J49</f>
-        <v>27132170.6666667</v>
-      </c>
-      <c r="K50" s="52" t="n">
-        <f aca="false">J50+K49</f>
-        <v>25293909.3333333</v>
-      </c>
-      <c r="L50" s="52" t="n">
-        <f aca="false">K50+L49</f>
-        <v>23455648</v>
-      </c>
-      <c r="M50" s="52" t="n">
-        <f aca="false">L50+M49</f>
-        <v>21617386.6666667</v>
-      </c>
-      <c r="N50" s="52" t="n">
-        <f aca="false">M50+N49</f>
-        <v>19779125.3333333</v>
-      </c>
-      <c r="O50" s="52" t="n">
-        <f aca="false">N50+O49</f>
-        <v>17940864</v>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -12023,31 +12235,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="38" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C5" s="54" t="n">
         <v>-114793431</v>
@@ -12057,12 +12269,12 @@
         <v>-114793431</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">②前提!$C$7*12-229139405</f>
@@ -12073,12 +12285,12 @@
         <v>-143330908</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">343932836-②前提!$C$8*12</f>
@@ -12089,56 +12301,40 @@
         <v>-99559136</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">②前提!$C$21</f>
-        <v>112500000</v>
+        <f aca="false">②前提!$C$22</f>
+        <v>132500000</v>
       </c>
       <c r="D8" s="34" t="n">
         <f aca="false">D7+C8</f>
-        <v>12940864</v>
+        <v>32940864</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <f aca="false">-②前提!$C$25</f>
-        <v>-0</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <f aca="false">D8+C9</f>
-        <v>12940864</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="16" t="n">
-        <f aca="false">D9</f>
-        <v>12940864</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="B9" s="55" t="s">
         <v>175</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">D8</f>
+        <v>32940864</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="21" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12147,11 +12343,11 @@
       </c>
       <c r="C13" s="24" t="n">
         <f aca="false">①サマリー!C23</f>
-        <v>168883018.135581</v>
+        <v>159183690.420246</v>
       </c>
       <c r="E13" s="56" t="n">
         <f aca="false">①サマリー!D23</f>
-        <v>0.158426846281033</v>
+        <v>0.149328039793852</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>178</v>
@@ -12297,43 +12493,43 @@
         <v>194</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H11" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K11" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N11" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O11" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P11" s="41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12656,7 +12852,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:Q59"/>
+  <dimension ref="B1:Q58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -12769,43 +12965,43 @@
         <v>194</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H12" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I12" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L12" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N12" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O12" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P12" s="41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13047,359 +13243,362 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="65" t="s">
         <v>229</v>
       </c>
-      <c r="D18" s="12" t="n">
-        <f aca="false">SUM(D14:D17)</f>
+      <c r="D18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!D15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!E15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!F15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!G15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!H15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!I15*(1+$C$6)</f>
+        <v>11000000</v>
+      </c>
+      <c r="J18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!J15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!K15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!L15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!M15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!N15*(1+$C$6)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="51" t="n">
+        <f aca="false">③FY2027月次推移!O15*(1+$C$6)</f>
+        <v>11000000</v>
+      </c>
+      <c r="P18" s="34" t="n">
+        <f aca="false">SUM(D18:O18)</f>
+        <v>22000000</v>
+      </c>
+      <c r="Q18" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <f aca="false">SUM(D14:D18)</f>
         <v>264150403.733333</v>
       </c>
-      <c r="E18" s="12" t="n">
-        <f aca="false">SUM(E14:E17)</f>
+      <c r="E19" s="12" t="n">
+        <f aca="false">SUM(E14:E18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <f aca="false">SUM(F14:F17)</f>
+      <c r="F19" s="12" t="n">
+        <f aca="false">SUM(F14:F18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <f aca="false">SUM(G14:G17)</f>
+      <c r="G19" s="12" t="n">
+        <f aca="false">SUM(G14:G18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <f aca="false">SUM(H14:H17)</f>
+      <c r="H19" s="12" t="n">
+        <f aca="false">SUM(H14:H18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <f aca="false">SUM(I14:I17)</f>
-        <v>66150403.7333333</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <f aca="false">SUM(J14:J17)</f>
+      <c r="I19" s="12" t="n">
+        <f aca="false">SUM(I14:I18)</f>
+        <v>77150403.7333333</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <f aca="false">SUM(J14:J18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="K18" s="12" t="n">
-        <f aca="false">SUM(K14:K17)</f>
+      <c r="K19" s="12" t="n">
+        <f aca="false">SUM(K14:K18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <f aca="false">SUM(L14:L17)</f>
+      <c r="L19" s="12" t="n">
+        <f aca="false">SUM(L14:L18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <f aca="false">SUM(M14:M17)</f>
+      <c r="M19" s="12" t="n">
+        <f aca="false">SUM(M14:M18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="N18" s="12" t="n">
-        <f aca="false">SUM(N14:N17)</f>
+      <c r="N19" s="12" t="n">
+        <f aca="false">SUM(N14:N18)</f>
         <v>44150403.7333333</v>
       </c>
-      <c r="O18" s="12" t="n">
-        <f aca="false">SUM(O14:O17)</f>
-        <v>44150403.7333333</v>
-      </c>
-      <c r="P18" s="12" t="n">
-        <f aca="false">SUM(D18:O18)</f>
-        <v>771804844.8</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
+      <c r="O19" s="12" t="n">
+        <f aca="false">SUM(O14:O18)</f>
+        <v>55150403.7333333</v>
+      </c>
+      <c r="P19" s="12" t="n">
+        <f aca="false">SUM(D19:O19)</f>
+        <v>793804844.8</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="65" t="s">
-        <v>231</v>
-      </c>
-      <c r="D21" s="51" t="n">
+      <c r="B21" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="D22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="E21" s="51" t="n">
+      <c r="E22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!E16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="G21" s="51" t="n">
+      <c r="G22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!F16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="H21" s="51" t="n">
+      <c r="H22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!G16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="I21" s="51" t="n">
+      <c r="I22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!H16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="J21" s="51" t="n">
+      <c r="J22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!I16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="K21" s="51" t="n">
+      <c r="K22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!J16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="L21" s="51" t="n">
+      <c r="L22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!K16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="M21" s="51" t="n">
+      <c r="M22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!L16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="N21" s="51" t="n">
+      <c r="N22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!M16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="O21" s="51" t="n">
+      <c r="O22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!N16*(1+$C$6)</f>
         <v>17282727</v>
       </c>
-      <c r="P21" s="34" t="n">
-        <f aca="false">SUM(D21:O21)</f>
+      <c r="P22" s="34" t="n">
+        <f aca="false">SUM(D22:O22)</f>
         <v>207392724</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="D22" s="51" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="D23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="E22" s="51" t="n">
+      <c r="E23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="F22" s="51" t="n">
+      <c r="F23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="G22" s="51" t="n">
+      <c r="G23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="H22" s="51" t="n">
+      <c r="H23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="I22" s="51" t="n">
+      <c r="I23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="J22" s="51" t="n">
+      <c r="J23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="K22" s="51" t="n">
+      <c r="K23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="L22" s="51" t="n">
+      <c r="L23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="M22" s="51" t="n">
+      <c r="M23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="N22" s="51" t="n">
+      <c r="N23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="O22" s="51" t="n">
+      <c r="O23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="P22" s="34" t="n">
-        <f aca="false">SUM(D22:O22)</f>
-        <v>73078396</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="65" t="s">
-        <v>233</v>
-      </c>
-      <c r="D23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!D41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="E23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!E41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="F23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!F41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="G23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!G41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="H23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!H41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="I23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!I41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="J23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!J41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="K23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!K41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="L23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!L41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="M23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!M41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="N23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!N41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
-      <c r="O23" s="51" t="n">
-        <f aca="false">((③FY2027月次推移!O41-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
-        <v>16762493.2333333</v>
-      </c>
       <c r="P23" s="34" t="n">
         <f aca="false">SUM(D23:O23)</f>
-        <v>201149918.8</v>
+        <v>73078396</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="65" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!D42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!D42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="E24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!E42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!E42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="F24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!F42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!F42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="G24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!G42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!G42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="H24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!H42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!H42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="I24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!I42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!I42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="J24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!J42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!J42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="K24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!K42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!K42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="L24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!L42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!L42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="M24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!M42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!M42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="N24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!N42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!N42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="O24" s="51" t="n">
-        <f aca="false">③FY2027月次推移!O42*(1+$C$6)</f>
-        <v>0</v>
+        <f aca="false">((③FY2027月次推移!O42-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
+        <v>16762493.2333333</v>
       </c>
       <c r="P24" s="34" t="n">
         <f aca="false">SUM(D24:O24)</f>
-        <v>0</v>
+        <v>201149918.8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!D48</f>
+        <f aca="false">③FY2027月次推移!D47</f>
         <v>1250000</v>
       </c>
       <c r="E25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!E48</f>
+        <f aca="false">③FY2027月次推移!E47</f>
         <v>1250000</v>
       </c>
       <c r="F25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!F48</f>
+        <f aca="false">③FY2027月次推移!F47</f>
         <v>1250000</v>
       </c>
       <c r="G25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!G48</f>
+        <f aca="false">③FY2027月次推移!G47</f>
         <v>1250000</v>
       </c>
       <c r="H25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!H48</f>
+        <f aca="false">③FY2027月次推移!H47</f>
         <v>1250000</v>
       </c>
       <c r="I25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!I48</f>
+        <f aca="false">③FY2027月次推移!I47</f>
         <v>1250000</v>
       </c>
       <c r="J25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!J48</f>
+        <f aca="false">③FY2027月次推移!J47</f>
         <v>1250000</v>
       </c>
       <c r="K25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!K48</f>
+        <f aca="false">③FY2027月次推移!K47</f>
         <v>1250000</v>
       </c>
       <c r="L25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!L48</f>
+        <f aca="false">③FY2027月次推移!L47</f>
         <v>1250000</v>
       </c>
       <c r="M25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!M48</f>
+        <f aca="false">③FY2027月次推移!M47</f>
         <v>1250000</v>
       </c>
       <c r="N25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!N48</f>
+        <f aca="false">③FY2027月次推移!N47</f>
         <v>1250000</v>
       </c>
       <c r="O25" s="51" t="n">
-        <f aca="false">③FY2027月次推移!O48</f>
+        <f aca="false">③FY2027月次推移!O47</f>
         <v>1250000</v>
       </c>
       <c r="P25" s="34" t="n">
@@ -13409,7 +13608,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D26" s="45" t="n">
         <v>0</v>
@@ -13452,12 +13651,12 @@
         <v>35000000</v>
       </c>
       <c r="Q26" s="43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D27" s="45" t="n">
         <v>0</v>
@@ -13502,54 +13701,54 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D28" s="12" t="n">
-        <f aca="false">SUM(D21:D27)</f>
+        <f aca="false">SUM(D22:D27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="E28" s="12" t="n">
-        <f aca="false">SUM(E21:E27)</f>
+        <f aca="false">SUM(E22:E27)</f>
         <v>71848191.5666667</v>
       </c>
       <c r="F28" s="12" t="n">
-        <f aca="false">SUM(F21:F27)</f>
+        <f aca="false">SUM(F22:F27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="G28" s="12" t="n">
-        <f aca="false">SUM(G21:G27)</f>
+        <f aca="false">SUM(G22:G27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="H28" s="12" t="n">
-        <f aca="false">SUM(H21:H27)</f>
+        <f aca="false">SUM(H22:H27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="I28" s="12" t="n">
-        <f aca="false">SUM(I21:I27)</f>
+        <f aca="false">SUM(I22:I27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="J28" s="12" t="n">
-        <f aca="false">SUM(J21:J27)</f>
+        <f aca="false">SUM(J22:J27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="K28" s="12" t="n">
-        <f aca="false">SUM(K21:K27)</f>
+        <f aca="false">SUM(K22:K27)</f>
         <v>46385086.5666667</v>
       </c>
       <c r="L28" s="12" t="n">
-        <f aca="false">SUM(L21:L27)</f>
+        <f aca="false">SUM(L22:L27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="M28" s="12" t="n">
-        <f aca="false">SUM(M21:M27)</f>
+        <f aca="false">SUM(M22:M27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="N28" s="12" t="n">
-        <f aca="false">SUM(N21:N27)</f>
+        <f aca="false">SUM(N22:N27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="O28" s="12" t="n">
-        <f aca="false">SUM(O21:O27)</f>
+        <f aca="false">SUM(O22:O27)</f>
         <v>41385086.5666667</v>
       </c>
       <c r="P28" s="12" t="n">
@@ -13559,64 +13758,64 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D29" s="16" t="n">
-        <f aca="false">D18-D28</f>
+        <f aca="false">D19-D28</f>
         <v>222765317.166667</v>
       </c>
       <c r="E29" s="16" t="n">
-        <f aca="false">E18-E28</f>
+        <f aca="false">E19-E28</f>
         <v>-27697787.8333333</v>
       </c>
       <c r="F29" s="16" t="n">
-        <f aca="false">F18-F28</f>
+        <f aca="false">F19-F28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="G29" s="16" t="n">
-        <f aca="false">G18-G28</f>
+        <f aca="false">G19-G28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="H29" s="16" t="n">
-        <f aca="false">H18-H28</f>
+        <f aca="false">H19-H28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="I29" s="16" t="n">
-        <f aca="false">I18-I28</f>
-        <v>24765317.1666667</v>
+        <f aca="false">I19-I28</f>
+        <v>35765317.1666667</v>
       </c>
       <c r="J29" s="16" t="n">
-        <f aca="false">J18-J28</f>
+        <f aca="false">J19-J28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="K29" s="16" t="n">
-        <f aca="false">K18-K28</f>
+        <f aca="false">K19-K28</f>
         <v>-2234682.83333334</v>
       </c>
       <c r="L29" s="16" t="n">
-        <f aca="false">L18-L28</f>
+        <f aca="false">L19-L28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="M29" s="16" t="n">
-        <f aca="false">M18-M28</f>
+        <f aca="false">M19-M28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="N29" s="16" t="n">
-        <f aca="false">N18-N28</f>
+        <f aca="false">N19-N28</f>
         <v>2765317.16666666</v>
       </c>
       <c r="O29" s="16" t="n">
-        <f aca="false">O18-O28</f>
-        <v>2765317.16666666</v>
+        <f aca="false">O19-O28</f>
+        <v>13765317.1666667</v>
       </c>
       <c r="P29" s="16" t="n">
         <f aca="false">SUM(D29:O29)</f>
-        <v>239720701</v>
+        <v>261720701</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C31" s="50"/>
       <c r="D31" s="50"/>
@@ -13635,7 +13834,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="65" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D32" s="51" t="n">
         <f aca="false">-$C$9</f>
@@ -13692,7 +13891,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D33" s="51" t="n">
         <f aca="false">$C$10</f>
@@ -13749,7 +13948,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D34" s="45" t="n">
         <v>0</v>
@@ -13793,555 +13992,498 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="65" t="s">
-        <v>245</v>
-      </c>
-      <c r="D35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!D47</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!E47</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!F47</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!G47</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!H47</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!I47</f>
-        <v>20000000</v>
-      </c>
-      <c r="J35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!J47</f>
-        <v>0</v>
-      </c>
-      <c r="K35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!K47</f>
-        <v>0</v>
-      </c>
-      <c r="L35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!L47</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!M47</f>
-        <v>0</v>
-      </c>
-      <c r="N35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!N47</f>
-        <v>0</v>
-      </c>
-      <c r="O35" s="51" t="n">
-        <f aca="false">③FY2027月次推移!O47</f>
+      <c r="B35" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="45" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="E35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="45" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="34" t="n">
         <f aca="false">SUM(D35:O35)</f>
-        <v>20000000</v>
+        <v>-200000000</v>
+      </c>
+      <c r="Q35" s="30" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D36" s="45" t="n">
-        <v>-200000000</v>
-      </c>
-      <c r="E36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="34" t="n">
+      <c r="B36" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <f aca="false">SUM(D32:D35)</f>
+        <v>-202662179</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <f aca="false">SUM(E32:E35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <f aca="false">SUM(F32:F35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <f aca="false">SUM(G32:G35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <f aca="false">SUM(H32:H35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <f aca="false">SUM(I32:I35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <f aca="false">SUM(J32:J35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <f aca="false">SUM(K32:K35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <f aca="false">SUM(L32:L35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <f aca="false">SUM(M32:M35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="N36" s="12" t="n">
+        <f aca="false">SUM(N32:N35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="O36" s="12" t="n">
+        <f aca="false">SUM(O32:O35)</f>
+        <v>-2662179</v>
+      </c>
+      <c r="P36" s="12" t="n">
         <f aca="false">SUM(D36:O36)</f>
-        <v>-200000000</v>
-      </c>
-      <c r="Q36" s="30" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <f aca="false">SUM(D32:D36)</f>
-        <v>-202662179</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <f aca="false">SUM(E32:E36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <f aca="false">SUM(F32:F36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <f aca="false">SUM(G32:G36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <f aca="false">SUM(H32:H36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <f aca="false">SUM(I32:I36)</f>
-        <v>17337821</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <f aca="false">SUM(J32:J36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <f aca="false">SUM(K32:K36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <f aca="false">SUM(L32:L36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <f aca="false">SUM(M32:M36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <f aca="false">SUM(N32:N36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="O37" s="12" t="n">
-        <f aca="false">SUM(O32:O36)</f>
-        <v>-2662179</v>
-      </c>
-      <c r="P37" s="12" t="n">
-        <f aca="false">SUM(D37:O37)</f>
-        <v>-211946148</v>
+        <v>-231946148</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <f aca="false">D29+D36</f>
+        <v>20103138.1666667</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <f aca="false">E29+E36</f>
+        <v>-30359966.8333333</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <f aca="false">F29+F36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <f aca="false">G29+G36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <f aca="false">H29+H36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <f aca="false">I29+I36</f>
+        <v>33103138.1666667</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <f aca="false">J29+J36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <f aca="false">K29+K36</f>
+        <v>-4896861.83333334</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <f aca="false">L29+L36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <f aca="false">M29+M36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="N38" s="12" t="n">
+        <f aca="false">N29+N36</f>
+        <v>103138.166666664</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <f aca="false">O29+O36</f>
+        <v>11103138.1666667</v>
+      </c>
+      <c r="P38" s="12" t="n">
+        <f aca="false">SUM(D38:O38)</f>
+        <v>29774553</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <f aca="false">D29+D37</f>
-        <v>20103138.1666667</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <f aca="false">E29+E37</f>
-        <v>-30359966.8333333</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <f aca="false">F29+F37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <f aca="false">G29+G37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <f aca="false">H29+H37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <f aca="false">I29+I37</f>
-        <v>42103138.1666667</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <f aca="false">J29+J37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <f aca="false">K29+K37</f>
-        <v>-4896861.83333334</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <f aca="false">L29+L37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <f aca="false">M29+M37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <f aca="false">N29+N37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <f aca="false">O29+O37</f>
-        <v>103138.166666664</v>
-      </c>
-      <c r="P39" s="12" t="n">
-        <f aca="false">SUM(D39:O39)</f>
-        <v>27774553</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D40" s="8" t="n">
+      <c r="D39" s="8" t="n">
         <f aca="false">$C$5</f>
         <v>24390278</v>
       </c>
-      <c r="E40" s="8" t="n">
-        <f aca="false">D41</f>
+      <c r="E39" s="8" t="n">
+        <f aca="false">D40</f>
         <v>44493416.1666667</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <f aca="false">E41</f>
+      <c r="F39" s="8" t="n">
+        <f aca="false">E40</f>
         <v>14133449.3333334</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <f aca="false">F41</f>
+      <c r="G39" s="8" t="n">
+        <f aca="false">F40</f>
         <v>14236587.5</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <f aca="false">G41</f>
+      <c r="H39" s="8" t="n">
+        <f aca="false">G40</f>
         <v>14339725.6666667</v>
       </c>
-      <c r="I40" s="8" t="n">
-        <f aca="false">H41</f>
+      <c r="I39" s="8" t="n">
+        <f aca="false">H40</f>
         <v>14442863.8333334</v>
       </c>
-      <c r="J40" s="8" t="n">
-        <f aca="false">I41</f>
-        <v>56546002</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <f aca="false">J41</f>
-        <v>56649140.1666667</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <f aca="false">K41</f>
-        <v>51752278.3333333</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <f aca="false">L41</f>
-        <v>51855416.5</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <f aca="false">M41</f>
-        <v>51958554.6666667</v>
-      </c>
-      <c r="O40" s="8" t="n">
-        <f aca="false">N41</f>
-        <v>52061692.8333333</v>
+      <c r="J39" s="8" t="n">
+        <f aca="false">I40</f>
+        <v>47546002</v>
+      </c>
+      <c r="K39" s="8" t="n">
+        <f aca="false">J40</f>
+        <v>47649140.1666667</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <f aca="false">K40</f>
+        <v>42752278.3333333</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <f aca="false">L40</f>
+        <v>42855416.5</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <f aca="false">M40</f>
+        <v>42958554.6666667</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <f aca="false">N40</f>
+        <v>43061692.8333333</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <f aca="false">D39+D38</f>
+        <v>44493416.1666667</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <f aca="false">E39+E38</f>
+        <v>14133449.3333334</v>
+      </c>
+      <c r="F40" s="19" t="n">
+        <f aca="false">F39+F38</f>
+        <v>14236587.5</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <f aca="false">G39+G38</f>
+        <v>14339725.6666667</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <f aca="false">H39+H38</f>
+        <v>14442863.8333334</v>
+      </c>
+      <c r="I40" s="19" t="n">
+        <f aca="false">I39+I38</f>
+        <v>47546002</v>
+      </c>
+      <c r="J40" s="19" t="n">
+        <f aca="false">J39+J38</f>
+        <v>47649140.1666667</v>
+      </c>
+      <c r="K40" s="19" t="n">
+        <f aca="false">K39+K38</f>
+        <v>42752278.3333333</v>
+      </c>
+      <c r="L40" s="19" t="n">
+        <f aca="false">L39+L38</f>
+        <v>42855416.5</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <f aca="false">M39+M38</f>
+        <v>42958554.6666667</v>
+      </c>
+      <c r="N40" s="19" t="n">
+        <f aca="false">N39+N38</f>
+        <v>43061692.8333333</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <f aca="false">O39+O38</f>
+        <v>54164831</v>
+      </c>
+      <c r="P40" s="52" t="n">
+        <f aca="false">O40</f>
+        <v>54164831</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <f aca="false">D40+D39</f>
-        <v>44493416.1666667</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <f aca="false">E40+E39</f>
-        <v>14133449.3333334</v>
-      </c>
-      <c r="F41" s="19" t="n">
-        <f aca="false">F40+F39</f>
-        <v>14236587.5</v>
-      </c>
-      <c r="G41" s="19" t="n">
-        <f aca="false">G40+G39</f>
-        <v>14339725.6666667</v>
-      </c>
-      <c r="H41" s="19" t="n">
-        <f aca="false">H40+H39</f>
-        <v>14442863.8333334</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <f aca="false">I40+I39</f>
-        <v>56546002</v>
-      </c>
-      <c r="J41" s="19" t="n">
-        <f aca="false">J40+J39</f>
-        <v>56649140.1666667</v>
-      </c>
-      <c r="K41" s="19" t="n">
-        <f aca="false">K40+K39</f>
-        <v>51752278.3333333</v>
-      </c>
-      <c r="L41" s="19" t="n">
-        <f aca="false">L40+L39</f>
-        <v>51855416.5</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <f aca="false">M40+M39</f>
-        <v>51958554.6666667</v>
-      </c>
-      <c r="N41" s="19" t="n">
-        <f aca="false">N40+N39</f>
-        <v>52061692.8333333</v>
-      </c>
-      <c r="O41" s="19" t="n">
-        <f aca="false">O40+O39</f>
-        <v>52164831</v>
-      </c>
-      <c r="P41" s="52" t="n">
-        <f aca="false">O41</f>
-        <v>52164831</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="66" t="s">
+      <c r="B41" s="66" t="s">
         <v>252</v>
       </c>
-      <c r="D42" s="67" t="n">
-        <f aca="false">IF(D41&lt;0,D41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="67" t="n">
-        <f aca="false">IF(E41&lt;0,E41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="67" t="n">
-        <f aca="false">IF(F41&lt;0,F41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="67" t="n">
-        <f aca="false">IF(G41&lt;0,G41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="67" t="n">
-        <f aca="false">IF(H41&lt;0,H41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="67" t="n">
-        <f aca="false">IF(I41&lt;0,I41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="67" t="n">
-        <f aca="false">IF(J41&lt;0,J41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="67" t="n">
-        <f aca="false">IF(K41&lt;0,K41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="67" t="n">
-        <f aca="false">IF(L41&lt;0,L41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="67" t="n">
-        <f aca="false">IF(M41&lt;0,M41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N42" s="67" t="n">
-        <f aca="false">IF(N41&lt;0,N41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O42" s="67" t="n">
-        <f aca="false">IF(O41&lt;0,O41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P42" s="67" t="n">
-        <f aca="false">MIN(D42:O42)</f>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="30" t="s">
+      <c r="D41" s="67" t="n">
+        <f aca="false">IF(D40&lt;0,D40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="67" t="n">
+        <f aca="false">IF(E40&lt;0,E40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="67" t="n">
+        <f aca="false">IF(F40&lt;0,F40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="67" t="n">
+        <f aca="false">IF(G40&lt;0,G40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="67" t="n">
+        <f aca="false">IF(H40&lt;0,H40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="67" t="n">
+        <f aca="false">IF(I40&lt;0,I40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="67" t="n">
+        <f aca="false">IF(J40&lt;0,J40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="67" t="n">
+        <f aca="false">IF(K40&lt;0,K40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="67" t="n">
+        <f aca="false">IF(L40&lt;0,L40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="67" t="n">
+        <f aca="false">IF(M40&lt;0,M40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N41" s="67" t="n">
+        <f aca="false">IF(N40&lt;0,N40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O41" s="67" t="n">
+        <f aca="false">IF(O40&lt;0,O40,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P41" s="67" t="n">
+        <f aca="false">MIN(D41:O41)</f>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="30" t="s">
         <v>253</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="3" t="s">
-        <v>256</v>
+      <c r="B46" s="30" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="30" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="30" t="s">
         <v>258</v>
       </c>
     </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+      <c r="Q49" s="40"/>
+    </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="40"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="40"/>
-      <c r="Q50" s="40"/>
+      <c r="B50" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>264</v>
+      <c r="B51" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="C51" s="34" t="n">
+        <f aca="false">O40</f>
+        <v>54164831</v>
+      </c>
+      <c r="D51" s="34" t="n">
+        <f aca="false">MIN(D40:O40)</f>
+        <v>14133449.3333334</v>
+      </c>
+      <c r="E51" s="24" t="n">
+        <f aca="false">IF(C51&lt;0,-MIN(C51,D51)+$C$55,MAX(0,-D51+$C$55))</f>
+        <v>21537787.7333333</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="C52" s="34" t="n">
-        <f aca="false">O41</f>
-        <v>52164831</v>
-      </c>
-      <c r="D52" s="34" t="n">
-        <f aca="false">MIN(D41:O41)</f>
-        <v>14133449.3333334</v>
+      <c r="B52" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="C52" s="67" t="n">
+        <f aca="false">C51-(P16+P18)</f>
+        <v>10164831</v>
+      </c>
+      <c r="D52" s="67" t="n">
+        <f aca="false">D51-(P16+P18)</f>
+        <v>-29866550.6666666</v>
       </c>
       <c r="E52" s="24" t="n">
-        <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$56,MAX(0,-D52+$C$56))</f>
-        <v>21537787.7333333</v>
+        <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$55,MAX(0,-D52+$C$55))</f>
+        <v>65537787.7333333</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="68" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C53" s="67" t="n">
-        <f aca="false">C52-(P16+P35)</f>
-        <v>10164831</v>
+        <f aca="false">C51-23333333*(1+$C$6)*12</f>
+        <v>-253835164.6</v>
       </c>
       <c r="D53" s="67" t="n">
-        <f aca="false">D52-(P16+P35)</f>
-        <v>-27866550.6666666</v>
+        <f aca="false">D51-23333333*(1+$C$6)*12</f>
+        <v>-293866546.266667</v>
       </c>
       <c r="E53" s="24" t="n">
-        <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$56,MAX(0,-D53+$C$56))</f>
-        <v>63537787.7333333</v>
+        <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$55,MAX(0,-D53+$C$55))</f>
+        <v>329537783.333333</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="68" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C54" s="67" t="n">
-        <f aca="false">C52-23333333*(1+$C$6)*12</f>
-        <v>-255835164.6</v>
+        <f aca="false">C51-(5043131-$C$9)*12</f>
+        <v>25593407</v>
       </c>
       <c r="D54" s="67" t="n">
-        <f aca="false">D52-23333333*(1+$C$6)*12</f>
-        <v>-293866546.266667</v>
+        <f aca="false">D51-(5043131-$C$9)*12</f>
+        <v>-14437974.6666666</v>
       </c>
       <c r="E54" s="24" t="n">
-        <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$56,MAX(0,-D54+$C$56))</f>
-        <v>329537783.333333</v>
+        <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$55,MAX(0,-D54+$C$55))</f>
+        <v>50109211.7333333</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="68" t="s">
-        <v>271</v>
-      </c>
-      <c r="C55" s="67" t="n">
-        <f aca="false">C52-(5043131-$C$9)*12</f>
-        <v>23593407</v>
-      </c>
-      <c r="D55" s="67" t="n">
-        <f aca="false">D52-(5043131-$C$9)*12</f>
-        <v>-14437974.6666666</v>
-      </c>
-      <c r="E55" s="24" t="n">
-        <f aca="false">IF(C55&lt;0,-MIN(C55,D55)+$C$56,MAX(0,-D55+$C$56))</f>
-        <v>50109211.7333333</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="6" t="s">
+      <c r="B55" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C56" s="51" t="n">
+      <c r="C55" s="51" t="n">
         <f aca="false">③FY2027月次推移!$C$6*(1+$C$6)</f>
         <v>35671237.0666667</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="30" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="30" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="30" t="s">
         <v>276</v>
       </c>
     </row>

--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -32,7 +32,7 @@
       <rPr>
         <b val="true"/>
         <sz val="15"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -51,7 +51,7 @@
       <rPr>
         <b val="true"/>
         <sz val="15"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -70,7 +70,7 @@
       <rPr>
         <b val="true"/>
         <sz val="15"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -90,17 +90,17 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ベース：飲食撤退後の実力値（</t>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ベース：再編後の実力値（</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -109,7 +109,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -118,8 +118,8 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -128,7 +128,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -139,7 +139,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -148,8 +148,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -158,7 +158,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -167,8 +167,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -177,7 +177,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -193,7 +193,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -216,7 +216,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -230,7 +230,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">撤退後実力値
+      <t xml:space="preserve">再編後実力値
 横ばいのみ</t>
     </r>
   </si>
@@ -240,7 +240,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -262,7 +262,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -285,7 +285,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -307,7 +307,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -330,7 +330,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -364,7 +364,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -373,8 +373,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -383,7 +383,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -392,8 +392,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -402,7 +402,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -411,8 +411,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -435,8 +435,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -445,7 +445,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -454,8 +454,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -481,8 +481,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -491,7 +491,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -500,8 +500,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -510,7 +510,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -519,8 +519,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -529,7 +529,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -543,7 +543,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -552,8 +552,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -562,7 +562,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -593,7 +593,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -613,7 +613,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -630,7 +630,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -649,7 +649,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -666,7 +666,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -688,7 +688,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -700,12 +700,12 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：撤退後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+      <t xml:space="preserve">：再編後の実力値を横ばいで延ばすだけでは営業利益▲</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -722,7 +722,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -741,7 +741,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -758,7 +758,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -775,7 +775,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -792,7 +792,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -811,7 +811,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -828,7 +828,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -845,7 +845,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -862,7 +862,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -879,7 +879,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -898,7 +898,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -915,7 +915,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -932,7 +932,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -949,7 +949,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -966,7 +966,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -993,7 +993,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1010,7 +1010,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1037,7 +1037,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1054,7 +1054,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1071,7 +1071,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1098,7 +1098,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1115,7 +1115,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1132,7 +1132,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1149,7 +1149,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1169,7 +1169,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1188,7 +1188,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1207,7 +1207,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1226,7 +1226,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1245,7 +1245,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1265,7 +1265,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1274,8 +1274,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1284,7 +1284,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1293,8 +1293,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1303,7 +1303,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1312,8 +1312,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1322,7 +1322,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1333,17 +1333,36 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飲食事業の撤退により、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店舗の撤退により、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1352,30 +1371,49 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以降が撤退後の実力値。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025/10-2026/03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には撤退店舗の費用が含まれる。</t>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降が再編後の実力値。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WineBank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テラスは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">WineBank CLUB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のフラッグシップ店として改善のうえ継続。</t>
     </r>
   </si>
   <si>
@@ -1422,7 +1460,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1444,7 +1482,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1475,7 +1513,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1570,7 +1608,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1579,8 +1617,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1589,17 +1627,36 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」がマイナスの科目＝飲食撤退および固定費削減により減少した費用。合計で月▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」がマイナスの科目＝不採算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店舗の撤退および固定費削減により減少した費用。合計で月▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1608,7 +1665,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1617,8 +1674,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1627,7 +1684,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1639,7 +1696,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1658,7 +1715,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1677,7 +1734,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1697,7 +1754,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1706,8 +1763,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1730,7 +1787,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1744,14 +1801,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">】ベース：飲食撤退後の実力値（</t>
+      <t xml:space="preserve">】ベース：再編後の実力値（</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1772,7 +1829,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1799,8 +1856,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1809,11 +1866,30 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以前は飲食撤退店舗の売上・費用を含むため基準から除外（貴社ご指摘）。</t>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以前は撤退した不採算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店舗の売上・費用を含むため基準から除外（貴社ご指摘）。</t>
     </r>
   </si>
   <si>
@@ -1835,7 +1911,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1856,7 +1932,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1894,7 +1970,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1913,7 +1989,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1940,7 +2016,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1959,7 +2035,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -1978,12 +2054,54 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Thierry Marx</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【グループ／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月開業】</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1997,7 +2115,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2014,7 +2132,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2031,7 +2149,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2050,12 +2168,20 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Apicius2 shot</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【外部／株主売却】</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">営業収益（成功報酬・一時）</t>
@@ -2072,7 +2198,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2099,7 +2225,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2126,7 +2252,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2153,7 +2279,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2175,7 +2301,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2184,8 +2310,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2194,7 +2320,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2203,8 +2329,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2213,7 +2339,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2222,8 +2348,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2232,7 +2358,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2241,8 +2367,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2251,7 +2377,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2265,26 +2391,26 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※うち約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※うち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2293,8 +2419,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2303,7 +2429,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2312,8 +2438,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2322,7 +2448,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2331,8 +2457,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2341,7 +2467,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2350,22 +2476,79 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Thierry Marx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）。</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Thierry Marx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月開業のグループ店。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">　うち 営業外収益</t>
@@ -2374,17 +2557,112 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">クルーザー事業利益は投資損益ではなく事業利益のため、全額を営業収益に計上。営業外収益は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※外部</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ito</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Aqua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hokkaido</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apicius2 shot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（外部株主売却）／クルーザー事業利益。クルーザーは事業利益のため全額営業収益に計上し、営業外収益は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2393,7 +2671,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2416,7 +2694,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2440,7 +2718,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2449,8 +2727,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2459,7 +2737,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2478,7 +2756,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2495,7 +2773,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2514,8 +2792,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2524,7 +2802,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2533,8 +2811,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2543,7 +2821,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2552,8 +2830,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2562,7 +2840,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2581,7 +2859,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2608,7 +2886,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2627,8 +2905,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2637,7 +2915,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2646,8 +2924,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2656,7 +2934,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2665,8 +2943,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2675,7 +2953,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2689,7 +2967,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2698,8 +2976,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2708,7 +2986,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2727,7 +3005,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2757,7 +3035,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2774,7 +3052,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2791,7 +3069,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2808,7 +3086,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2825,7 +3103,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2842,7 +3120,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2859,7 +3137,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2889,7 +3167,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2906,7 +3184,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2923,7 +3201,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2945,7 +3223,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2964,7 +3242,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2973,8 +3251,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -2983,7 +3261,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -2992,8 +3270,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3002,7 +3280,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3011,8 +3289,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3021,7 +3299,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3035,7 +3313,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3044,8 +3322,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3054,7 +3332,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3063,8 +3341,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3073,7 +3351,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3082,8 +3360,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3092,7 +3370,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3101,8 +3379,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3111,7 +3389,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3120,8 +3398,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3130,7 +3408,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3142,7 +3420,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3161,7 +3439,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3180,7 +3458,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3199,7 +3477,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3218,7 +3496,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3237,7 +3515,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3256,7 +3534,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3275,7 +3553,7 @@
       <rPr>
         <b val="true"/>
         <sz val="13"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3295,8 +3573,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3305,7 +3583,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3314,8 +3592,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3324,7 +3602,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3333,8 +3611,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3343,7 +3621,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3365,7 +3643,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3384,7 +3662,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3445,7 +3723,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3462,7 +3740,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3501,7 +3779,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3520,7 +3798,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3539,7 +3817,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3558,7 +3836,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3577,7 +3855,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3594,7 +3872,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3611,7 +3889,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3630,7 +3908,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3656,7 +3934,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3665,8 +3943,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3675,7 +3953,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3686,7 +3964,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3695,8 +3973,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3705,7 +3983,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3714,8 +3992,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3724,7 +4002,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3733,8 +4011,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3743,7 +4021,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3752,8 +4030,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3762,7 +4040,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3774,7 +4052,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3793,7 +4071,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3826,7 +4104,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3852,8 +4130,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3862,7 +4140,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3871,8 +4149,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3881,7 +4159,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3890,8 +4168,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3900,7 +4178,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3914,17 +4192,36 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">飲食撤退＋固定費削減。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不採算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店舗の撤退＋固定費削減。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3933,7 +4230,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3942,8 +4239,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3952,7 +4249,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3966,7 +4263,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3975,8 +4272,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -3985,7 +4282,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -3994,8 +4291,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4004,7 +4301,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4013,8 +4310,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4026,7 +4323,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4045,7 +4342,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4078,7 +4375,7 @@
       <rPr>
         <b val="true"/>
         <sz val="12"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4106,7 +4403,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4125,7 +4422,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4134,8 +4431,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4144,7 +4441,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4165,7 +4462,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4185,7 +4482,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4194,8 +4491,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4204,7 +4501,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4227,7 +4524,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4252,7 +4549,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4273,7 +4570,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4294,7 +4591,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4315,7 +4612,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4336,7 +4633,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4360,7 +4657,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4379,7 +4676,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4399,7 +4696,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4408,8 +4705,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4418,7 +4715,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4429,7 +4726,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4438,8 +4735,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4448,7 +4745,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4459,7 +4756,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4468,8 +4765,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4478,7 +4775,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4487,8 +4784,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4497,7 +4794,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4506,8 +4803,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4516,7 +4813,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4539,7 +4836,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4560,7 +4857,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4587,8 +4884,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4597,7 +4894,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4606,8 +4903,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4616,7 +4913,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4625,8 +4922,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4635,7 +4932,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4644,8 +4941,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4654,7 +4951,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4663,8 +4960,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4673,7 +4970,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4682,8 +4979,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4692,7 +4989,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4706,8 +5003,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4716,7 +5013,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4742,7 +5039,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4751,8 +5048,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4761,7 +5058,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4770,8 +5067,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4780,7 +5077,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4789,8 +5086,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4799,7 +5096,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4808,8 +5105,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4818,7 +5115,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4838,7 +5135,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4847,8 +5144,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4857,7 +5154,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4866,8 +5163,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4876,7 +5173,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4885,8 +5182,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4895,7 +5192,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4909,8 +5206,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4919,7 +5216,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4928,8 +5225,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4938,7 +5235,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4947,8 +5244,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4957,7 +5254,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -4969,7 +5266,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -4988,7 +5285,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5007,7 +5304,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5026,7 +5323,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5045,7 +5342,7 @@
       <rPr>
         <b val="true"/>
         <sz val="14"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5065,7 +5362,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5074,8 +5371,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5084,7 +5381,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5093,8 +5390,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5103,7 +5400,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5112,8 +5409,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5122,7 +5419,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5144,7 +5441,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5163,8 +5460,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5173,7 +5470,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5182,8 +5479,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5192,7 +5489,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5209,7 +5506,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5218,8 +5515,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5228,7 +5525,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5237,8 +5534,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5247,7 +5544,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5256,8 +5553,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5266,7 +5563,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5275,8 +5572,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5285,7 +5582,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5294,8 +5591,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5304,7 +5601,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5318,7 +5615,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5327,8 +5624,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5337,7 +5634,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5346,8 +5643,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5356,7 +5653,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5365,8 +5662,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5375,7 +5672,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5384,8 +5681,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5394,7 +5691,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5403,8 +5700,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5413,7 +5710,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5427,7 +5724,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5436,8 +5733,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5446,7 +5743,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5455,8 +5752,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5465,7 +5762,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5474,8 +5771,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5484,7 +5781,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5493,8 +5790,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5503,7 +5800,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5517,7 +5814,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5526,8 +5823,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5536,7 +5833,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5562,8 +5859,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5572,7 +5869,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5581,8 +5878,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5591,7 +5888,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5600,8 +5897,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5610,7 +5907,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5619,8 +5916,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5629,7 +5926,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5643,8 +5940,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5653,7 +5950,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5662,8 +5959,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5672,7 +5969,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5681,8 +5978,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5691,7 +5988,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5723,8 +6020,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5733,7 +6030,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5742,8 +6039,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5752,7 +6049,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5761,8 +6058,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5771,7 +6068,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5780,8 +6077,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5790,7 +6087,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5799,8 +6096,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5809,7 +6106,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5844,8 +6141,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5854,7 +6151,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5863,8 +6160,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5873,7 +6170,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5882,8 +6179,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5892,7 +6189,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5921,7 +6218,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5930,8 +6227,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5940,7 +6237,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5954,7 +6251,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5963,8 +6260,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -5973,7 +6270,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5987,7 +6284,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -5996,8 +6293,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6006,7 +6303,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6036,7 +6333,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6055,7 +6352,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6074,7 +6371,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6093,7 +6390,7 @@
       <rPr>
         <b val="true"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6113,7 +6410,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6122,8 +6419,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6132,7 +6429,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6141,8 +6438,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6151,7 +6448,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6160,8 +6457,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6170,7 +6467,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6179,8 +6476,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6189,7 +6486,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6200,7 +6497,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6219,7 +6516,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6228,8 +6525,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6238,7 +6535,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6249,7 +6546,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6266,7 +6563,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6285,7 +6582,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6294,8 +6591,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6304,7 +6601,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6313,8 +6610,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6323,7 +6620,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6334,7 +6631,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6351,7 +6648,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6370,7 +6667,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6379,8 +6676,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6389,7 +6686,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6398,8 +6695,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6408,7 +6705,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6427,7 +6724,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6446,7 +6743,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6455,8 +6752,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6465,7 +6762,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6476,7 +6773,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6485,8 +6782,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6495,7 +6792,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6504,8 +6801,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6514,7 +6811,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6525,7 +6822,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6534,8 +6831,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6544,7 +6841,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6553,8 +6850,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6563,7 +6860,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6586,7 +6883,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6607,7 +6904,7 @@
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6631,8 +6928,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6641,7 +6938,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF595959"/>
+        <color rgb="FF8C8C8C"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6679,7 +6976,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6688,8 +6985,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6698,7 +6995,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6709,7 +7006,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6718,8 +7015,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6728,7 +7025,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6737,8 +7034,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6747,7 +7044,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6756,8 +7053,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6766,7 +7063,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6777,7 +7074,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6786,8 +7083,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6796,7 +7093,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6805,8 +7102,8 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
@@ -6815,7 +7112,7 @@
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
+        <color rgb="FF333333"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -6840,61 +7137,61 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="メイリオ"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="15"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="15"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -6902,167 +7199,169 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="13"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <color rgb="FF333333"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
+      <color rgb="FF333333"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="Arial"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="Arial"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
+      <color rgb="FF595959"/>
+      <name val="メイリオ"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="メイリオ"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="メイリオ"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <color rgb="FF595959"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="WenQuanYi Zen Hei"/>
+      <name val="メイリオ"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7071,56 +7370,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF1A1A1A"/>
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFE6E4E0"/>
+        <bgColor rgb="FFE8E6E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFDF6E3"/>
+        <fgColor rgb="FFF0EFEC"/>
+        <bgColor rgb="FFEEEDEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFDF6E3"/>
+        <fgColor rgb="FFEEEDEA"/>
+        <bgColor rgb="FFF0EFEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
+        <fgColor rgb="FFE0DEDA"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFE7E6E6"/>
+        <fgColor rgb="FFE8E6E2"/>
+        <bgColor rgb="FFE6E4E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFD9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6E3"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFF5F4F1"/>
+        <bgColor rgb="FFF0EFEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -7135,7 +7422,9 @@
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color rgb="FF1A1A1A"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -7165,7 +7454,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7250,11 +7539,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7290,11 +7579,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7310,7 +7599,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7330,7 +7619,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7366,7 +7655,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7410,11 +7699,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7430,11 +7719,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7455,7 +7740,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -7467,12 +7752,12 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC6E0B4"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFE0DEDA"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF6D2E46"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFF5F4F1"/>
+      <rgbColor rgb="FFF0EFEC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -7486,13 +7771,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFD9E2F3"/>
-      <rgbColor rgb="FFE7E6E6"/>
-      <rgbColor rgb="FFFDF6E3"/>
+      <rgbColor rgb="FFEEEDEA"/>
+      <rgbColor rgb="FFE8E6E2"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF8CBAD"/>
+      <rgbColor rgb="FFE6E4E0"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -7500,11 +7785,11 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF8C8C8C"/>
+      <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF1A1A1A"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
@@ -7563,11 +7848,11 @@
           <c:order val="0"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="6d2e46"/>
+              <a:srgbClr val="1a1a1a"/>
             </a:solidFill>
             <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="6d2e46"/>
+                <a:srgbClr val="1a1a1a"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -7699,11 +7984,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="13334797"/>
-        <c:axId val="23143219"/>
+        <c:axId val="34988111"/>
+        <c:axId val="51477183"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="13334797"/>
+        <c:axId val="34988111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7735,7 +8020,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23143219"/>
+        <c:crossAx val="51477183"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7743,7 +8028,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23143219"/>
+        <c:axId val="51477183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7819,7 +8104,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13334797"/>
+        <c:crossAx val="34988111"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15502,55 +15787,55 @@
       <c r="B41" s="66" t="s">
         <v>266</v>
       </c>
-      <c r="D41" s="67" t="n">
+      <c r="D41" s="52" t="n">
         <f aca="false">IF(D40&lt;0,D40,0)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="67" t="n">
+      <c r="E41" s="52" t="n">
         <f aca="false">IF(E40&lt;0,E40,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="67" t="n">
+      <c r="F41" s="52" t="n">
         <f aca="false">IF(F40&lt;0,F40,0)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="67" t="n">
+      <c r="G41" s="52" t="n">
         <f aca="false">IF(G40&lt;0,G40,0)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="67" t="n">
+      <c r="H41" s="52" t="n">
         <f aca="false">IF(H40&lt;0,H40,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="67" t="n">
+      <c r="I41" s="52" t="n">
         <f aca="false">IF(I40&lt;0,I40,0)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="67" t="n">
+      <c r="J41" s="52" t="n">
         <f aca="false">IF(J40&lt;0,J40,0)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="67" t="n">
+      <c r="K41" s="52" t="n">
         <f aca="false">IF(K40&lt;0,K40,0)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="67" t="n">
+      <c r="L41" s="52" t="n">
         <f aca="false">IF(L40&lt;0,L40,0)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="67" t="n">
+      <c r="M41" s="52" t="n">
         <f aca="false">IF(M40&lt;0,M40,0)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="67" t="n">
+      <c r="N41" s="52" t="n">
         <f aca="false">IF(N40&lt;0,N40,0)</f>
         <v>0</v>
       </c>
-      <c r="O41" s="67" t="n">
+      <c r="O41" s="52" t="n">
         <f aca="false">IF(O40&lt;0,O40,0)</f>
         <v>0</v>
       </c>
-      <c r="P41" s="67" t="n">
+      <c r="P41" s="52" t="n">
         <f aca="false">MIN(D41:O41)</f>
         <v>0</v>
       </c>
@@ -15644,11 +15929,11 @@
       <c r="B52" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="67" t="n">
+      <c r="C52" s="52" t="n">
         <f aca="false">C51+(②前提!$C$34-③FY2027月次推移!$P$9)*(1+$C$6)</f>
         <v>171289494.492619</v>
       </c>
-      <c r="D52" s="67" t="n">
+      <c r="D52" s="52" t="n">
         <f aca="false">D51+(②前提!$C$34-③FY2027月次推移!$P$9)*(1+$C$6)</f>
         <v>129973969.492619</v>
       </c>
@@ -15664,11 +15949,11 @@
       <c r="B53" s="23" t="s">
         <v>283</v>
       </c>
-      <c r="C53" s="67" t="n">
+      <c r="C53" s="52" t="n">
         <f aca="false">C51-(P16+P18)</f>
         <v>-2684475.00000007</v>
       </c>
-      <c r="D53" s="67" t="n">
+      <c r="D53" s="52" t="n">
         <f aca="false">D51-(P16+P18)</f>
         <v>-44000000</v>
       </c>
@@ -15684,11 +15969,11 @@
       <c r="B54" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="C54" s="67" t="n">
+      <c r="C54" s="52" t="n">
         <f aca="false">C51-①サマリー!$C$24*(1+$C$6)</f>
         <v>-213805778.4</v>
       </c>
-      <c r="D54" s="67" t="n">
+      <c r="D54" s="52" t="n">
         <f aca="false">D51-①サマリー!$C$24*(1+$C$6)</f>
         <v>-255121303.4</v>
       </c>
@@ -15807,40 +16092,40 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D84" s="68" t="s">
+      <c r="D84" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="E84" s="68" t="s">
+      <c r="E84" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="F84" s="68" t="s">
+      <c r="F84" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="G84" s="68" t="s">
+      <c r="G84" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="H84" s="68" t="s">
+      <c r="H84" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="I84" s="68" t="s">
+      <c r="I84" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="J84" s="68" t="s">
+      <c r="J84" s="67" t="s">
         <v>147</v>
       </c>
-      <c r="K84" s="68" t="s">
+      <c r="K84" s="67" t="s">
         <v>148</v>
       </c>
-      <c r="L84" s="68" t="s">
+      <c r="L84" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="M84" s="68" t="s">
+      <c r="M84" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="N84" s="68" t="s">
+      <c r="N84" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="O84" s="68" t="s">
+      <c r="O84" s="67" t="s">
         <v>152</v>
       </c>
     </row>

--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="340">
   <si>
     <r>
       <rPr>
@@ -334,7 +334,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">D. CF</t>
+      <t xml:space="preserve">D. </t>
     </r>
     <r>
       <rPr>
@@ -344,8 +344,19 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">が回る
-売上水準</t>
+      <t xml:space="preserve">保守シナリオ
+売上前期並み・粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42%</t>
     </r>
   </si>
   <si>
@@ -355,9 +366,146 @@
     <t xml:space="preserve">既存事業 売上</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は売上高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円−上乗せ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">売上総利益（既存事業）</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の加重平均）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">＋上乗せ案件（営業収益）</t>
   </si>
   <si>
@@ -442,12 +590,80 @@
     <t xml:space="preserve">＋追加で必要な粗利</t>
   </si>
   <si>
-    <t xml:space="preserve">追加売上から生じる粗利</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ：経常利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円に必要な粗利の上積み</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">売上総利益 合計</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の総合粗利率は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42.3%</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">販管費</t>
   </si>
   <si>
@@ -488,7 +704,7 @@
     <t xml:space="preserve">営業外収益</t>
   </si>
   <si>
-    <t xml:space="preserve">クルーザー事業利益は営業収益に計上</t>
+    <t xml:space="preserve">新規クルーザー事業利益は営業収益に計上</t>
   </si>
   <si>
     <t xml:space="preserve">営業外費用</t>
@@ -514,7 +730,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は目標経常利益・</t>
+      <t xml:space="preserve">は目標経常利益から逆算・</t>
     </r>
     <r>
       <rPr>
@@ -533,26 +749,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は所要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">から逆算</t>
+      <t xml:space="preserve">は前提から算出</t>
     </r>
   </si>
   <si>
@@ -592,7 +789,7 @@
     <t xml:space="preserve">当期純利益</t>
   </si>
   <si>
-    <t xml:space="preserve">【必要となる追加売上】</t>
+    <t xml:space="preserve">【参考：必要となる売上水準】</t>
   </si>
   <si>
     <t xml:space="preserve">追加売上</t>
@@ -661,13 +858,263 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億円に必要な追加売上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t xml:space="preserve">億円に必要な追加売上（粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前提）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">資金繰りが回る最低売上高（仕入固定のため粗利率に依存しない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【判定】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：再編後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">99.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">114.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せ案件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を全額営業収益に計上すると営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：粗利率を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のまま置いた場合、経常利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億円には追加売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,918</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円が必要。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
@@ -676,66 +1123,132 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">が回るのに必要な追加売上</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【判定】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（本線）：売上を前期・今期と同程度</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：再編後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">99.6</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に置き、粗利率を保守的に落とした前提。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">　　既存事業の粗利率は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025 26.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 32.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の加重平均）。上乗せ案件は原価なしのため総合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">百万円・経常利益▲</t>
     </r>
     <r>
@@ -745,7 +1258,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">114.6</t>
+      <t xml:space="preserve">6.2</t>
     </r>
     <r>
       <rPr>
@@ -753,10 +1266,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円。</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">百万円。損益はほぼ均衡だが、減価償却</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -764,7 +1275,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B</t>
+      <t xml:space="preserve">43.7</t>
     </r>
     <r>
       <rPr>
@@ -772,416 +1283,72 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：上乗せ案件</t>
-    </r>
+      <t xml:space="preserve">百万円があるため資金は回る。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132.5</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ワイン仕入を</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を全額営業収益に計上すると営業利益＋</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32.9</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と同額</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・経常利益＋</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">419.1</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17.9</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に固定した場合、売上原価</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円で黒字化する。</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">421.6</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：経常利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円には追加売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5,918</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円が必要（新規顧客売上計画の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。ただしこの水準では資金が回らない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：ワイン仕入を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と同水準（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">419.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）に維持したまま資金を回すには、追加売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,193</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円が必要。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　　このとき売上高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">621.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・経常利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">137.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円となり、期中の現預金は一度もマイナスにならない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※在庫は成長の源泉であり仕入を絞らない方針のため、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を本線とする。期末在庫は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">538.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">118.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ボトルネックは</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分の消費税</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円の納付月）。詳細は⑦資金繰り表の必要売上高の算定を参照。</t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円で在庫はほぼ横ばい。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※資金繰りは粗利率ではなく売上高で決まる（仕入を固定額で置くため）。詳細は⑦資金繰り表を参照。</t>
   </si>
   <si>
     <r>
@@ -3855,6 +4022,378 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">百万円では納付側。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（保守シナリオ）の前提　売上は前期・今期と同程度、粗利率は保守的に設定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">売上高（前期・今期と同程度）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">752,864,901</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">見込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">708,205,820</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の平均</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　うち 上乗せ案件（原価なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料等。粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　うち 既存事業 売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売上高−上乗せ案件。上乗せ分を差し引くことで保守的に置く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存事業の粗利率（保守）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025 26.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 32.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の加重平均。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月実績の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は用いない</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　既存事業 売上総利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存事業＋上乗せ案件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総合粗利率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上乗せ案件が原価なしのため、既存</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に対し全体では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前後になる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※仕入を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と同額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">419.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円に固定すると売上原価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">421.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円となり在庫はほぼ横ばい。資金繰りは粗利率ではなく売上高で決まる。</t>
     </r>
   </si>
   <si>
@@ -7934,7 +8473,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7971,6 +8510,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7984,10 +8527,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8128,6 +8667,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8416,40 +8959,40 @@
                 <c:formatCode>\¥#,##0;"(¥"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>25206248.275</c:v>
+                  <c:v>28120114.8166667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16394882.45</c:v>
+                  <c:v>22222615.5333333</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11601130.725</c:v>
+                  <c:v>20342730.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6807379.00000006</c:v>
+                  <c:v>18462845.1666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.45058059692383E-008</c:v>
+                  <c:v>14569332.7083334</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28206248.2750001</c:v>
+                  <c:v>45689447.525</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>23412496.5500001</c:v>
+                  <c:v>43809562.3416667</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>16605117.5500001</c:v>
+                  <c:v>39916049.8833334</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11811365.8250001</c:v>
+                  <c:v>38036164.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7017614.10000014</c:v>
+                  <c:v>36156279.5166667</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>210235.100000158</c:v>
+                  <c:v>32262767.0583334</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6416483.37500017</c:v>
+                  <c:v>41382881.8750001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8464,11 +9007,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42551222"/>
-        <c:axId val="81923714"/>
+        <c:axId val="32171718"/>
+        <c:axId val="85420272"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="42551222"/>
+        <c:axId val="32171718"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8500,7 +9043,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81923714"/>
+        <c:crossAx val="85420272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8508,7 +9051,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81923714"/>
+        <c:axId val="85420272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8584,7 +9127,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42551222"/>
+        <c:crossAx val="32171718"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8827,7 +9370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:H35"/>
+  <dimension ref="B1:H36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -8894,14 +9437,16 @@
         <v>548324458.420246</v>
       </c>
       <c r="G6" s="8" t="n">
-        <f aca="false">E6+$C$24</f>
-        <v>566247725</v>
-      </c>
-      <c r="H6" s="3"/>
+        <f aca="false">②前提!$C$51</f>
+        <v>598035360</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>229139405</v>
@@ -8919,14 +9464,16 @@
         <v>200601928</v>
       </c>
       <c r="G7" s="8" t="n">
-        <f aca="false">E7</f>
-        <v>200601928</v>
-      </c>
-      <c r="H7" s="3"/>
+        <f aca="false">②前提!$C$53</f>
+        <v>176420431.2</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -8947,56 +9494,55 @@
         <v>132500000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">②前提!$C$28+F14-F13+F11-F7-F8</f>
         <v>82059136</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <f aca="false">$C$24*②前提!$C$9</f>
-        <v>91298573.5702025</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>15</v>
+      <c r="G9" s="10"/>
+      <c r="H9" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="11" t="n">
+      <c r="B10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>229139405</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="12" t="n">
         <f aca="false">D7+D8</f>
         <v>200601928</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="12" t="n">
         <f aca="false">E7+E8</f>
         <v>333101928</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <f aca="false">F7+F8+F9</f>
         <v>415161064</v>
       </c>
-      <c r="G10" s="11" t="n">
-        <f aca="false">G7+G8+G9</f>
-        <v>424400501.570202</v>
-      </c>
-      <c r="H10" s="12"/>
+      <c r="G10" s="12" t="n">
+        <f aca="false">②前提!$C$54</f>
+        <v>308920431.2</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>343932836</v>
@@ -9017,38 +9563,38 @@
         <f aca="false">E11</f>
         <v>300161064</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>18</v>
+      <c r="H11" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="11" t="n">
+      <c r="B12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>-114793431</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="12" t="n">
         <f aca="false">D10-D11</f>
         <v>-99559136</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="12" t="n">
         <f aca="false">E10-E11</f>
         <v>32940864</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <f aca="false">F10-F11</f>
         <v>115000000</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="12" t="n">
         <f aca="false">G10-G11</f>
-        <v>124239437.570202</v>
-      </c>
-      <c r="H12" s="12"/>
+        <v>8759367.19999999</v>
+      </c>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -9066,12 +9612,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>10000000</v>
@@ -9096,7 +9642,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C15" s="15" t="n">
         <v>-124793431</v>
@@ -9115,15 +9661,15 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G12+G13-G14</f>
-        <v>109239437.570202</v>
+        <v>-6240632.80000001</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -9141,50 +9687,50 @@
         <v>0</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="11" t="n">
+      <c r="B17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>-124793431</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">D15-D16</f>
         <v>-114559136</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">E15-E16</f>
         <v>17940864</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <f aca="false">F15-F16</f>
         <v>100000000</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">G15-G16</f>
-        <v>109239437.570202</v>
-      </c>
-      <c r="H17" s="12"/>
+        <v>-6240632.80000001</v>
+      </c>
+      <c r="H17" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="18" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C23" s="21" t="n">
         <f aca="false">F9/②前提!$C$9</f>
@@ -9196,17 +9742,14 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20" t="s">
-        <v>32</v>
+      <c r="B24" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C24" s="21" t="n">
         <f aca="false">⑦FY2027資金繰り表!$C$88</f>
         <v>177106957</v>
       </c>
-      <c r="D24" s="22" t="n">
-        <f aca="false">C24/②前提!$C$29</f>
-        <v>0.166141610694184</v>
-      </c>
+      <c r="D24" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="23"/>
@@ -9219,7 +9762,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -9230,7 +9773,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -9241,7 +9784,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -9252,7 +9795,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="23"/>
@@ -9263,7 +9806,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C31" s="23"/>
       <c r="D31" s="23"/>
@@ -9274,7 +9817,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
@@ -9284,28 +9827,28 @@
       <c r="H32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
+      <c r="B33" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
@@ -9314,8 +9857,19 @@
       <c r="G35" s="25"/>
       <c r="H35" s="25"/>
     </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="B28:H28"/>
@@ -9326,6 +9880,7 @@
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B34:H34"/>
     <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9354,17 +9909,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9372,57 +9927,57 @@
         <v>3</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K5" s="28" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M5" s="28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N5" s="28" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P5" s="29" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Q5" s="29" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="R5" s="19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>32789307</v>
@@ -9479,7 +10034,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>18502877</v>
@@ -9536,7 +10091,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="32" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>14286430</v>
@@ -9593,12 +10148,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>1450000</v>
@@ -9655,7 +10210,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>5733907</v>
@@ -9712,7 +10267,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2678253</v>
@@ -9769,7 +10324,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>932201</v>
@@ -9826,7 +10381,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>53900</v>
@@ -9883,7 +10438,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>234134</v>
@@ -9940,7 +10495,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2786025</v>
@@ -9997,7 +10552,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4193310</v>
@@ -10054,7 +10609,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>298477</v>
@@ -10111,7 +10666,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>956603</v>
@@ -10168,7 +10723,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>385679</v>
@@ -10225,7 +10780,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>163840</v>
@@ -10282,7 +10837,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0</v>
@@ -10339,7 +10894,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>208971</v>
@@ -10396,7 +10951,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>732759</v>
@@ -10453,7 +11008,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>216380</v>
@@ -10510,7 +11065,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>31310</v>
@@ -10567,7 +11122,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>64335</v>
@@ -10624,7 +11179,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10000</v>
@@ -10681,7 +11236,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>0</v>
@@ -10738,7 +11293,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>10091</v>
@@ -10795,7 +11350,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>3815699</v>
@@ -10852,7 +11407,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>419018</v>
@@ -10909,133 +11464,133 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C34" s="12" t="n">
         <f aca="false">SUM(C11:C33)</f>
         <v>25374892</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="12" t="n">
         <f aca="false">SUM(D11:D33)</f>
         <v>30963282</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="12" t="n">
         <f aca="false">SUM(E11:E33)</f>
         <v>38572456</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="12" t="n">
         <f aca="false">SUM(F11:F33)</f>
         <v>33761779</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="12" t="n">
         <f aca="false">SUM(G11:G33)</f>
         <v>34133901</v>
       </c>
-      <c r="H34" s="11" t="n">
+      <c r="H34" s="12" t="n">
         <f aca="false">SUM(H11:H33)</f>
         <v>38737868</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="I34" s="12" t="n">
         <f aca="false">SUM(I11:I33)</f>
         <v>25883967</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J34" s="12" t="n">
         <f aca="false">SUM(J11:J33)</f>
         <v>24529013</v>
       </c>
-      <c r="K34" s="11" t="n">
+      <c r="K34" s="12" t="n">
         <f aca="false">SUM(K11:K33)</f>
         <v>24627286</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="12" t="n">
         <f aca="false">SUM(L11:L33)</f>
         <v>21021014</v>
       </c>
-      <c r="M34" s="11" t="n">
+      <c r="M34" s="12" t="n">
         <f aca="false">SUM(M11:M33)</f>
         <v>23912797</v>
       </c>
-      <c r="N34" s="11" t="n">
+      <c r="N34" s="12" t="n">
         <f aca="false">SUM(N11:N33)</f>
         <v>22414578</v>
       </c>
-      <c r="O34" s="11" t="n">
+      <c r="O34" s="12" t="n">
         <f aca="false">SUM(C34:N34)</f>
         <v>343932833</v>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="P34" s="12" t="n">
         <f aca="false">AVERAGE(C34:H34)</f>
         <v>33590696.3333333</v>
       </c>
-      <c r="Q34" s="11" t="n">
+      <c r="Q34" s="12" t="n">
         <f aca="false">AVERAGE(I34:K34)</f>
         <v>25013422</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="R34" s="12" t="n">
         <f aca="false">Q34-P34</f>
         <v>-8577274.33333334</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C35" s="11" t="n">
+      <c r="B35" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="12" t="n">
         <f aca="false">C8-C34</f>
         <v>-11088462</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="12" t="n">
         <f aca="false">D8-D34</f>
         <v>-3256174</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <f aca="false">E8-E34</f>
         <v>-16617901</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="12" t="n">
         <f aca="false">F8-F34</f>
         <v>-17805770</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="12" t="n">
         <f aca="false">G8-G34</f>
         <v>-13913836</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="H35" s="12" t="n">
         <f aca="false">H8-H34</f>
         <v>-24158947</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I35" s="12" t="n">
         <f aca="false">I8-I34</f>
         <v>-10204526</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="J35" s="12" t="n">
         <f aca="false">J8-J34</f>
         <v>-6389820</v>
       </c>
-      <c r="K35" s="11" t="n">
+      <c r="K35" s="12" t="n">
         <f aca="false">K8-K34</f>
         <v>-8295438</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="12" t="n">
         <f aca="false">L8-L34</f>
         <v>1072434</v>
       </c>
-      <c r="M35" s="11" t="n">
+      <c r="M35" s="12" t="n">
         <f aca="false">M8-M34</f>
         <v>-9672102</v>
       </c>
-      <c r="N35" s="11" t="n">
+      <c r="N35" s="12" t="n">
         <f aca="false">N8-N34</f>
         <v>5537114</v>
       </c>
-      <c r="O35" s="11" t="n">
+      <c r="O35" s="12" t="n">
         <f aca="false">SUM(C35:N35)</f>
         <v>-114793428</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -11054,7 +11609,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G46"/>
+  <dimension ref="B1:G57"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -11065,17 +11620,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="35" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="36" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
@@ -11085,27 +11640,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I6:K6)</f>
         <v>32428397.3333333</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C7" s="39" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I8:K8)</f>
@@ -11114,7 +11669,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I34:K34)</f>
@@ -11123,7 +11678,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C9" s="41" t="n">
         <f aca="false">C7/C6</f>
@@ -11132,7 +11687,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C11" s="37"/>
       <c r="D11" s="37"/>
@@ -11142,140 +11697,140 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="42" t="n">
         <v>80000000</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C14" s="42" t="n">
         <v>2500000</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C15" s="42" t="n">
         <v>10000000</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C16" s="42" t="n">
         <v>20000000</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C17" s="42" t="n">
         <v>10000000</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C18" s="42" t="n">
         <v>10000000</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="43" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C19" s="31" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>132500000</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>132500000</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -11285,117 +11840,117 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C24" s="42" t="n">
         <v>15000000</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C25" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>122</v>
+      <c r="F25" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C26" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>122</v>
+      <c r="F26" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C27" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>125</v>
+      <c r="F27" s="9" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C28" s="42" t="n">
         <v>100000000</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C29" s="42" t="n">
         <v>1066000000</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C30" s="44" t="n">
         <v>3</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C31" s="44" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C32" s="42" t="n">
         <v>419066414</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C33" s="45" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F33" s="46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="36" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -11405,7 +11960,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C36" s="47" t="n">
         <v>0.1</v>
@@ -11414,41 +11969,41 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C37" s="42" t="n">
         <v>708205820</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="20" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C38" s="31" t="n">
         <f aca="false">C32</f>
         <v>419066414</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C39" s="42" t="n">
         <v>208594315</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C40" s="31" t="n">
         <f aca="false">C37*C36</f>
@@ -11458,7 +12013,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C41" s="31" t="n">
         <f aca="false">(C38+C39)*C36</f>
@@ -11468,54 +12023,149 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C42" s="48" t="n">
         <f aca="false">C40-C41</f>
         <v>8054509.09999999</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C43" s="42" t="n">
         <v>4500000</v>
       </c>
-      <c r="F43" s="13" t="s">
-        <v>151</v>
+      <c r="F43" s="9" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">C42-C43</f>
         <v>3554509.09999999</v>
       </c>
-      <c r="F44" s="13" t="s">
-        <v>153</v>
+      <c r="F44" s="9" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">C42/4</f>
         <v>2013627.275</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F46" s="27" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="42" t="n">
+        <v>730535360</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C50" s="31" t="n">
+        <f aca="false">C20</f>
+        <v>132500000</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="31" t="n">
+        <f aca="false">C49-C50</f>
+        <v>598035360</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="47" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C53" s="31" t="n">
+        <f aca="false">C51*C52</f>
+        <v>176420431.2</v>
+      </c>
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="48" t="n">
+        <f aca="false">C53+C50</f>
+        <v>308920431.2</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" s="49" t="n">
+        <f aca="false">C54/C49</f>
+        <v>0.422868553823322</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F57" s="27" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -11546,12 +12196,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="26" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="13" t="s">
-        <v>158</v>
+      <c r="B2" s="9" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11559,72 +12209,72 @@
         <v>3</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="K4" s="28" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M4" s="28" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="P4" s="38" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
+        <v>191</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="51" t="n">
         <f aca="false">②前提!$C$6</f>
         <v>32428397.3333333</v>
       </c>
@@ -11683,314 +12333,314 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="D7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="E7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="F7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="G7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="H7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="I7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="K7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="L7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="M7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="N7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
-      </c>
-      <c r="O7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=3,⑦FY2027資金繰り表!$C$88/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
-        <v>14758913.0833333</v>
+        <v>192</v>
+      </c>
+      <c r="C7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="D7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="E7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="H7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="I7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="J7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="K7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="L7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="M7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="N7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
+      </c>
+      <c r="O7" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(②前提!$C$51-②前提!$C$6*12)/12,IF(②前提!$C$30=2,①サマリー!$C$23/12,0))</f>
+        <v>17407882.6666667</v>
       </c>
       <c r="P7" s="31" t="n">
         <f aca="false">SUM(D7:O7)</f>
-        <v>177106957</v>
+        <v>208894592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="32" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="C8" s="31" t="n">
         <f aca="false">C6+C7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="D8" s="31" t="n">
         <f aca="false">D6+D7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="E8" s="31" t="n">
         <f aca="false">E6+E7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="F8" s="31" t="n">
         <f aca="false">F6+F7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="G8" s="31" t="n">
         <f aca="false">G6+G7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="H8" s="31" t="n">
         <f aca="false">H6+H7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="I8" s="31" t="n">
         <f aca="false">I6+I7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="J8" s="31" t="n">
         <f aca="false">J6+J7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="K8" s="31" t="n">
         <f aca="false">K6+K7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="L8" s="31" t="n">
         <f aca="false">L6+L7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="M8" s="31" t="n">
         <f aca="false">M6+M7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="N8" s="31" t="n">
         <f aca="false">N6+N7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="O8" s="31" t="n">
         <f aca="false">O6+O7</f>
-        <v>47187310.4166667</v>
+        <v>49836280</v>
       </c>
       <c r="P8" s="31" t="n">
         <f aca="false">SUM(D8:O8)</f>
-        <v>566247725</v>
+        <v>598035360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="50" t="n">
+        <v>194</v>
+      </c>
+      <c r="C9" s="51" t="n">
         <f aca="false">C8-C10-C11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">D8-D10-D11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="E9" s="8" t="n">
         <f aca="false">E8-E10-E11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">F8-F10-F11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="G9" s="8" t="n">
         <f aca="false">G8-G10-G11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="H9" s="8" t="n">
         <f aca="false">H8-H10-H11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="I9" s="8" t="n">
         <f aca="false">I8-I10-I11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="J9" s="8" t="n">
         <f aca="false">J8-J10-J11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="K9" s="8" t="n">
         <f aca="false">K8-K10-K11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="L9" s="8" t="n">
         <f aca="false">L8-L10-L11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="M9" s="8" t="n">
         <f aca="false">M8-M10-M11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">N8-N10-N11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="O9" s="8" t="n">
         <f aca="false">O8-O10-O11</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="P9" s="31" t="n">
         <f aca="false">SUM(D9:O9)</f>
-        <v>274347223.429798</v>
+        <v>421614928.8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="50" t="n">
-        <f aca="false">②前提!$C$7</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <f aca="false">$C$10</f>
-        <v>16716827.3333333</v>
+        <v>195</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(C6+C7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="D10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(D6+D7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="E10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(E6+E7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(F6+F7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="G10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(G6+G7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="H10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(H6+H7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="I10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(I6+I7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="J10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(J6+J7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="K10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(K6+K7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="L10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(L6+L7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="M10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(M6+M7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="N10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(N6+N7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
+      </c>
+      <c r="O10" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,(O6+O7)*②前提!$C$52,②前提!$C$7)</f>
+        <v>14701702.6</v>
       </c>
       <c r="P10" s="31" t="n">
         <f aca="false">SUM(D10:O10)</f>
-        <v>200601928</v>
+        <v>176420431.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="50" t="n">
-        <f aca="false">C7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <f aca="false">D7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <f aca="false">E7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <f aca="false">F7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <f aca="false">G7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <f aca="false">H7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <f aca="false">I7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <f aca="false">J7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <f aca="false">K7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <f aca="false">L7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <f aca="false">M7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <f aca="false">N7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <f aca="false">O7*②前提!$C$9</f>
-        <v>7608214.46418354</v>
+        <v>196</v>
+      </c>
+      <c r="C11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,C7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,D7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,E7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,F7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,G7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,H7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,I7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,J7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,K7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,L7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,M7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,N7*②前提!$C$9)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="51" t="n">
+        <f aca="false">IF(②前提!$C$30=3,0,O7*②前提!$C$9)</f>
+        <v>0</v>
       </c>
       <c r="P11" s="31" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>91298573.5702025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C12" s="50" t="n">
+        <v>197</v>
+      </c>
+      <c r="C12" s="51" t="n">
         <f aca="false">②前提!$C$13/12</f>
         <v>6666666.66666667</v>
       </c>
@@ -12049,9 +12699,9 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="50" t="n">
+        <v>198</v>
+      </c>
+      <c r="C13" s="51" t="n">
         <f aca="false">②前提!$C$14/12</f>
         <v>208333.333333333</v>
       </c>
@@ -12110,9 +12760,9 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C14" s="50" t="n">
+        <v>199</v>
+      </c>
+      <c r="C14" s="51" t="n">
         <f aca="false">②前提!$C$15/12</f>
         <v>833333.333333333</v>
       </c>
@@ -12171,7 +12821,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$25,②前提!$C$16,0)</f>
@@ -12228,7 +12878,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$26,②前提!$C$17,0)+IF(1=②前提!$C$27,②前提!$C$18,0)</f>
@@ -12284,90 +12934,90 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="11" t="n">
+      <c r="B17" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <f aca="false">C10+C11+SUM(C12:C14)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="D17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <f aca="false">D10+D11+SUM(D12:D16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="E17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <f aca="false">E10+E11+SUM(E12:E16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="F17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="F17" s="12" t="n">
         <f aca="false">F10+F11+SUM(F12:F16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="G17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <f aca="false">G10+G11+SUM(G12:G16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="H17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <f aca="false">H10+H11+SUM(H12:H16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="I17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="I17" s="12" t="n">
         <f aca="false">I10+I11+SUM(I12:I16)</f>
-        <v>62033375.1308502</v>
-      </c>
-      <c r="J17" s="11" t="n">
+        <v>52410035.9333333</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <f aca="false">J10+J11+SUM(J12:J16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="K17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <f aca="false">K10+K11+SUM(K12:K16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="L17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="L17" s="12" t="n">
         <f aca="false">L10+L11+SUM(L12:L16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="M17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <f aca="false">M10+M11+SUM(M12:M16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="N17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <f aca="false">N10+N11+SUM(N12:N16)</f>
-        <v>32033375.1308502</v>
-      </c>
-      <c r="O17" s="11" t="n">
+        <v>22410035.9333333</v>
+      </c>
+      <c r="O17" s="12" t="n">
         <f aca="false">O10+O11+SUM(O12:O16)</f>
-        <v>42033375.1308502</v>
-      </c>
-      <c r="P17" s="11" t="n">
+        <v>32410035.9333333</v>
+      </c>
+      <c r="P17" s="12" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>424400501.570202</v>
+        <v>308920431.2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
+        <v>202</v>
+      </c>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="50" t="n">
+        <v>68</v>
+      </c>
+      <c r="C20" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)</f>
         <v>2104000</v>
       </c>
@@ -12426,9 +13076,9 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="50" t="n">
+        <v>69</v>
+      </c>
+      <c r="C21" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I12:K12)</f>
         <v>2844602</v>
       </c>
@@ -12487,9 +13137,9 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="50" t="n">
+        <v>70</v>
+      </c>
+      <c r="C22" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I13:K13)</f>
         <v>198075</v>
       </c>
@@ -12548,9 +13198,9 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="50" t="n">
+        <v>71</v>
+      </c>
+      <c r="C23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>943189.333333333</v>
       </c>
@@ -12609,9 +13259,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="50" t="n">
+        <v>72</v>
+      </c>
+      <c r="C24" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I15:K15)</f>
         <v>520742.333333333</v>
       </c>
@@ -12670,9 +13320,9 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="50" t="n">
+        <v>73</v>
+      </c>
+      <c r="C25" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I16:K16)</f>
         <v>986309.666666667</v>
       </c>
@@ -12731,9 +13381,9 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="50" t="n">
+        <v>74</v>
+      </c>
+      <c r="C26" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I17:K17)</f>
         <v>3258950</v>
       </c>
@@ -12792,9 +13442,9 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="50" t="n">
+        <v>75</v>
+      </c>
+      <c r="C27" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I18:K18)</f>
         <v>3721702.66666667</v>
       </c>
@@ -12853,9 +13503,9 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="50" t="n">
+        <v>76</v>
+      </c>
+      <c r="C28" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I19:K19)</f>
         <v>400027.333333333</v>
       </c>
@@ -12914,9 +13564,9 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="50" t="n">
+        <v>77</v>
+      </c>
+      <c r="C29" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I20:K20)</f>
         <v>687496.333333333</v>
       </c>
@@ -12975,9 +13625,9 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="50" t="n">
+        <v>78</v>
+      </c>
+      <c r="C30" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I21:K21)</f>
         <v>154132.333333333</v>
       </c>
@@ -13036,9 +13686,9 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="50" t="n">
+        <v>79</v>
+      </c>
+      <c r="C31" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I22:K22)</f>
         <v>122950.333333333</v>
       </c>
@@ -13097,9 +13747,9 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="50" t="n">
+        <v>80</v>
+      </c>
+      <c r="C32" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I23:K23)</f>
         <v>0</v>
       </c>
@@ -13158,9 +13808,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="50" t="n">
+        <v>81</v>
+      </c>
+      <c r="C33" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I24:K24)</f>
         <v>246493.666666667</v>
       </c>
@@ -13219,9 +13869,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="50" t="n">
+        <v>82</v>
+      </c>
+      <c r="C34" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I25:K25)</f>
         <v>1213002</v>
       </c>
@@ -13280,9 +13930,9 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="50" t="n">
+        <v>83</v>
+      </c>
+      <c r="C35" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I26:K26)</f>
         <v>0</v>
       </c>
@@ -13341,9 +13991,9 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="50" t="n">
+        <v>84</v>
+      </c>
+      <c r="C36" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I27:K27)</f>
         <v>3250243.33333333</v>
       </c>
@@ -13402,9 +14052,9 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="50" t="n">
+        <v>85</v>
+      </c>
+      <c r="C37" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I28:K28)</f>
         <v>49855.6666666667</v>
       </c>
@@ -13463,9 +14113,9 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="50" t="n">
+        <v>86</v>
+      </c>
+      <c r="C38" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I29:K29)</f>
         <v>6666.66666666667</v>
       </c>
@@ -13524,9 +14174,9 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="50" t="n">
+        <v>87</v>
+      </c>
+      <c r="C39" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I30:K30)</f>
         <v>394626.666666667</v>
       </c>
@@ -13585,9 +14235,9 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="50" t="n">
+        <v>88</v>
+      </c>
+      <c r="C40" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I31:K31)</f>
         <v>0</v>
       </c>
@@ -13646,9 +14296,9 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="50" t="n">
+        <v>89</v>
+      </c>
+      <c r="C41" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I32:K32)</f>
         <v>3637873</v>
       </c>
@@ -13707,9 +14357,9 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="50" t="n">
+        <v>90</v>
+      </c>
+      <c r="C42" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I33:K33)</f>
         <v>272483.666666667</v>
       </c>
@@ -13767,149 +14417,149 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="11" t="n">
+      <c r="B43" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="12" t="n">
         <f aca="false">SUM(C20:C42)</f>
         <v>25013422</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="12" t="n">
         <f aca="false">SUM(D20:D42)</f>
         <v>25013422</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="12" t="n">
         <f aca="false">SUM(E20:E42)</f>
         <v>25013422</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="12" t="n">
         <f aca="false">SUM(F20:F42)</f>
         <v>25013422</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="12" t="n">
         <f aca="false">SUM(G20:G42)</f>
         <v>25013422</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H43" s="12" t="n">
         <f aca="false">SUM(H20:H42)</f>
         <v>25013422</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="12" t="n">
         <f aca="false">SUM(I20:I42)</f>
         <v>25013422</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="J43" s="12" t="n">
         <f aca="false">SUM(J20:J42)</f>
         <v>25013422</v>
       </c>
-      <c r="K43" s="11" t="n">
+      <c r="K43" s="12" t="n">
         <f aca="false">SUM(K20:K42)</f>
         <v>25013422</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="12" t="n">
         <f aca="false">SUM(L20:L42)</f>
         <v>25013422</v>
       </c>
-      <c r="M43" s="11" t="n">
+      <c r="M43" s="12" t="n">
         <f aca="false">SUM(M20:M42)</f>
         <v>25013422</v>
       </c>
-      <c r="N43" s="11" t="n">
+      <c r="N43" s="12" t="n">
         <f aca="false">SUM(N20:N42)</f>
         <v>25013422</v>
       </c>
-      <c r="O43" s="11" t="n">
+      <c r="O43" s="12" t="n">
         <f aca="false">SUM(O20:O42)</f>
         <v>25013422</v>
       </c>
-      <c r="P43" s="11" t="n">
+      <c r="P43" s="12" t="n">
         <f aca="false">SUM(D43:O43)</f>
         <v>300161064</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="49"/>
-      <c r="O45" s="49"/>
-      <c r="P45" s="49"/>
+        <v>203</v>
+      </c>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="50"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="50"/>
+      <c r="O45" s="50"/>
+      <c r="P45" s="50"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" s="11" t="n">
+      <c r="B46" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="12" t="n">
         <f aca="false">C17-C43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="D46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="D46" s="12" t="n">
         <f aca="false">D17-D43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="E46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <f aca="false">E17-E43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="F46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <f aca="false">F17-F43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="G46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <f aca="false">G17-G43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="H46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <f aca="false">H17-H43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="I46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="I46" s="12" t="n">
         <f aca="false">I17-I43</f>
-        <v>37019953.1308502</v>
-      </c>
-      <c r="J46" s="11" t="n">
+        <v>27396613.9333333</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <f aca="false">J17-J43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="K46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="K46" s="12" t="n">
         <f aca="false">K17-K43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="L46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="L46" s="12" t="n">
         <f aca="false">L17-L43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="M46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <f aca="false">M17-M43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="N46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="N46" s="12" t="n">
         <f aca="false">N17-N43</f>
-        <v>7019953.13085021</v>
-      </c>
-      <c r="O46" s="11" t="n">
+        <v>-2603386.06666667</v>
+      </c>
+      <c r="O46" s="12" t="n">
         <f aca="false">O17-O43</f>
-        <v>17019953.1308502</v>
-      </c>
-      <c r="P46" s="11" t="n">
+        <v>7396613.93333334</v>
+      </c>
+      <c r="P46" s="12" t="n">
         <f aca="false">SUM(D46:O46)</f>
-        <v>124239437.570202</v>
+        <v>8759367.2</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D47" s="8" t="n">
         <f aca="false">0</f>
@@ -13966,9 +14616,9 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" s="50" t="n">
+        <v>204</v>
+      </c>
+      <c r="C48" s="51" t="n">
         <f aca="false">②前提!$C$24/12</f>
         <v>1250000</v>
       </c>
@@ -14027,126 +14677,126 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C49" s="15" t="n">
         <f aca="false">C46+C47-C48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="D49" s="15" t="n">
         <f aca="false">D46+D47-D48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="E49" s="15" t="n">
         <f aca="false">E46+E47-E48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="F49" s="15" t="n">
         <f aca="false">F46+F47-F48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">G46+G47-G48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="H49" s="15" t="n">
         <f aca="false">H46+H47-H48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="I49" s="15" t="n">
         <f aca="false">I46+I47-I48</f>
-        <v>35769953.1308502</v>
+        <v>26146613.9333333</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">J46+J47-J48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="K49" s="15" t="n">
         <f aca="false">K46+K47-K48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="L49" s="15" t="n">
         <f aca="false">L46+L47-L48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="M49" s="15" t="n">
         <f aca="false">M46+M47-M48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="N49" s="15" t="n">
         <f aca="false">N46+N47-N48</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="O49" s="15" t="n">
         <f aca="false">O46+O47-O48</f>
-        <v>15769953.1308502</v>
+        <v>6146613.93333334</v>
       </c>
       <c r="P49" s="15" t="n">
         <f aca="false">SUM(D49:O49)</f>
-        <v>109239437.570202</v>
+        <v>-6240632.8</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="43" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="D50" s="48" t="n">
         <f aca="false">D49</f>
-        <v>5769953.13085021</v>
+        <v>-3853386.06666667</v>
       </c>
       <c r="E50" s="48" t="n">
         <f aca="false">D50+E49</f>
-        <v>11539906.2617004</v>
+        <v>-7706772.13333333</v>
       </c>
       <c r="F50" s="48" t="n">
         <f aca="false">E50+F49</f>
-        <v>17309859.3925506</v>
+        <v>-11560158.2</v>
       </c>
       <c r="G50" s="48" t="n">
         <f aca="false">F50+G49</f>
-        <v>23079812.5234008</v>
+        <v>-15413544.2666667</v>
       </c>
       <c r="H50" s="48" t="n">
         <f aca="false">G50+H49</f>
-        <v>28849765.654251</v>
+        <v>-19266930.3333333</v>
       </c>
       <c r="I50" s="48" t="n">
         <f aca="false">H50+I49</f>
-        <v>64619718.7851012</v>
+        <v>6879683.6</v>
       </c>
       <c r="J50" s="48" t="n">
         <f aca="false">I50+J49</f>
-        <v>70389671.9159515</v>
+        <v>3026297.53333333</v>
       </c>
       <c r="K50" s="48" t="n">
         <f aca="false">J50+K49</f>
-        <v>76159625.0468017</v>
+        <v>-827088.533333335</v>
       </c>
       <c r="L50" s="48" t="n">
         <f aca="false">K50+L49</f>
-        <v>81929578.1776519</v>
+        <v>-4680474.6</v>
       </c>
       <c r="M50" s="48" t="n">
         <f aca="false">L50+M49</f>
-        <v>87699531.3085021</v>
+        <v>-8533860.66666667</v>
       </c>
       <c r="N50" s="48" t="n">
         <f aca="false">M50+N49</f>
-        <v>93469484.4393523</v>
+        <v>-12387246.7333333</v>
       </c>
       <c r="O50" s="48" t="n">
         <f aca="false">N50+O49</f>
-        <v>109239437.570203</v>
+        <v>-6240632.8</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="3" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -14176,33 +14826,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="35" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="36" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="C5" s="52" t="n">
+      <c r="B5" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="53" t="n">
         <v>-114793431</v>
       </c>
       <c r="D5" s="31" t="n">
@@ -14210,12 +14860,12 @@
         <v>-114793431</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">②前提!$C$7*12-229139405</f>
@@ -14225,13 +14875,13 @@
         <f aca="false">D5+C6</f>
         <v>-143330908</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>198</v>
+      <c r="E6" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">343932836-②前提!$C$8*12</f>
@@ -14242,12 +14892,12 @@
         <v>-99559136</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">②前提!$C$20</f>
@@ -14258,40 +14908,40 @@
         <v>32940864</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="53" t="s">
-        <v>202</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="B9" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <f aca="false">D8</f>
         <v>32940864</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C13" s="21" t="n">
         <f aca="false">①サマリー!C23</f>
         <v>159183690.420246</v>
       </c>
-      <c r="E13" s="54" t="n">
+      <c r="E13" s="55" t="n">
         <f aca="false">①サマリー!D23</f>
         <v>0.149328039793852</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -14322,18 +14972,18 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="55" t="s">
-        <v>207</v>
+      <c r="B1" s="56" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="27" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="36" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
@@ -14344,71 +14994,71 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="56" t="n">
+        <v>234</v>
+      </c>
+      <c r="C6" s="57" t="n">
         <v>560</v>
       </c>
-      <c r="D6" s="56" t="n">
+      <c r="D6" s="57" t="n">
         <v>470</v>
       </c>
-      <c r="E6" s="56" t="n">
+      <c r="E6" s="57" t="n">
         <v>480</v>
       </c>
-      <c r="F6" s="56" t="n">
+      <c r="F6" s="57" t="n">
         <v>530</v>
       </c>
-      <c r="G6" s="56" t="n">
+      <c r="G6" s="57" t="n">
         <v>620</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="C7" s="57" t="n">
+      <c r="B7" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="58" t="n">
         <f aca="false">G6-E6</f>
         <v>140</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="58" t="n">
+        <v>236</v>
+      </c>
+      <c r="E7" s="59" t="n">
         <f aca="false">C7/6</f>
         <v>23.3333333333333</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="36" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="37"/>
@@ -14431,73 +15081,73 @@
         <v>3</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="K11" s="28" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M11" s="28" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="O11" s="28" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="P11" s="38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C12" s="42" t="n">
         <v>420000000</v>
       </c>
       <c r="Q12" s="40" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="13" t="s">
-        <v>226</v>
+      <c r="Q13" s="9" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>0</v>
@@ -14540,12 +15190,12 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>0</v>
@@ -14588,12 +15238,12 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">IF(②前提!$C$31=2,②前提!$C$32/12,D18)</f>
@@ -14648,58 +15298,58 @@
         <v>419066414</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="34" t="s">
-        <v>233</v>
-      </c>
-      <c r="D17" s="11" t="n">
+        <v>251</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <f aca="false">D16+$C$13+D14+D15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">E16+$C$13+E14+E15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <f aca="false">F16+$C$13+F14+F15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">G16+$C$13+G14+G15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <f aca="false">H16+$C$13+H14+H15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <f aca="false">I16+$C$13+I14+I15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">J16+$C$13+J14+J15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <f aca="false">K16+$C$13+K14+K15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <f aca="false">L16+$C$13+L14+L15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <f aca="false">M16+$C$13+M14+M15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <f aca="false">N16+$C$13+N14+N15</f>
         <v>34922201.1666667</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="12" t="n">
         <f aca="false">O16+$C$13+O14+O15</f>
         <v>34922201.1666667</v>
       </c>
@@ -14710,131 +15360,131 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D18" s="50" t="n">
+        <v>252</v>
+      </c>
+      <c r="D18" s="51" t="n">
         <f aca="false">③FY2027月次推移!D9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="E18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="E18" s="51" t="n">
         <f aca="false">③FY2027月次推移!E9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="F18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="F18" s="51" t="n">
         <f aca="false">③FY2027月次推移!F9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="G18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="G18" s="51" t="n">
         <f aca="false">③FY2027月次推移!G9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="H18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="H18" s="51" t="n">
         <f aca="false">③FY2027月次推移!H9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="I18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="I18" s="51" t="n">
         <f aca="false">③FY2027月次推移!I9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="J18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="J18" s="51" t="n">
         <f aca="false">③FY2027月次推移!J9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="K18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="K18" s="51" t="n">
         <f aca="false">③FY2027月次推移!K9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="L18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="L18" s="51" t="n">
         <f aca="false">③FY2027月次推移!L9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="M18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="M18" s="51" t="n">
         <f aca="false">③FY2027月次推移!M9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="N18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="N18" s="51" t="n">
         <f aca="false">③FY2027月次推移!N9</f>
-        <v>22862268.6191498</v>
-      </c>
-      <c r="O18" s="50" t="n">
+        <v>35134577.4</v>
+      </c>
+      <c r="O18" s="51" t="n">
         <f aca="false">③FY2027月次推移!O9</f>
-        <v>22862268.6191498</v>
+        <v>35134577.4</v>
       </c>
       <c r="P18" s="31" t="n">
         <f aca="false">SUM(D18:O18)</f>
-        <v>274347223.429798</v>
+        <v>421614928.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="D19" s="59" t="n">
+        <v>253</v>
+      </c>
+      <c r="D19" s="60" t="n">
         <f aca="false">$C$12+D17-D18</f>
-        <v>432059932.547517</v>
-      </c>
-      <c r="E19" s="59" t="n">
+        <v>419787623.766667</v>
+      </c>
+      <c r="E19" s="60" t="n">
         <f aca="false">D19+E17-E18</f>
-        <v>444119865.095034</v>
-      </c>
-      <c r="F19" s="59" t="n">
+        <v>419575247.533333</v>
+      </c>
+      <c r="F19" s="60" t="n">
         <f aca="false">E19+F17-F18</f>
-        <v>456179797.642551</v>
-      </c>
-      <c r="G19" s="59" t="n">
+        <v>419362871.3</v>
+      </c>
+      <c r="G19" s="60" t="n">
         <f aca="false">F19+G17-G18</f>
-        <v>468239730.190068</v>
-      </c>
-      <c r="H19" s="59" t="n">
+        <v>419150495.066667</v>
+      </c>
+      <c r="H19" s="60" t="n">
         <f aca="false">G19+H17-H18</f>
-        <v>480299662.737584</v>
-      </c>
-      <c r="I19" s="59" t="n">
+        <v>418938118.833334</v>
+      </c>
+      <c r="I19" s="60" t="n">
         <f aca="false">H19+I17-I18</f>
-        <v>492359595.285101</v>
-      </c>
-      <c r="J19" s="59" t="n">
+        <v>418725742.6</v>
+      </c>
+      <c r="J19" s="60" t="n">
         <f aca="false">I19+J17-J18</f>
-        <v>504419527.832618</v>
-      </c>
-      <c r="K19" s="59" t="n">
+        <v>418513366.366667</v>
+      </c>
+      <c r="K19" s="60" t="n">
         <f aca="false">J19+K17-K18</f>
-        <v>516479460.380135</v>
-      </c>
-      <c r="L19" s="59" t="n">
+        <v>418300990.133334</v>
+      </c>
+      <c r="L19" s="60" t="n">
         <f aca="false">K19+L17-L18</f>
-        <v>528539392.927652</v>
-      </c>
-      <c r="M19" s="59" t="n">
+        <v>418088613.9</v>
+      </c>
+      <c r="M19" s="60" t="n">
         <f aca="false">L19+M17-M18</f>
-        <v>540599325.475169</v>
-      </c>
-      <c r="N19" s="59" t="n">
+        <v>417876237.666667</v>
+      </c>
+      <c r="N19" s="60" t="n">
         <f aca="false">M19+N17-N18</f>
-        <v>552659258.022686</v>
-      </c>
-      <c r="O19" s="59" t="n">
+        <v>417663861.433334</v>
+      </c>
+      <c r="O19" s="60" t="n">
         <f aca="false">N19+O17-O18</f>
-        <v>564719190.570202</v>
-      </c>
-      <c r="P19" s="60" t="n">
+        <v>417451485.200001</v>
+      </c>
+      <c r="P19" s="61" t="n">
         <f aca="false">O19</f>
-        <v>564719190.570202</v>
+        <v>417451485.200001</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="27" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="27" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="40" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -14866,17 +15516,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="35" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="36" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
@@ -14896,69 +15546,69 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="C5" s="42" t="n">
         <v>30000000</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="61" t="n">
+        <v>143</v>
+      </c>
+      <c r="C6" s="62" t="n">
         <f aca="false">②前提!$C$36</f>
         <v>0.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C7" s="62" t="n">
+        <v>263</v>
+      </c>
+      <c r="C7" s="63" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="62" t="n">
+        <v>265</v>
+      </c>
+      <c r="C8" s="63" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C9" s="42" t="n">
         <v>2662179</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14966,173 +15616,173 @@
         <v>3</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="L12" s="28" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="O12" s="28" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="P12" s="38" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
+        <v>271</v>
+      </c>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="63" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14" s="50" t="n">
+      <c r="B14" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="D14" s="51" t="n">
         <f aca="false">③FY2027月次推移!D8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="E14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="E14" s="51" t="n">
         <f aca="false">③FY2027月次推移!E8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="F14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="F14" s="51" t="n">
         <f aca="false">③FY2027月次推移!F8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="G14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="G14" s="51" t="n">
         <f aca="false">③FY2027月次推移!G8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="H14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="H14" s="51" t="n">
         <f aca="false">③FY2027月次推移!H8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="I14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="I14" s="51" t="n">
         <f aca="false">③FY2027月次推移!I8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="J14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="J14" s="51" t="n">
         <f aca="false">③FY2027月次推移!J8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="K14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="K14" s="51" t="n">
         <f aca="false">③FY2027月次推移!K8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="L14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="L14" s="51" t="n">
         <f aca="false">③FY2027月次推移!L8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="M14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="M14" s="51" t="n">
         <f aca="false">③FY2027月次推移!M8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="N14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="N14" s="51" t="n">
         <f aca="false">③FY2027月次推移!N8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
-      </c>
-      <c r="O14" s="50" t="n">
+        <v>54819908</v>
+      </c>
+      <c r="O14" s="51" t="n">
         <f aca="false">③FY2027月次推移!O8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
+        <v>54819908</v>
       </c>
       <c r="P14" s="31" t="n">
         <f aca="false">SUM(D14:O14)</f>
-        <v>622872497.5</v>
+        <v>657838896</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="63" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15" s="50" t="n">
+      <c r="B15" s="64" t="s">
+        <v>273</v>
+      </c>
+      <c r="D15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!D12:D14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="E15" s="50" t="n">
+      <c r="E15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!E12:E14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="F15" s="50" t="n">
+      <c r="F15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!F12:F14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="G15" s="50" t="n">
+      <c r="G15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!G12:G14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="H15" s="50" t="n">
+      <c r="H15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!H12:H14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="I15" s="50" t="n">
+      <c r="I15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!I12:I14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="J15" s="50" t="n">
+      <c r="J15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!J12:J14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="K15" s="50" t="n">
+      <c r="K15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!K12:K14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="L15" s="50" t="n">
+      <c r="L15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!L12:L14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="M15" s="50" t="n">
+      <c r="M15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!M12:M14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="N15" s="50" t="n">
+      <c r="N15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!N12:N14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
-      <c r="O15" s="50" t="n">
+      <c r="O15" s="51" t="n">
         <f aca="false">SUM(③FY2027月次推移!O12:O14)*(1+$C$6)</f>
         <v>8479166.66666667</v>
       </c>
@@ -15142,54 +15792,54 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="64" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="50" t="n">
+      <c r="B16" s="65" t="s">
+        <v>274</v>
+      </c>
+      <c r="D16" s="51" t="n">
         <f aca="false">③FY2027月次推移!D15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="50" t="n">
+      <c r="E16" s="51" t="n">
         <f aca="false">③FY2027月次推移!E15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="50" t="n">
+      <c r="F16" s="51" t="n">
         <f aca="false">③FY2027月次推移!F15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="50" t="n">
+      <c r="G16" s="51" t="n">
         <f aca="false">③FY2027月次推移!G15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="50" t="n">
+      <c r="H16" s="51" t="n">
         <f aca="false">③FY2027月次推移!H15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="50" t="n">
+      <c r="I16" s="51" t="n">
         <f aca="false">③FY2027月次推移!I15*(1+$C$6)</f>
         <v>22000000</v>
       </c>
-      <c r="J16" s="50" t="n">
+      <c r="J16" s="51" t="n">
         <f aca="false">③FY2027月次推移!J15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="K16" s="50" t="n">
+      <c r="K16" s="51" t="n">
         <f aca="false">③FY2027月次推移!K15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="50" t="n">
+      <c r="L16" s="51" t="n">
         <f aca="false">③FY2027月次推移!L15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="M16" s="50" t="n">
+      <c r="M16" s="51" t="n">
         <f aca="false">③FY2027月次推移!M15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="50" t="n">
+      <c r="N16" s="51" t="n">
         <f aca="false">③FY2027月次推移!N15*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="50" t="n">
+      <c r="O16" s="51" t="n">
         <f aca="false">③FY2027月次推移!O15*(1+$C$6)</f>
         <v>0</v>
       </c>
@@ -15200,7 +15850,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D17" s="42" t="n">
         <v>0</v>
@@ -15243,58 +15893,58 @@
         <v>0</v>
       </c>
       <c r="Q17" s="40" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="63" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="50" t="n">
+      <c r="B18" s="64" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" s="51" t="n">
         <f aca="false">③FY2027月次推移!D16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="50" t="n">
+      <c r="E18" s="51" t="n">
         <f aca="false">③FY2027月次推移!E16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="50" t="n">
+      <c r="F18" s="51" t="n">
         <f aca="false">③FY2027月次推移!F16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="50" t="n">
+      <c r="G18" s="51" t="n">
         <f aca="false">③FY2027月次推移!G16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="50" t="n">
+      <c r="H18" s="51" t="n">
         <f aca="false">③FY2027月次推移!H16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="50" t="n">
+      <c r="I18" s="51" t="n">
         <f aca="false">③FY2027月次推移!I16*(1+$C$6)</f>
         <v>11000000</v>
       </c>
-      <c r="J18" s="50" t="n">
+      <c r="J18" s="51" t="n">
         <f aca="false">③FY2027月次推移!J16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="50" t="n">
+      <c r="K18" s="51" t="n">
         <f aca="false">③FY2027月次推移!K16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="50" t="n">
+      <c r="L18" s="51" t="n">
         <f aca="false">③FY2027月次推移!L16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="M18" s="50" t="n">
+      <c r="M18" s="51" t="n">
         <f aca="false">③FY2027月次推移!M16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="50" t="n">
+      <c r="N18" s="51" t="n">
         <f aca="false">③FY2027月次推移!N16*(1+$C$6)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="50" t="n">
+      <c r="O18" s="51" t="n">
         <f aca="false">③FY2027月次推移!O16*(1+$C$6)</f>
         <v>11000000</v>
       </c>
@@ -15303,134 +15953,134 @@
         <v>22000000</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="11" t="n">
+      <c r="B19" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <f aca="false">SUM(D14:D18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <f aca="false">SUM(E14:E18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="F19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="F19" s="12" t="n">
         <f aca="false">SUM(F14:F18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="G19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <f aca="false">SUM(G14:G18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="H19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <f aca="false">SUM(H14:H18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="I19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <f aca="false">SUM(I14:I18)</f>
-        <v>93385208.125</v>
-      </c>
-      <c r="J19" s="11" t="n">
+        <v>96299074.6666667</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <f aca="false">SUM(J14:J18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="K19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <f aca="false">SUM(K14:K18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="L19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <f aca="false">SUM(L14:L18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="M19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <f aca="false">SUM(M14:M18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="N19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="N19" s="12" t="n">
         <f aca="false">SUM(N14:N18)</f>
-        <v>60385208.125</v>
-      </c>
-      <c r="O19" s="11" t="n">
+        <v>63299074.6666667</v>
+      </c>
+      <c r="O19" s="12" t="n">
         <f aca="false">SUM(O14:O18)</f>
-        <v>71385208.125</v>
-      </c>
-      <c r="P19" s="11" t="n">
+        <v>74299074.6666667</v>
+      </c>
+      <c r="P19" s="12" t="n">
         <f aca="false">SUM(D19:O19)</f>
-        <v>768622497.5</v>
+        <v>803588896</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
+        <v>280</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="63" t="s">
-        <v>263</v>
-      </c>
-      <c r="D22" s="50" t="n">
+      <c r="B22" s="64" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="E22" s="50" t="n">
+      <c r="E22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="F22" s="50" t="n">
+      <c r="F22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!E17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="G22" s="50" t="n">
+      <c r="G22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!F17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="H22" s="50" t="n">
+      <c r="H22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!G17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="I22" s="50" t="n">
+      <c r="I22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!H17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="J22" s="50" t="n">
+      <c r="J22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!I17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="K22" s="50" t="n">
+      <c r="K22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!J17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="L22" s="50" t="n">
+      <c r="L22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!K17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="M22" s="50" t="n">
+      <c r="M22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!L17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="N22" s="50" t="n">
+      <c r="N22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!M17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
-      <c r="O22" s="50" t="n">
+      <c r="O22" s="51" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!N17*(1+$C$6)</f>
         <v>38414421.2833333</v>
       </c>
@@ -15440,54 +16090,54 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="63" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" s="50" t="n">
+      <c r="B23" s="64" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="E23" s="50" t="n">
+      <c r="E23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="F23" s="50" t="n">
+      <c r="F23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="G23" s="50" t="n">
+      <c r="G23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="H23" s="50" t="n">
+      <c r="H23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="I23" s="50" t="n">
+      <c r="I23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="J23" s="50" t="n">
+      <c r="J23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="K23" s="50" t="n">
+      <c r="K23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="L23" s="50" t="n">
+      <c r="L23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="M23" s="50" t="n">
+      <c r="M23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="N23" s="50" t="n">
+      <c r="N23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
-      <c r="O23" s="50" t="n">
+      <c r="O23" s="51" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
         <v>6089866.33333333</v>
       </c>
@@ -15497,54 +16147,54 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="63" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" s="50" t="n">
+      <c r="B24" s="64" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!D43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="E24" s="50" t="n">
+      <c r="E24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!E43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="F24" s="50" t="n">
+      <c r="F24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!F43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="G24" s="50" t="n">
+      <c r="G24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!G43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="H24" s="50" t="n">
+      <c r="H24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!H43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="I24" s="50" t="n">
+      <c r="I24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!I43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="J24" s="50" t="n">
+      <c r="J24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!J43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="K24" s="50" t="n">
+      <c r="K24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!K43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="L24" s="50" t="n">
+      <c r="L24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!L43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="M24" s="50" t="n">
+      <c r="M24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!M43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="N24" s="50" t="n">
+      <c r="N24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!N43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
-      <c r="O24" s="50" t="n">
+      <c r="O24" s="51" t="n">
         <f aca="false">((③FY2027月次推移!O43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
         <v>16762493.2333333</v>
       </c>
@@ -15554,54 +16204,54 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="63" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="50" t="n">
+      <c r="B25" s="64" t="s">
+        <v>284</v>
+      </c>
+      <c r="D25" s="51" t="n">
         <f aca="false">③FY2027月次推移!D48</f>
         <v>1250000</v>
       </c>
-      <c r="E25" s="50" t="n">
+      <c r="E25" s="51" t="n">
         <f aca="false">③FY2027月次推移!E48</f>
         <v>1250000</v>
       </c>
-      <c r="F25" s="50" t="n">
+      <c r="F25" s="51" t="n">
         <f aca="false">③FY2027月次推移!F48</f>
         <v>1250000</v>
       </c>
-      <c r="G25" s="50" t="n">
+      <c r="G25" s="51" t="n">
         <f aca="false">③FY2027月次推移!G48</f>
         <v>1250000</v>
       </c>
-      <c r="H25" s="50" t="n">
+      <c r="H25" s="51" t="n">
         <f aca="false">③FY2027月次推移!H48</f>
         <v>1250000</v>
       </c>
-      <c r="I25" s="50" t="n">
+      <c r="I25" s="51" t="n">
         <f aca="false">③FY2027月次推移!I48</f>
         <v>1250000</v>
       </c>
-      <c r="J25" s="50" t="n">
+      <c r="J25" s="51" t="n">
         <f aca="false">③FY2027月次推移!J48</f>
         <v>1250000</v>
       </c>
-      <c r="K25" s="50" t="n">
+      <c r="K25" s="51" t="n">
         <f aca="false">③FY2027月次推移!K48</f>
         <v>1250000</v>
       </c>
-      <c r="L25" s="50" t="n">
+      <c r="L25" s="51" t="n">
         <f aca="false">③FY2027月次推移!L48</f>
         <v>1250000</v>
       </c>
-      <c r="M25" s="50" t="n">
+      <c r="M25" s="51" t="n">
         <f aca="false">③FY2027月次推移!M48</f>
         <v>1250000</v>
       </c>
-      <c r="N25" s="50" t="n">
+      <c r="N25" s="51" t="n">
         <f aca="false">③FY2027月次推移!N48</f>
         <v>1250000</v>
       </c>
-      <c r="O25" s="50" t="n">
+      <c r="O25" s="51" t="n">
         <f aca="false">③FY2027月次推移!O48</f>
         <v>1250000</v>
       </c>
@@ -15611,47 +16261,47 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="63" t="s">
-        <v>267</v>
-      </c>
-      <c r="D26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="50" t="n">
+      <c r="B26" s="64" t="s">
+        <v>285</v>
+      </c>
+      <c r="D26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="51" t="n">
         <f aca="false">②前提!$C$44</f>
         <v>3554509.09999999</v>
       </c>
-      <c r="F26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="50" t="n">
+      <c r="F26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="51" t="n">
         <f aca="false">②前提!$C$45</f>
         <v>2013627.275</v>
       </c>
-      <c r="I26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="50" t="n">
+      <c r="I26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="51" t="n">
         <f aca="false">②前提!$C$45</f>
         <v>2013627.275</v>
       </c>
-      <c r="L26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="50" t="n">
+      <c r="L26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="51" t="n">
         <f aca="false">②前提!$C$45</f>
         <v>2013627.275</v>
       </c>
-      <c r="O26" s="50" t="n">
+      <c r="O26" s="51" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="31" t="n">
@@ -15659,12 +16309,12 @@
         <v>9595390.92499999</v>
       </c>
       <c r="Q26" s="27" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="D27" s="42" t="n">
         <v>0</v>
@@ -15708,187 +16358,187 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="D28" s="11" t="n">
+      <c r="B28" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <f aca="false">SUM(D22:D27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">SUM(E22:E27)</f>
         <v>66534394.95</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <f aca="false">SUM(F22:F27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="12" t="n">
         <f aca="false">SUM(G22:G27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H28" s="12" t="n">
         <f aca="false">SUM(H22:H27)</f>
         <v>64530408.125</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <f aca="false">SUM(I22:I27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <f aca="false">SUM(J22:J27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <f aca="false">SUM(K22:K27)</f>
         <v>64530408.125</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <f aca="false">SUM(L22:L27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="M28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <f aca="false">SUM(M22:M27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="N28" s="11" t="n">
+      <c r="N28" s="12" t="n">
         <f aca="false">SUM(N22:N27)</f>
         <v>64530408.125</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" s="12" t="n">
         <f aca="false">SUM(O22:O27)</f>
         <v>62516780.85</v>
       </c>
-      <c r="P28" s="11" t="n">
+      <c r="P28" s="12" t="n">
         <f aca="false">SUM(D28:O28)</f>
         <v>760259866.125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="D29" s="11" t="n">
+      <c r="B29" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D29" s="12" t="n">
         <f aca="false">D19-D28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="E29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="E29" s="12" t="n">
         <f aca="false">E19-E28</f>
-        <v>-6149186.82499998</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>-3235320.28333332</v>
+      </c>
+      <c r="F29" s="12" t="n">
         <f aca="false">F19-F28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="G29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="G29" s="12" t="n">
         <f aca="false">G19-G28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="H29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <f aca="false">H19-H28</f>
-        <v>-4145199.99999999</v>
-      </c>
-      <c r="I29" s="11" t="n">
+        <v>-1231333.45833333</v>
+      </c>
+      <c r="I29" s="12" t="n">
         <f aca="false">I19-I28</f>
-        <v>30868427.275</v>
-      </c>
-      <c r="J29" s="11" t="n">
+        <v>33782293.8166667</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <f aca="false">J19-J28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="K29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <f aca="false">K19-K28</f>
-        <v>-4145199.99999999</v>
-      </c>
-      <c r="L29" s="11" t="n">
+        <v>-1231333.45833333</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <f aca="false">L19-L28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="M29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <f aca="false">M19-M28</f>
-        <v>-2131572.72499999</v>
-      </c>
-      <c r="N29" s="11" t="n">
+        <v>782293.81666667</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <f aca="false">N19-N28</f>
-        <v>-4145199.99999999</v>
-      </c>
-      <c r="O29" s="11" t="n">
+        <v>-1231333.45833333</v>
+      </c>
+      <c r="O29" s="12" t="n">
         <f aca="false">O19-O28</f>
-        <v>8868427.27500001</v>
-      </c>
-      <c r="P29" s="11" t="n">
+        <v>11782293.8166667</v>
+      </c>
+      <c r="P29" s="12" t="n">
         <f aca="false">SUM(D29:O29)</f>
-        <v>8362631.37500017</v>
+        <v>43329029.8750001</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="P31" s="49"/>
+        <v>290</v>
+      </c>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="D32" s="50" t="n">
+      <c r="B32" s="64" t="s">
+        <v>291</v>
+      </c>
+      <c r="D32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="E32" s="50" t="n">
+      <c r="E32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="F32" s="50" t="n">
+      <c r="F32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="G32" s="50" t="n">
+      <c r="G32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="H32" s="50" t="n">
+      <c r="H32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="I32" s="50" t="n">
+      <c r="I32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="J32" s="50" t="n">
+      <c r="J32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="K32" s="50" t="n">
+      <c r="K32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="L32" s="50" t="n">
+      <c r="L32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="M32" s="50" t="n">
+      <c r="M32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="N32" s="50" t="n">
+      <c r="N32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
-      <c r="O32" s="50" t="n">
+      <c r="O32" s="51" t="n">
         <f aca="false">-$C$9</f>
         <v>-2662179</v>
       </c>
@@ -15898,54 +16548,54 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="63" t="s">
-        <v>274</v>
-      </c>
-      <c r="D33" s="50" t="n">
+      <c r="B33" s="64" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="E33" s="50" t="n">
+      <c r="E33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="F33" s="50" t="n">
+      <c r="F33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="G33" s="50" t="n">
+      <c r="G33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="H33" s="50" t="n">
+      <c r="H33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="I33" s="50" t="n">
+      <c r="I33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="J33" s="50" t="n">
+      <c r="J33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="K33" s="50" t="n">
+      <c r="K33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="L33" s="50" t="n">
+      <c r="L33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="M33" s="50" t="n">
+      <c r="M33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="N33" s="50" t="n">
+      <c r="N33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
-      <c r="O33" s="50" t="n">
+      <c r="O33" s="51" t="n">
         <f aca="false">$C$10</f>
         <v>0</v>
       </c>
@@ -15956,7 +16606,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D34" s="42" t="n">
         <v>0</v>
@@ -16001,7 +16651,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="D35" s="42" t="n">
         <v>0</v>
@@ -16044,126 +16694,126 @@
         <v>0</v>
       </c>
       <c r="Q35" s="40" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="D36" s="11" t="n">
+      <c r="B36" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <f aca="false">SUM(D32:D35)</f>
         <v>-2662179</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="12" t="n">
         <f aca="false">SUM(E32:E35)</f>
         <v>-2662179</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="12" t="n">
         <f aca="false">SUM(F32:F35)</f>
         <v>-2662179</v>
       </c>
-      <c r="G36" s="11" t="n">
+      <c r="G36" s="12" t="n">
         <f aca="false">SUM(G32:G35)</f>
         <v>-2662179</v>
       </c>
-      <c r="H36" s="11" t="n">
+      <c r="H36" s="12" t="n">
         <f aca="false">SUM(H32:H35)</f>
         <v>-2662179</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="I36" s="12" t="n">
         <f aca="false">SUM(I32:I35)</f>
         <v>-2662179</v>
       </c>
-      <c r="J36" s="11" t="n">
+      <c r="J36" s="12" t="n">
         <f aca="false">SUM(J32:J35)</f>
         <v>-2662179</v>
       </c>
-      <c r="K36" s="11" t="n">
+      <c r="K36" s="12" t="n">
         <f aca="false">SUM(K32:K35)</f>
         <v>-2662179</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" s="12" t="n">
         <f aca="false">SUM(L32:L35)</f>
         <v>-2662179</v>
       </c>
-      <c r="M36" s="11" t="n">
+      <c r="M36" s="12" t="n">
         <f aca="false">SUM(M32:M35)</f>
         <v>-2662179</v>
       </c>
-      <c r="N36" s="11" t="n">
+      <c r="N36" s="12" t="n">
         <f aca="false">SUM(N32:N35)</f>
         <v>-2662179</v>
       </c>
-      <c r="O36" s="11" t="n">
+      <c r="O36" s="12" t="n">
         <f aca="false">SUM(O32:O35)</f>
         <v>-2662179</v>
       </c>
-      <c r="P36" s="11" t="n">
+      <c r="P36" s="12" t="n">
         <f aca="false">SUM(D36:O36)</f>
         <v>-31946148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="D38" s="11" t="n">
+      <c r="B38" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <f aca="false">D29+D36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="E38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="E38" s="12" t="n">
         <f aca="false">E29+E36</f>
-        <v>-8811365.82499998</v>
-      </c>
-      <c r="F38" s="11" t="n">
+        <v>-5897499.28333332</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <f aca="false">F29+F36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="G38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <f aca="false">G29+G36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="H38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <f aca="false">H29+H36</f>
-        <v>-6807378.99999999</v>
-      </c>
-      <c r="I38" s="11" t="n">
+        <v>-3893512.45833333</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <f aca="false">I29+I36</f>
-        <v>28206248.275</v>
-      </c>
-      <c r="J38" s="11" t="n">
+        <v>31120114.8166667</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <f aca="false">J29+J36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="K38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <f aca="false">K29+K36</f>
-        <v>-6807378.99999999</v>
-      </c>
-      <c r="L38" s="11" t="n">
+        <v>-3893512.45833333</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <f aca="false">L29+L36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="M38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <f aca="false">M29+M36</f>
-        <v>-4793751.72499999</v>
-      </c>
-      <c r="N38" s="11" t="n">
+        <v>-1879885.18333333</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <f aca="false">N29+N36</f>
-        <v>-6807378.99999999</v>
-      </c>
-      <c r="O38" s="11" t="n">
+        <v>-3893512.45833333</v>
+      </c>
+      <c r="O38" s="12" t="n">
         <f aca="false">O29+O36</f>
-        <v>6206248.27500001</v>
-      </c>
-      <c r="P38" s="11" t="n">
+        <v>9120114.81666667</v>
+      </c>
+      <c r="P38" s="12" t="n">
         <f aca="false">SUM(D38:O38)</f>
-        <v>-23583516.6249998</v>
+        <v>11382881.8750001</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D39" s="8" t="n">
         <f aca="false">$C$5</f>
@@ -16171,194 +16821,194 @@
       </c>
       <c r="E39" s="8" t="n">
         <f aca="false">D40</f>
-        <v>25206248.275</v>
+        <v>28120114.8166667</v>
       </c>
       <c r="F39" s="8" t="n">
         <f aca="false">E40</f>
-        <v>16394882.45</v>
+        <v>22222615.5333333</v>
       </c>
       <c r="G39" s="8" t="n">
         <f aca="false">F40</f>
-        <v>11601130.725</v>
+        <v>20342730.35</v>
       </c>
       <c r="H39" s="8" t="n">
         <f aca="false">G40</f>
-        <v>6807379.00000006</v>
+        <v>18462845.1666667</v>
       </c>
       <c r="I39" s="8" t="n">
         <f aca="false">H40</f>
-        <v>7.45058059692383E-008</v>
+        <v>14569332.7083334</v>
       </c>
       <c r="J39" s="8" t="n">
         <f aca="false">I40</f>
-        <v>28206248.2750001</v>
+        <v>45689447.525</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">J40</f>
-        <v>23412496.5500001</v>
+        <v>43809562.3416667</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">K40</f>
-        <v>16605117.5500001</v>
+        <v>39916049.8833334</v>
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">L40</f>
-        <v>11811365.8250001</v>
+        <v>38036164.7</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">M40</f>
-        <v>7017614.10000014</v>
+        <v>36156279.5166667</v>
       </c>
       <c r="O39" s="8" t="n">
         <f aca="false">N40</f>
-        <v>210235.100000158</v>
+        <v>32262767.0583334</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="14" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D40" s="15" t="n">
         <f aca="false">D39+D38</f>
-        <v>25206248.275</v>
+        <v>28120114.8166667</v>
       </c>
       <c r="E40" s="15" t="n">
         <f aca="false">E39+E38</f>
-        <v>16394882.45</v>
+        <v>22222615.5333333</v>
       </c>
       <c r="F40" s="15" t="n">
         <f aca="false">F39+F38</f>
-        <v>11601130.725</v>
+        <v>20342730.35</v>
       </c>
       <c r="G40" s="15" t="n">
         <f aca="false">G39+G38</f>
-        <v>6807379.00000006</v>
+        <v>18462845.1666667</v>
       </c>
       <c r="H40" s="15" t="n">
         <f aca="false">H39+H38</f>
-        <v>7.45058059692383E-008</v>
+        <v>14569332.7083334</v>
       </c>
       <c r="I40" s="15" t="n">
         <f aca="false">I39+I38</f>
-        <v>28206248.2750001</v>
+        <v>45689447.525</v>
       </c>
       <c r="J40" s="15" t="n">
         <f aca="false">J39+J38</f>
-        <v>23412496.5500001</v>
+        <v>43809562.3416667</v>
       </c>
       <c r="K40" s="15" t="n">
         <f aca="false">K39+K38</f>
-        <v>16605117.5500001</v>
+        <v>39916049.8833334</v>
       </c>
       <c r="L40" s="15" t="n">
         <f aca="false">L39+L38</f>
-        <v>11811365.8250001</v>
+        <v>38036164.7</v>
       </c>
       <c r="M40" s="15" t="n">
         <f aca="false">M39+M38</f>
-        <v>7017614.10000014</v>
+        <v>36156279.5166667</v>
       </c>
       <c r="N40" s="15" t="n">
         <f aca="false">N39+N38</f>
-        <v>210235.100000158</v>
+        <v>32262767.0583334</v>
       </c>
       <c r="O40" s="15" t="n">
         <f aca="false">O39+O38</f>
-        <v>6416483.37500017</v>
+        <v>41382881.8750001</v>
       </c>
       <c r="P40" s="48" t="n">
         <f aca="false">O40</f>
-        <v>6416483.37500017</v>
+        <v>41382881.8750001</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="65" t="s">
-        <v>282</v>
-      </c>
-      <c r="D41" s="66" t="n">
+      <c r="B41" s="66" t="s">
+        <v>300</v>
+      </c>
+      <c r="D41" s="67" t="n">
         <f aca="false">IF(D40&lt;0,D40,0)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="66" t="n">
+      <c r="E41" s="67" t="n">
         <f aca="false">IF(E40&lt;0,E40,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="66" t="n">
+      <c r="F41" s="67" t="n">
         <f aca="false">IF(F40&lt;0,F40,0)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="66" t="n">
+      <c r="G41" s="67" t="n">
         <f aca="false">IF(G40&lt;0,G40,0)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="66" t="n">
+      <c r="H41" s="67" t="n">
         <f aca="false">IF(H40&lt;0,H40,0)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="66" t="n">
+      <c r="I41" s="67" t="n">
         <f aca="false">IF(I40&lt;0,I40,0)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="66" t="n">
+      <c r="J41" s="67" t="n">
         <f aca="false">IF(J40&lt;0,J40,0)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="66" t="n">
+      <c r="K41" s="67" t="n">
         <f aca="false">IF(K40&lt;0,K40,0)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="66" t="n">
+      <c r="L41" s="67" t="n">
         <f aca="false">IF(L40&lt;0,L40,0)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="66" t="n">
+      <c r="M41" s="67" t="n">
         <f aca="false">IF(M40&lt;0,M40,0)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="66" t="n">
+      <c r="N41" s="67" t="n">
         <f aca="false">IF(N40&lt;0,N40,0)</f>
         <v>0</v>
       </c>
-      <c r="O41" s="66" t="n">
+      <c r="O41" s="67" t="n">
         <f aca="false">IF(O40&lt;0,O40,0)</f>
         <v>0</v>
       </c>
-      <c r="P41" s="66" t="n">
+      <c r="P41" s="67" t="n">
         <f aca="false">MIN(D41:O41)</f>
         <v>0</v>
       </c>
       <c r="Q41" s="27" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="27" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="27" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="36" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C49" s="37"/>
       <c r="D49" s="37"/>
@@ -16378,126 +17028,126 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="18" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="F50" s="18" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="51" t="s">
-        <v>295</v>
+      <c r="B51" s="52" t="s">
+        <v>313</v>
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">O40</f>
-        <v>6416483.37500017</v>
+        <v>41382881.8750001</v>
       </c>
       <c r="D51" s="31" t="n">
         <f aca="false">MIN(D40:O40)</f>
-        <v>7.45058059692383E-008</v>
+        <v>14569332.7083334</v>
       </c>
       <c r="E51" s="21" t="n">
         <f aca="false">IF(C51&lt;0,-MIN(C51,D51)+$C$55,MAX(0,-D51+$C$55))</f>
-        <v>51906041.4583333</v>
+        <v>40250575.2916667</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="C52" s="66" t="n">
+        <v>315</v>
+      </c>
+      <c r="C52" s="67" t="n">
         <f aca="false">C51+(②前提!$C$32-③FY2027月次推移!$P$9)*(1+$C$6)</f>
-        <v>165607593.002223</v>
-      </c>
-      <c r="D52" s="66" t="n">
+        <v>38579515.5950001</v>
+      </c>
+      <c r="D52" s="67" t="n">
         <f aca="false">D51+(②前提!$C$32-③FY2027月次推移!$P$9)*(1+$C$6)</f>
-        <v>159191109.627223</v>
+        <v>11765966.4283334</v>
       </c>
       <c r="E52" s="21" t="n">
         <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$55,MAX(0,-D52+$C$55))</f>
-        <v>0</v>
+        <v>43053941.5716666</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="C53" s="66" t="n">
+        <v>317</v>
+      </c>
+      <c r="C53" s="67" t="n">
         <f aca="false">C51-(P16+P18)</f>
-        <v>-37583516.6249998</v>
-      </c>
-      <c r="D53" s="66" t="n">
+        <v>-2617118.12499995</v>
+      </c>
+      <c r="D53" s="67" t="n">
         <f aca="false">D51-(P16+P18)</f>
-        <v>-43999999.9999999</v>
+        <v>-29430667.2916666</v>
       </c>
       <c r="E53" s="21" t="n">
         <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$55,MAX(0,-D53+$C$55))</f>
-        <v>95906041.4583333</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>300</v>
+        <v>84250575.2916667</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="20" t="s">
-        <v>301</v>
-      </c>
-      <c r="C54" s="66" t="n">
+        <v>319</v>
+      </c>
+      <c r="C54" s="67" t="n">
         <f aca="false">C51-①サマリー!$C$24*(1+$C$6)</f>
-        <v>-188401169.325</v>
-      </c>
-      <c r="D54" s="66" t="n">
+        <v>-153434770.825</v>
+      </c>
+      <c r="D54" s="67" t="n">
         <f aca="false">D51-①サマリー!$C$24*(1+$C$6)</f>
-        <v>-194817652.7</v>
+        <v>-180248319.991667</v>
       </c>
       <c r="E54" s="21" t="n">
         <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$55,MAX(0,-D54+$C$55))</f>
-        <v>246723694.158333</v>
+        <v>235068227.991667</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="C55" s="50" t="n">
+        <v>321</v>
+      </c>
+      <c r="C55" s="51" t="n">
         <f aca="false">③FY2027月次推移!$C$8*(1+$C$6)</f>
-        <v>51906041.4583333</v>
+        <v>54819908</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="27" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="27" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="36" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C79" s="37"/>
       <c r="D79" s="37"/>
@@ -16517,30 +17167,30 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="6" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C80" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="13" t="s">
-        <v>309</v>
+      <c r="F80" s="9" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="6" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C81" s="31" t="n">
         <f aca="false">②前提!$C$6*(1+$C$6)+SUM(②前提!$C$13:$C$15)/12*(1+$C$6)-②前提!$C$32/12*(1+$C$6)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(((②前提!$C$8-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))-②前提!$C$24/12-$C$9</f>
         <v>-21028556.1166667</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="18" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D83" s="38" t="n">
         <v>1</v>
@@ -16580,46 +17230,46 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D84" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="E84" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="F84" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="G84" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="H84" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="I84" s="67" t="s">
-        <v>165</v>
-      </c>
-      <c r="J84" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="K84" s="67" t="s">
-        <v>167</v>
-      </c>
-      <c r="L84" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="M84" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="N84" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="O84" s="67" t="s">
-        <v>171</v>
+      <c r="D84" s="68" t="s">
+        <v>178</v>
+      </c>
+      <c r="E84" s="68" t="s">
+        <v>179</v>
+      </c>
+      <c r="F84" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="G84" s="68" t="s">
+        <v>181</v>
+      </c>
+      <c r="H84" s="68" t="s">
+        <v>182</v>
+      </c>
+      <c r="I84" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="J84" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="K84" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="L84" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="M84" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="N84" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="O84" s="68" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="6" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D85" s="8" t="n">
         <f aca="false">$C$5+D$83*$C$81+(SUM($D$16:D16)+SUM($D$18:D18))-(SUM($D$26:D26)+SUM($D$27:D27))</f>
@@ -16672,7 +17322,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="6" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="D86" s="8" t="n">
         <f aca="false">MAX(0,($C$80-D85)*12/((1+$C$6)*D$83))</f>
@@ -16725,7 +17375,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="43" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C88" s="21" t="n">
         <f aca="false">MAX(D86:O86)</f>
@@ -16734,7 +17384,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="43" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C89" s="21" t="n">
         <f aca="false">②前提!$C$6*12+C88</f>
@@ -16743,29 +17393,29 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="6" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C90" s="43" t="str">
         <f aca="false">INDEX(D84:O84,MATCH(C88,D86:O86,0))</f>
         <v>2027/02</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="27" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="27" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="27" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/out/WineBank_FY2027_forecast.xlsx
+++ b/out/WineBank_FY2027_forecast.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="340">
   <si>
     <r>
       <rPr>
@@ -230,8 +230,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">再編後実力値
-横ばいのみ</t>
+      <t xml:space="preserve">横ばいのみ</t>
     </r>
   </si>
   <si>
@@ -289,7 +288,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C. B</t>
+      <t xml:space="preserve">C. </t>
     </r>
     <r>
       <rPr>
@@ -299,9 +298,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＋差額売上
-（粗利率</t>
-    </r>
+      <t xml:space="preserve">上乗せを
+売上平均の内数</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -311,24 +312,173 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">D. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上乗せを
+売上平均に外数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">コメント</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既存事業 売上</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円は前期・今期の平均そのもの</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">売上総利益（既存事業）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差額売上の粗利率は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">30%</t>
     </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">コメント</t>
-  </si>
-  <si>
-    <t xml:space="preserve">既存事業 売上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＋上乗せ案件（営業収益）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">経営指導料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M&amp;A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仲介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋新規事業利益</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">売上高（上乗せ含む）</t>
   </si>
   <si>
     <r>
@@ -348,204 +498,59 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">は差額売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">208.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を上積み</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">売上総利益（既存事業）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は差額売上の粗利</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">62.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円（粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を加算</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">＋上乗せ案件（営業収益）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">経営指導料</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">M&amp;A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仲介</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋新規事業利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
+      <t xml:space="preserve">は内数のため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は外数のため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">863.0</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">売上総利益 合計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の総合粗利率は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">54.2%</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">販管費</t>
@@ -640,7 +645,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【プラン</t>
+      <t xml:space="preserve">【差額売上（</t>
     </r>
     <r>
       <rPr>
@@ -650,7 +655,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C</t>
+      <t xml:space="preserve">B</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +664,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の差額売上】</t>
+      <t xml:space="preserve">プランからの上積み）】</t>
     </r>
   </si>
   <si>
@@ -704,19 +709,540 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せを内数とした場合の差額売上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せを外数とした場合の差額売上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【判定】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：再編後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">99.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益▲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">114.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">B</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プランからの差額売上（粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せ案件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">132.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を計上すると営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。契約ベースの下限。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せを売上平均の内数とした場合。売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">95.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：上乗せを外数として加算した場合。売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">863.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・営業利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">135.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円・経常利益＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">120.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は「何もしなくても」到達する下限。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が目指すべき最低限の姿。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※既存事業売上は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">598.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（過去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期平均の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">81.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　　過去</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期の売上実績に照らすと、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のレンジが最も蓋然性が高い。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※差額売上の粗利率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="メイリオ"/>
         <family val="0"/>
         <charset val="1"/>
@@ -725,529 +1251,79 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で加算）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【判定】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：再編後の実力値を横ばいで延ばすだけでは営業利益▲</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025 26.8%</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">99.6</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・経常利益▲</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 32.4%</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">114.6</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の実績水準。</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円。</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-6</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月実績の</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：上乗せ案件</t>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">51.5%</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を全額営業収益に計上すると営業利益＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・経常利益＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円で黒字化する。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（本線）：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に、前期・今期の売上平均</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">730.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円までの差額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">208.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円を粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で加算。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　　売上高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">730.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・営業利益＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">95.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円・経常利益＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※差額売上の粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は、既存事業の実績（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2025 26.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 32.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を踏まえた保守値。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4-6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月実績の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">51.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は用いていない。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※差額売上</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">208.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円は新規顧客売上計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,066</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">19.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※上乗せ案件のうち</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円はグループ内取引（中野出資</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Apicius</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">グループ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は用いない。</t>
     </r>
   </si>
   <si>
@@ -2948,15 +3024,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上乗せのみ／</t>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
     </r>
     <r>
       <rPr>
@@ -2982,15 +3058,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">差額売上を加算）</t>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -3897,6 +4007,27 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">の前提　</t>
     </r>
     <r>
@@ -3918,7 +4049,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">プランに、前期・今期の売上平均までの差額売上を粗利率</t>
+      <t xml:space="preserve">に、前期・今期の売上平均までの差額売上を粗利率</t>
     </r>
     <r>
       <rPr>
@@ -4024,6 +4155,112 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">上乗せ案件（経営指導料等）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">差額売上の粗利率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">既存事業の実績（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2025 26.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 32.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を踏まえ保守的に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】上乗せ案件を売上平均の内数とする</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　既存事業 売上</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　差額売上（</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -4039,218 +4276,157 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">プランの売上高（上乗せ含む）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">既存事業</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">389,140,768</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋上乗せ案件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132,500,000</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差額売上</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前期・今期の平均−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">プランの売上高</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差額売上の粗利率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">既存事業の実績（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2025 26.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 32.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）を踏まえ保守的に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">差額売上の粗利</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">既存</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">200.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋差額分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">62.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＋上乗せ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">132.5</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">総合粗利率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※差額売上</t>
+      <t xml:space="preserve">プランからの上積み）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　差額売上の粗利</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　売上総利益 合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　売上高（上乗せ含む）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　総合粗利率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">】上乗せ案件を売上平均に外数で加算する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">※C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は上乗せ案件を売上平均の内数、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は外数として扱う。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の既存事業売上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">730.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円は前期・今期の平均そのもの。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※差額売上は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が</t>
     </r>
     <r>
       <rPr>
@@ -4269,26 +4445,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円は新規顧客売上計画</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,066</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円の</t>
+      <t xml:space="preserve">百万円（新規顧客計画の</t>
     </r>
     <r>
       <rPr>
@@ -4307,64 +4464,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。既存事業の粗利率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">51.5%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4-6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月実績）ではなく</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF333333"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">で置くことで保守性を確保。</t>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">341.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円（同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
     </r>
   </si>
   <si>
@@ -4499,7 +4656,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（経常利益</t>
+      <t xml:space="preserve">（内数）／</t>
     </r>
     <r>
       <rPr>
@@ -4509,7 +4666,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">D</t>
     </r>
     <r>
       <rPr>
@@ -4518,7 +4675,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">億円）を切替</t>
+      <t xml:space="preserve">（外数）を切替</t>
     </r>
   </si>
   <si>
@@ -5220,6 +5377,36 @@
   <si>
     <r>
       <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の差額売上】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="メイリオ"/>
         <family val="0"/>
@@ -6211,35 +6398,16 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（経常利益</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">億円）／ワイン仕入</t>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（②前提の「シナリオ選択」に連動）／ワイン仕入</t>
     </r>
     <r>
       <rPr>
@@ -8599,11 +8767,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8888,40 +9056,40 @@
                 <c:formatCode>\¥#,##0;"(¥"#,##0\);\-</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>28120114.8166667</c:v>
+                  <c:v>40265948.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22222615.5333333</c:v>
+                  <c:v>46514282.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20342730.35</c:v>
+                  <c:v>56780230.35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18462845.1666667</c:v>
+                  <c:v>67046178.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14569332.7083334</c:v>
+                  <c:v>75298499.375</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45689447.525</c:v>
+                  <c:v>118564447.525</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43809562.3416667</c:v>
+                  <c:v>128830395.675</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>39916049.8833334</c:v>
+                  <c:v>137082716.55</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>38036164.7</c:v>
+                  <c:v>147348664.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>36156279.5166667</c:v>
+                  <c:v>157614612.85</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>32262767.0583334</c:v>
+                  <c:v>165866933.725</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>41382881.8750001</c:v>
+                  <c:v>187132881.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8936,11 +9104,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="92532992"/>
-        <c:axId val="9054212"/>
+        <c:axId val="46766280"/>
+        <c:axId val="68505770"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="92532992"/>
+        <c:axId val="46766280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8972,7 +9140,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9054212"/>
+        <c:crossAx val="68505770"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8980,7 +9148,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9054212"/>
+        <c:axId val="68505770"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9056,7 +9224,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92532992"/>
+        <c:crossAx val="46766280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9299,13 +9467,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G36"/>
+  <dimension ref="B1:H36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9339,13 +9507,16 @@
       <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>8</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>708205820</v>
@@ -9359,16 +9530,20 @@
         <v>389140768</v>
       </c>
       <c r="F6" s="8" t="n">
-        <f aca="false">E6+②前提!$C$51</f>
+        <f aca="false">②前提!$C$54</f>
         <v>598035360</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>10</v>
+      <c r="G6" s="8" t="n">
+        <f aca="false">②前提!$C$61</f>
+        <v>730535360</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>229139405</v>
@@ -9382,16 +9557,20 @@
         <v>200601928</v>
       </c>
       <c r="F7" s="8" t="n">
-        <f aca="false">E7+②前提!$C$53</f>
+        <f aca="false">E7+②前提!$C$56</f>
         <v>263270305.6</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>12</v>
+      <c r="G7" s="8" t="n">
+        <f aca="false">E7+②前提!$C$63</f>
+        <v>303020305.6</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -9407,204 +9586,276 @@
         <f aca="false">②前提!$C$20</f>
         <v>132500000</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>14</v>
+      <c r="G8" s="8" t="n">
+        <f aca="false">②前提!$C$20</f>
+        <v>132500000</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11" t="n">
+        <v>708205820</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <f aca="false">D6</f>
+        <v>389140768</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <f aca="false">E6+E8</f>
+        <v>521640768</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <f aca="false">②前提!$C$58</f>
+        <v>730535360</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <f aca="false">②前提!$C$65</f>
+        <v>863035360</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <v>229139405</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D10" s="11" t="n">
         <f aca="false">D7</f>
         <v>200601928</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E10" s="11" t="n">
         <f aca="false">E7+E8</f>
         <v>333101928</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <f aca="false">F7+F8</f>
+      <c r="F10" s="11" t="n">
+        <f aca="false">②前提!$C$57</f>
         <v>395770305.6</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="7" t="n">
+      <c r="G10" s="11" t="n">
+        <f aca="false">②前提!$C$64</f>
+        <v>435520305.6</v>
+      </c>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>343932836</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D11" s="8" t="n">
         <f aca="false">②前提!$C$8*12</f>
         <v>300161064</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E11" s="8" t="n">
         <f aca="false">②前提!$C$8*12</f>
         <v>300161064</v>
       </c>
-      <c r="F10" s="8" t="n">
-        <f aca="false">E10</f>
+      <c r="F11" s="8" t="n">
+        <f aca="false">E11</f>
         <v>300161064</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="11" t="n">
+      <c r="G11" s="8" t="n">
+        <f aca="false">E11</f>
+        <v>300161064</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>-114793431</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <f aca="false">D9-D10</f>
+      <c r="D12" s="11" t="n">
+        <f aca="false">D10-D11</f>
         <v>-99559136</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <f aca="false">E9-E10</f>
+      <c r="E12" s="11" t="n">
+        <f aca="false">E10-E11</f>
         <v>32940864</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <f aca="false">F9-F10</f>
+      <c r="F12" s="11" t="n">
+        <f aca="false">F10-F11</f>
         <v>95609241.6</v>
       </c>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="G12" s="11" t="n">
+        <f aca="false">G10-G11</f>
+        <v>135359241.6</v>
+      </c>
+      <c r="H12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="7" t="n">
         <v>10000000</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D14" s="8" t="n">
         <f aca="false">②前提!$C$24</f>
         <v>15000000</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">②前提!$C$24</f>
         <v>15000000</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">②前提!$C$24</f>
         <v>15000000</v>
       </c>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="14" t="n">
+      <c r="G14" s="8" t="n">
+        <f aca="false">②前提!$C$24</f>
+        <v>15000000</v>
+      </c>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <v>-124793431</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <f aca="false">D11+D12-D13</f>
+      <c r="D15" s="14" t="n">
+        <f aca="false">D12+D13-D14</f>
         <v>-114559136</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <f aca="false">E11+E12-E13</f>
+      <c r="E15" s="14" t="n">
+        <f aca="false">E12+E13-E14</f>
         <v>17940864</v>
       </c>
-      <c r="F14" s="14" t="n">
-        <f aca="false">F11+F12-F13</f>
+      <c r="F15" s="14" t="n">
+        <f aca="false">F12+F13-F14</f>
         <v>80609241.6</v>
       </c>
-      <c r="G14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="G15" s="14" t="n">
+        <f aca="false">G12+G13-G14</f>
+        <v>120359241.6</v>
+      </c>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="11" t="n">
         <v>-124793431</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <f aca="false">D14-D15</f>
+      <c r="D17" s="11" t="n">
+        <f aca="false">D15-D16</f>
         <v>-114559136</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <f aca="false">E14-E15</f>
+      <c r="E17" s="11" t="n">
+        <f aca="false">E15-E16</f>
         <v>17940864</v>
       </c>
-      <c r="F16" s="11" t="n">
-        <f aca="false">F14-F15</f>
+      <c r="F17" s="11" t="n">
+        <f aca="false">F15-F16</f>
         <v>80609241.6</v>
       </c>
-      <c r="G16" s="12"/>
+      <c r="G17" s="11" t="n">
+        <f aca="false">G15-G16</f>
+        <v>120359241.6</v>
+      </c>
+      <c r="H17" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" s="20" t="n">
-        <f aca="false">②前提!$C$51</f>
+        <f aca="false">②前提!$C$55</f>
         <v>208894592</v>
       </c>
       <c r="D23" s="21" t="n">
         <f aca="false">C23/②前提!$C$29</f>
         <v>0.195961155722326</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <f aca="false">②前提!$C$62</f>
+        <v>341394592</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <f aca="false">C24/②前提!$C$29</f>
+        <v>0.320257590994371</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9614,56 +9865,62 @@
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C30" s="22"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
       <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="B31" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="22"/>
@@ -9672,60 +9929,65 @@
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
       <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="B33" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" s="24"/>
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" s="24"/>
       <c r="F36" s="24"/>
       <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9754,17 +10016,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9772,57 +10034,57 @@
         <v>3</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M5" s="27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N5" s="27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O5" s="18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P5" s="28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R5" s="18" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>32789307</v>
@@ -9879,7 +10141,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>18502877</v>
@@ -9936,7 +10198,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C8" s="30" t="n">
         <v>14286430</v>
@@ -9993,12 +10255,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="32" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>1450000</v>
@@ -10055,7 +10317,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>5733907</v>
@@ -10112,7 +10374,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>2678253</v>
@@ -10169,7 +10431,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>932201</v>
@@ -10226,7 +10488,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>53900</v>
@@ -10283,7 +10545,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>234134</v>
@@ -10340,7 +10602,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>2786025</v>
@@ -10397,7 +10659,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4193310</v>
@@ -10454,7 +10716,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>298477</v>
@@ -10511,7 +10773,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>956603</v>
@@ -10568,7 +10830,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>385679</v>
@@ -10625,7 +10887,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>163840</v>
@@ -10682,7 +10944,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0</v>
@@ -10739,7 +11001,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>208971</v>
@@ -10796,7 +11058,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>732759</v>
@@ -10853,7 +11115,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>216380</v>
@@ -10910,7 +11172,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>31310</v>
@@ -10967,7 +11229,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>64335</v>
@@ -11024,7 +11286,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10000</v>
@@ -11081,7 +11343,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>0</v>
@@ -11138,7 +11400,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>10091</v>
@@ -11195,7 +11457,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>3815699</v>
@@ -11252,7 +11514,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>419018</v>
@@ -11309,7 +11571,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="33" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C34" s="11" t="n">
         <f aca="false">SUM(C11:C33)</f>
@@ -11378,7 +11640,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C35" s="11" t="n">
         <f aca="false">C8-C34</f>
@@ -11435,7 +11697,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="26" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -11454,7 +11716,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G57"/>
+  <dimension ref="B1:G69"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -11465,17 +11727,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="34" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -11485,27 +11747,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C6" s="38" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I6:K6)</f>
         <v>32428397.3333333</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C7" s="38" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I8:K8)</f>
@@ -11514,7 +11776,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="38" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I34:K34)</f>
@@ -11523,7 +11785,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C9" s="40" t="n">
         <f aca="false">C7/C6</f>
@@ -11532,7 +11794,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="35" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
@@ -11542,140 +11804,140 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="41" t="n">
         <v>80000000</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="41" t="n">
         <v>2500000</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C15" s="41" t="n">
         <v>10000000</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C16" s="41" t="n">
         <v>20000000</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C17" s="41" t="n">
         <v>10000000</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C18" s="41" t="n">
         <v>10000000</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C19" s="30" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>132500000</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C20" s="8" t="n">
         <f aca="false">SUM(C13:C18)</f>
         <v>132500000</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
@@ -11685,117 +11947,117 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C24" s="41" t="n">
         <v>15000000</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C25" s="43" t="n">
         <v>6</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C26" s="43" t="n">
         <v>6</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C27" s="43" t="n">
         <v>12</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C28" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C29" s="41" t="n">
         <v>1066000000</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C30" s="43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C31" s="43" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C32" s="41" t="n">
         <v>419066414</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F33" s="45" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="35" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="36"/>
@@ -11805,7 +12067,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C36" s="46" t="n">
         <v>0.1</v>
@@ -11814,41 +12076,41 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C37" s="41" t="n">
         <v>708205820</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C38" s="30" t="n">
         <f aca="false">C32</f>
         <v>419066414</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C39" s="41" t="n">
         <v>208594315</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C40" s="30" t="n">
         <f aca="false">C37*C36</f>
@@ -11858,7 +12120,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C41" s="30" t="n">
         <f aca="false">(C38+C39)*C36</f>
@@ -11868,59 +12130,59 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="19" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C42" s="47" t="n">
         <f aca="false">C40-C41</f>
         <v>8054509.09999999</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C43" s="41" t="n">
         <v>4500000</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C44" s="30" t="n">
         <f aca="false">C42-C43</f>
         <v>3554509.09999999</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="19" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C45" s="30" t="n">
         <f aca="false">C42/4</f>
         <v>2013627.275</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F46" s="26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="35" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -11930,85 +12192,169 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C49" s="41" t="n">
         <v>730535360</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="19" t="s">
-        <v>159</v>
+      <c r="B50" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="C50" s="30" t="n">
-        <f aca="false">C6*12+C20</f>
-        <v>521640768</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>160</v>
+        <f aca="false">C20</f>
+        <v>132500000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C51" s="30" t="n">
-        <f aca="false">C49-C50</f>
-        <v>208894592</v>
+        <v>163</v>
+      </c>
+      <c r="C51" s="46" t="n">
+        <v>0.3</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F52" s="3" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="C53" s="30" t="n">
-        <f aca="false">C51*C52</f>
-        <v>62668377.6</v>
-      </c>
-      <c r="F53" s="3"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="47" t="n">
-        <f aca="false">C7*12+C20+C53</f>
-        <v>395770305.6</v>
-      </c>
-      <c r="F54" s="3" t="s">
         <v>166</v>
+      </c>
+      <c r="C54" s="30" t="n">
+        <f aca="false">C49-C50</f>
+        <v>598035360</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C55" s="48" t="n">
-        <f aca="false">C54/C49</f>
+      <c r="C55" s="30" t="n">
+        <f aca="false">C54-C6*12</f>
+        <v>208894592</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C56" s="30" t="n">
+        <f aca="false">C55*C51</f>
+        <v>62668377.6</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="47" t="n">
+        <f aca="false">C7*12+C56+C50</f>
+        <v>395770305.6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C58" s="30" t="n">
+        <f aca="false">C54+C50</f>
+        <v>730535360</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" s="49" t="n">
+        <f aca="false">C57/C58</f>
         <v>0.541753797653272</v>
       </c>
-      <c r="F55" s="3"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F57" s="26" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C60" s="48"/>
+      <c r="D60" s="48"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="30" t="n">
+        <f aca="false">C49</f>
+        <v>730535360</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="30" t="n">
+        <f aca="false">C61-C6*12</f>
+        <v>341394592</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="6" t="s">
         <v>168</v>
+      </c>
+      <c r="C63" s="30" t="n">
+        <f aca="false">C62*C51</f>
+        <v>102418377.6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="47" t="n">
+        <f aca="false">C7*12+C63+C50</f>
+        <v>435520305.6</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C65" s="30" t="n">
+        <f aca="false">C61+C50</f>
+        <v>863035360</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" s="49" t="n">
+        <f aca="false">C64/C65</f>
+        <v>0.504637846588348</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F68" s="39" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F69" s="26" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -12039,12 +12385,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="25" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12052,70 +12398,70 @@
         <v>3</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
-      <c r="P5" s="49"/>
+        <v>191</v>
+      </c>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="50" t="n">
         <f aca="false">②前提!$C$6</f>
@@ -12176,190 +12522,190 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="D7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="E7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="F7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="G7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="H7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="I7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="J7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="K7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="L7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="M7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="N7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="O7" s="50" t="n">
-        <f aca="false">IF(②前提!$C$30=2,②前提!$C$51/12,0)</f>
-        <v>17407882.6666667</v>
+        <f aca="false">IF(②前提!$C$30=3,②前提!$C$62/12,IF(②前提!$C$30=2,②前提!$C$55/12,0))</f>
+        <v>28449549.3333333</v>
       </c>
       <c r="P7" s="30" t="n">
         <f aca="false">SUM(D7:O7)</f>
-        <v>208894592</v>
+        <v>341394592</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="31" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C8" s="30" t="n">
         <f aca="false">C6+C7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="D8" s="30" t="n">
         <f aca="false">D6+D7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="false">E6+E7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="F8" s="30" t="n">
         <f aca="false">F6+F7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="G8" s="30" t="n">
         <f aca="false">G6+G7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="H8" s="30" t="n">
         <f aca="false">H6+H7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="I8" s="30" t="n">
         <f aca="false">I6+I7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="J8" s="30" t="n">
         <f aca="false">J6+J7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="K8" s="30" t="n">
         <f aca="false">K6+K7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="L8" s="30" t="n">
         <f aca="false">L6+L7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="M8" s="30" t="n">
         <f aca="false">M6+M7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="N8" s="30" t="n">
         <f aca="false">N6+N7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="O8" s="30" t="n">
         <f aca="false">O6+O7</f>
-        <v>49836280</v>
+        <v>60877946.6666667</v>
       </c>
       <c r="P8" s="30" t="n">
         <f aca="false">SUM(D8:O8)</f>
-        <v>598035360</v>
+        <v>730535360</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C9" s="50" t="n">
         <f aca="false">C8-C10-C11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">D8-D10-D11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="E9" s="8" t="n">
         <f aca="false">E8-E10-E11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">F8-F10-F11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="G9" s="8" t="n">
         <f aca="false">G8-G10-G11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="H9" s="8" t="n">
         <f aca="false">H8-H10-H11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="I9" s="8" t="n">
         <f aca="false">I8-I10-I11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="J9" s="8" t="n">
         <f aca="false">J8-J10-J11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="K9" s="8" t="n">
         <f aca="false">K8-K10-K11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="L9" s="8" t="n">
         <f aca="false">L8-L10-L11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="M9" s="8" t="n">
         <f aca="false">M8-M10-M11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">N8-N10-N11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="O9" s="8" t="n">
         <f aca="false">O8-O10-O11</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="P9" s="30" t="n">
         <f aca="false">SUM(D9:O9)</f>
-        <v>334765054.4</v>
+        <v>427515054.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C10" s="50" t="n">
         <f aca="false">②前提!$C$7</f>
@@ -12420,68 +12766,68 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C11" s="50" t="n">
-        <f aca="false">C7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">C7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="D11" s="50" t="n">
-        <f aca="false">D7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">D7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="E11" s="50" t="n">
-        <f aca="false">E7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">E7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="F11" s="50" t="n">
-        <f aca="false">F7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">F7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="G11" s="50" t="n">
-        <f aca="false">G7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">G7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="H11" s="50" t="n">
-        <f aca="false">H7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">H7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="I11" s="50" t="n">
-        <f aca="false">I7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">I7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="J11" s="50" t="n">
-        <f aca="false">J7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">J7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="K11" s="50" t="n">
-        <f aca="false">K7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">K7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="L11" s="50" t="n">
-        <f aca="false">L7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">L7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="M11" s="50" t="n">
-        <f aca="false">M7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">M7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="N11" s="50" t="n">
-        <f aca="false">N7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">N7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="O11" s="50" t="n">
-        <f aca="false">O7*②前提!$C$52</f>
-        <v>5222364.8</v>
+        <f aca="false">O7*②前提!$C$51</f>
+        <v>8534864.8</v>
       </c>
       <c r="P11" s="30" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>62668377.6</v>
+        <v>102418377.6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C12" s="50" t="n">
         <f aca="false">②前提!$C$13/12</f>
@@ -12542,7 +12888,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C13" s="50" t="n">
         <f aca="false">②前提!$C$14/12</f>
@@ -12603,7 +12949,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C14" s="50" t="n">
         <f aca="false">②前提!$C$15/12</f>
@@ -12664,7 +13010,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$25,②前提!$C$16,0)</f>
@@ -12721,7 +13067,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">IF(1=②前提!$C$26,②前提!$C$17,0)+IF(1=②前提!$C$27,②前提!$C$18,0)</f>
@@ -12778,87 +13124,87 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">C10+C11+SUM(C12:C14)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">D10+D11+SUM(D12:D16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">E10+E11+SUM(E12:E16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">F10+F11+SUM(F12:F16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="G17" s="11" t="n">
         <f aca="false">G10+G11+SUM(G12:G16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">H10+H11+SUM(H12:H16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="I17" s="11" t="n">
         <f aca="false">I10+I11+SUM(I12:I16)</f>
-        <v>59647525.4666667</v>
+        <v>62960025.4666667</v>
       </c>
       <c r="J17" s="11" t="n">
         <f aca="false">J10+J11+SUM(J12:J16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="K17" s="11" t="n">
         <f aca="false">K10+K11+SUM(K12:K16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="L17" s="11" t="n">
         <f aca="false">L10+L11+SUM(L12:L16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="M17" s="11" t="n">
         <f aca="false">M10+M11+SUM(M12:M16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="N17" s="11" t="n">
         <f aca="false">N10+N11+SUM(N12:N16)</f>
-        <v>29647525.4666667</v>
+        <v>32960025.4666667</v>
       </c>
       <c r="O17" s="11" t="n">
         <f aca="false">O10+O11+SUM(O12:O16)</f>
-        <v>39647525.4666667</v>
+        <v>42960025.4666667</v>
       </c>
       <c r="P17" s="11" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>395770305.6</v>
+        <v>435520305.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
+        <v>202</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C20" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)</f>
@@ -12919,7 +13265,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I12:K12)</f>
@@ -12980,7 +13326,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C22" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I13:K13)</f>
@@ -13041,7 +13387,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I14:K14)</f>
@@ -13102,7 +13448,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C24" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I15:K15)</f>
@@ -13163,7 +13509,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I16:K16)</f>
@@ -13224,7 +13570,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C26" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I17:K17)</f>
@@ -13285,7 +13631,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C27" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I18:K18)</f>
@@ -13346,7 +13692,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I19:K19)</f>
@@ -13407,7 +13753,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I20:K20)</f>
@@ -13468,7 +13814,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C30" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I21:K21)</f>
@@ -13529,7 +13875,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C31" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I22:K22)</f>
@@ -13590,7 +13936,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C32" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I23:K23)</f>
@@ -13651,7 +13997,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C33" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I24:K24)</f>
@@ -13712,7 +14058,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C34" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I25:K25)</f>
@@ -13773,7 +14119,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C35" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I26:K26)</f>
@@ -13834,7 +14180,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C36" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I27:K27)</f>
@@ -13895,7 +14241,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C37" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I28:K28)</f>
@@ -13956,7 +14302,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C38" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I29:K29)</f>
@@ -14017,7 +14363,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C39" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I30:K30)</f>
@@ -14078,7 +14424,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C40" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I31:K31)</f>
@@ -14139,7 +14485,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C41" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I32:K32)</f>
@@ -14200,7 +14546,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C42" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I33:K33)</f>
@@ -14261,7 +14607,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C43" s="11" t="n">
         <f aca="false">SUM(C20:C42)</f>
@@ -14322,87 +14668,87 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="32" t="s">
-        <v>197</v>
-      </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="49"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="49"/>
-      <c r="O45" s="49"/>
-      <c r="P45" s="49"/>
+        <v>203</v>
+      </c>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
+      <c r="L45" s="48"/>
+      <c r="M45" s="48"/>
+      <c r="N45" s="48"/>
+      <c r="O45" s="48"/>
+      <c r="P45" s="48"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C46" s="11" t="n">
         <f aca="false">C17-C43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="D46" s="11" t="n">
         <f aca="false">D17-D43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="E46" s="11" t="n">
         <f aca="false">E17-E43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="F46" s="11" t="n">
         <f aca="false">F17-F43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="G46" s="11" t="n">
         <f aca="false">G17-G43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="H46" s="11" t="n">
         <f aca="false">H17-H43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="I46" s="11" t="n">
         <f aca="false">I17-I43</f>
-        <v>34634103.4666667</v>
+        <v>37946603.4666667</v>
       </c>
       <c r="J46" s="11" t="n">
         <f aca="false">J17-J43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="K46" s="11" t="n">
         <f aca="false">K17-K43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="L46" s="11" t="n">
         <f aca="false">L17-L43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="M46" s="11" t="n">
         <f aca="false">M17-M43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="N46" s="11" t="n">
         <f aca="false">N17-N43</f>
-        <v>4634103.46666667</v>
+        <v>7946603.46666667</v>
       </c>
       <c r="O46" s="11" t="n">
         <f aca="false">O17-O43</f>
-        <v>14634103.4666667</v>
+        <v>17946603.4666667</v>
       </c>
       <c r="P46" s="11" t="n">
         <f aca="false">SUM(D46:O46)</f>
-        <v>95609241.6</v>
+        <v>135359241.6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47" s="8" t="n">
         <f aca="false">0</f>
@@ -14459,7 +14805,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C48" s="50" t="n">
         <f aca="false">②前提!$C$24/12</f>
@@ -14520,126 +14866,126 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C49" s="14" t="n">
         <f aca="false">C46+C47-C48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="D49" s="14" t="n">
         <f aca="false">D46+D47-D48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="E49" s="14" t="n">
         <f aca="false">E46+E47-E48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="F49" s="14" t="n">
         <f aca="false">F46+F47-F48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="G49" s="14" t="n">
         <f aca="false">G46+G47-G48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="H49" s="14" t="n">
         <f aca="false">H46+H47-H48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="I49" s="14" t="n">
         <f aca="false">I46+I47-I48</f>
-        <v>33384103.4666667</v>
+        <v>36696603.4666667</v>
       </c>
       <c r="J49" s="14" t="n">
         <f aca="false">J46+J47-J48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="K49" s="14" t="n">
         <f aca="false">K46+K47-K48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="L49" s="14" t="n">
         <f aca="false">L46+L47-L48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="M49" s="14" t="n">
         <f aca="false">M46+M47-M48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="N49" s="14" t="n">
         <f aca="false">N46+N47-N48</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="O49" s="14" t="n">
         <f aca="false">O46+O47-O48</f>
-        <v>13384103.4666667</v>
+        <v>16696603.4666667</v>
       </c>
       <c r="P49" s="14" t="n">
         <f aca="false">SUM(D49:O49)</f>
-        <v>80609241.6</v>
+        <v>120359241.6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="42" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D50" s="47" t="n">
         <f aca="false">D49</f>
-        <v>3384103.46666667</v>
+        <v>6696603.46666667</v>
       </c>
       <c r="E50" s="47" t="n">
         <f aca="false">D50+E49</f>
-        <v>6768206.93333333</v>
+        <v>13393206.9333333</v>
       </c>
       <c r="F50" s="47" t="n">
         <f aca="false">E50+F49</f>
-        <v>10152310.4</v>
+        <v>20089810.4</v>
       </c>
       <c r="G50" s="47" t="n">
         <f aca="false">F50+G49</f>
-        <v>13536413.8666667</v>
+        <v>26786413.8666667</v>
       </c>
       <c r="H50" s="47" t="n">
         <f aca="false">G50+H49</f>
-        <v>16920517.3333333</v>
+        <v>33483017.3333333</v>
       </c>
       <c r="I50" s="47" t="n">
         <f aca="false">H50+I49</f>
-        <v>50304620.8</v>
+        <v>70179620.8</v>
       </c>
       <c r="J50" s="47" t="n">
         <f aca="false">I50+J49</f>
-        <v>53688724.2666667</v>
+        <v>76876224.2666667</v>
       </c>
       <c r="K50" s="47" t="n">
         <f aca="false">J50+K49</f>
-        <v>57072827.7333333</v>
+        <v>83572827.7333333</v>
       </c>
       <c r="L50" s="47" t="n">
         <f aca="false">K50+L49</f>
-        <v>60456931.2</v>
+        <v>90269431.2</v>
       </c>
       <c r="M50" s="47" t="n">
         <f aca="false">L50+M49</f>
-        <v>63841034.6666667</v>
+        <v>96966034.6666667</v>
       </c>
       <c r="N50" s="47" t="n">
         <f aca="false">M50+N49</f>
-        <v>67225138.1333333</v>
+        <v>103662638.133333</v>
       </c>
       <c r="O50" s="47" t="n">
         <f aca="false">N50+O49</f>
-        <v>80609241.6</v>
+        <v>120359241.6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="3" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -14669,31 +15015,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="34" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="51" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C5" s="52" t="n">
         <v>-114793431</v>
@@ -14703,12 +15049,12 @@
         <v>-114793431</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C6" s="8" t="n">
         <f aca="false">②前提!$C$7*12-229139405</f>
@@ -14719,12 +15065,12 @@
         <v>-143330908</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C7" s="8" t="n">
         <f aca="false">343932836-②前提!$C$8*12</f>
@@ -14735,12 +15081,12 @@
         <v>-99559136</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C8" s="8" t="n">
         <f aca="false">②前提!$C$20</f>
@@ -14751,29 +15097,29 @@
         <v>32940864</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="53" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D8</f>
         <v>32940864</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="19" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">①サマリー!C23</f>
@@ -14784,7 +15130,7 @@
         <v>0.195961155722326</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -14816,17 +15162,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="55" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="26" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="35" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -14837,27 +15183,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="17" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C6" s="56" t="n">
         <v>560</v>
@@ -14877,31 +15223,31 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="51" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C7" s="57" t="n">
         <f aca="false">G6-E6</f>
         <v>140</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E7" s="58" t="n">
         <f aca="false">C7/6</f>
         <v>23.3333333333333</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="35" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C10" s="36"/>
       <c r="D10" s="36"/>
@@ -14924,73 +15270,73 @@
         <v>3</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I11" s="27" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M11" s="27" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N11" s="27" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O11" s="27" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C12" s="41" t="n">
         <v>420000000</v>
       </c>
       <c r="Q12" s="39" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C13" s="41" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D14" s="41" t="n">
         <v>0</v>
@@ -15033,12 +15379,12 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D15" s="41" t="n">
         <v>0</v>
@@ -15081,12 +15427,12 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">IF(②前提!$C$31=2,②前提!$C$32/12,D18)</f>
@@ -15141,12 +15487,12 @@
         <v>419066414</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="33" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">D16+$C$13+D14+D15</f>
@@ -15203,131 +15549,131 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D18" s="50" t="n">
         <f aca="false">③FY2027月次推移!D9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="E18" s="50" t="n">
         <f aca="false">③FY2027月次推移!E9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="F18" s="50" t="n">
         <f aca="false">③FY2027月次推移!F9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="G18" s="50" t="n">
         <f aca="false">③FY2027月次推移!G9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="H18" s="50" t="n">
         <f aca="false">③FY2027月次推移!H9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="I18" s="50" t="n">
         <f aca="false">③FY2027月次推移!I9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="J18" s="50" t="n">
         <f aca="false">③FY2027月次推移!J9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="K18" s="50" t="n">
         <f aca="false">③FY2027月次推移!K9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="L18" s="50" t="n">
         <f aca="false">③FY2027月次推移!L9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="M18" s="50" t="n">
         <f aca="false">③FY2027月次推移!M9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="N18" s="50" t="n">
         <f aca="false">③FY2027月次推移!N9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="O18" s="50" t="n">
         <f aca="false">③FY2027月次推移!O9</f>
-        <v>27897087.8666667</v>
+        <v>35626254.5333333</v>
       </c>
       <c r="P18" s="30" t="n">
         <f aca="false">SUM(D18:O18)</f>
-        <v>334765054.4</v>
+        <v>427515054.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="33" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D19" s="59" t="n">
         <f aca="false">$C$12+D17-D18</f>
-        <v>427025113.3</v>
+        <v>419295946.633333</v>
       </c>
       <c r="E19" s="59" t="n">
         <f aca="false">D19+E17-E18</f>
-        <v>434050226.6</v>
+        <v>418591893.266667</v>
       </c>
       <c r="F19" s="59" t="n">
         <f aca="false">E19+F17-F18</f>
-        <v>441075339.9</v>
+        <v>417887839.9</v>
       </c>
       <c r="G19" s="59" t="n">
         <f aca="false">F19+G17-G18</f>
-        <v>448100453.2</v>
+        <v>417183786.533333</v>
       </c>
       <c r="H19" s="59" t="n">
         <f aca="false">G19+H17-H18</f>
-        <v>455125566.5</v>
+        <v>416479733.166667</v>
       </c>
       <c r="I19" s="59" t="n">
         <f aca="false">H19+I17-I18</f>
-        <v>462150679.8</v>
+        <v>415775679.8</v>
       </c>
       <c r="J19" s="59" t="n">
         <f aca="false">I19+J17-J18</f>
-        <v>469175793.1</v>
+        <v>415071626.433333</v>
       </c>
       <c r="K19" s="59" t="n">
         <f aca="false">J19+K17-K18</f>
-        <v>476200906.4</v>
+        <v>414367573.066667</v>
       </c>
       <c r="L19" s="59" t="n">
         <f aca="false">K19+L17-L18</f>
-        <v>483226019.7</v>
+        <v>413663519.7</v>
       </c>
       <c r="M19" s="59" t="n">
         <f aca="false">L19+M17-M18</f>
-        <v>490251133</v>
+        <v>412959466.333333</v>
       </c>
       <c r="N19" s="59" t="n">
         <f aca="false">M19+N17-N18</f>
-        <v>497276246.3</v>
+        <v>412255412.966667</v>
       </c>
       <c r="O19" s="59" t="n">
         <f aca="false">N19+O17-O18</f>
-        <v>504301359.6</v>
+        <v>411551359.6</v>
       </c>
       <c r="P19" s="60" t="n">
         <f aca="false">O19</f>
-        <v>504301359.6</v>
+        <v>411551359.6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="26" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="26" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="39" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -15359,17 +15705,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="34" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="35" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -15389,69 +15735,69 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C5" s="41" t="n">
         <v>30000000</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C6" s="61" t="n">
         <f aca="false">②前提!$C$36</f>
         <v>0.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C7" s="62" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C8" s="62" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C9" s="41" t="n">
         <v>2662179</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15459,127 +15805,127 @@
         <v>3</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I12" s="27" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L12" s="27" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M12" s="27" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N12" s="27" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O12" s="27" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="P12" s="37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="49"/>
+        <v>271</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="63" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D14" s="50" t="n">
         <f aca="false">③FY2027月次推移!D8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="E14" s="50" t="n">
         <f aca="false">③FY2027月次推移!E8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="F14" s="50" t="n">
         <f aca="false">③FY2027月次推移!F8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="G14" s="50" t="n">
         <f aca="false">③FY2027月次推移!G8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="H14" s="50" t="n">
         <f aca="false">③FY2027月次推移!H8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="I14" s="50" t="n">
         <f aca="false">③FY2027月次推移!I8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="J14" s="50" t="n">
         <f aca="false">③FY2027月次推移!J8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="K14" s="50" t="n">
         <f aca="false">③FY2027月次推移!K8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="L14" s="50" t="n">
         <f aca="false">③FY2027月次推移!L8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="M14" s="50" t="n">
         <f aca="false">③FY2027月次推移!M8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="N14" s="50" t="n">
         <f aca="false">③FY2027月次推移!N8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="O14" s="50" t="n">
         <f aca="false">③FY2027月次推移!O8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="P14" s="30" t="n">
         <f aca="false">SUM(D14:O14)</f>
-        <v>657838896</v>
+        <v>803588896</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="63" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D15" s="50" t="n">
         <f aca="false">SUM(③FY2027月次推移!D12:D14)*(1+$C$6)</f>
@@ -15636,7 +15982,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="64" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D16" s="50" t="n">
         <f aca="false">③FY2027月次推移!D15*(1+$C$6)</f>
@@ -15693,7 +16039,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D17" s="41" t="n">
         <v>0</v>
@@ -15736,12 +16082,12 @@
         <v>0</v>
       </c>
       <c r="Q17" s="39" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="63" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D18" s="50" t="n">
         <f aca="false">③FY2027月次推移!D16*(1+$C$6)</f>
@@ -15796,88 +16142,88 @@
         <v>22000000</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="D19" s="11" t="n">
         <f aca="false">SUM(D14:D18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="E19" s="11" t="n">
         <f aca="false">SUM(E14:E18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="F19" s="11" t="n">
         <f aca="false">SUM(F14:F18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="G19" s="11" t="n">
         <f aca="false">SUM(G14:G18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="H19" s="11" t="n">
         <f aca="false">SUM(H14:H18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="I19" s="11" t="n">
         <f aca="false">SUM(I14:I18)</f>
-        <v>96299074.6666667</v>
+        <v>108444908</v>
       </c>
       <c r="J19" s="11" t="n">
         <f aca="false">SUM(J14:J18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="K19" s="11" t="n">
         <f aca="false">SUM(K14:K18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="L19" s="11" t="n">
         <f aca="false">SUM(L14:L18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="M19" s="11" t="n">
         <f aca="false">SUM(M14:M18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="N19" s="11" t="n">
         <f aca="false">SUM(N14:N18)</f>
-        <v>63299074.6666667</v>
+        <v>75444908</v>
       </c>
       <c r="O19" s="11" t="n">
         <f aca="false">SUM(O14:O18)</f>
-        <v>74299074.6666667</v>
+        <v>86444908</v>
       </c>
       <c r="P19" s="11" t="n">
         <f aca="false">SUM(D19:O19)</f>
-        <v>803588896</v>
+        <v>949338896</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="49"/>
+        <v>280</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="63" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D22" s="50" t="n">
         <f aca="false">⑥ワイン仕入・在庫計画!D17*(1+$C$6)</f>
@@ -15934,7 +16280,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="63" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D23" s="50" t="n">
         <f aca="false">AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14)</f>
@@ -15991,7 +16337,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="63" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D24" s="50" t="n">
         <f aca="false">((③FY2027月次推移!D43-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22))</f>
@@ -16048,7 +16394,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="63" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D25" s="50" t="n">
         <f aca="false">③FY2027月次推移!D48</f>
@@ -16105,7 +16451,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="63" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D26" s="50" t="n">
         <v>0</v>
@@ -16152,12 +16498,12 @@
         <v>9595390.92499999</v>
       </c>
       <c r="Q26" s="26" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="D27" s="41" t="n">
         <v>0</v>
@@ -16202,7 +16548,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="10" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D28" s="11" t="n">
         <f aca="false">SUM(D22:D27)</f>
@@ -16259,83 +16605,83 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="10" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D29" s="11" t="n">
         <f aca="false">D19-D28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="E29" s="11" t="n">
         <f aca="false">E19-E28</f>
-        <v>-3235320.28333332</v>
+        <v>8910513.05</v>
       </c>
       <c r="F29" s="11" t="n">
         <f aca="false">F19-F28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="G29" s="11" t="n">
         <f aca="false">G19-G28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="H29" s="11" t="n">
         <f aca="false">H19-H28</f>
-        <v>-1231333.45833333</v>
+        <v>10914499.875</v>
       </c>
       <c r="I29" s="11" t="n">
         <f aca="false">I19-I28</f>
-        <v>33782293.8166667</v>
+        <v>45928127.15</v>
       </c>
       <c r="J29" s="11" t="n">
         <f aca="false">J19-J28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="K29" s="11" t="n">
         <f aca="false">K19-K28</f>
-        <v>-1231333.45833333</v>
+        <v>10914499.875</v>
       </c>
       <c r="L29" s="11" t="n">
         <f aca="false">L19-L28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="M29" s="11" t="n">
         <f aca="false">M19-M28</f>
-        <v>782293.81666667</v>
+        <v>12928127.15</v>
       </c>
       <c r="N29" s="11" t="n">
         <f aca="false">N19-N28</f>
-        <v>-1231333.45833333</v>
+        <v>10914499.875</v>
       </c>
       <c r="O29" s="11" t="n">
         <f aca="false">O19-O28</f>
-        <v>11782293.8166667</v>
+        <v>23928127.15</v>
       </c>
       <c r="P29" s="11" t="n">
         <f aca="false">SUM(D29:O29)</f>
-        <v>43329029.8750001</v>
+        <v>189079029.875</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
-      <c r="L31" s="49"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="P31" s="49"/>
+        <v>290</v>
+      </c>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="63" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D32" s="50" t="n">
         <f aca="false">-$C$9</f>
@@ -16392,7 +16738,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="63" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D33" s="50" t="n">
         <f aca="false">$C$10</f>
@@ -16449,7 +16795,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D34" s="41" t="n">
         <v>0</v>
@@ -16494,7 +16840,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D35" s="41" t="n">
         <v>0</v>
@@ -16537,12 +16883,12 @@
         <v>0</v>
       </c>
       <c r="Q35" s="39" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="10" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D36" s="11" t="n">
         <f aca="false">SUM(D32:D35)</f>
@@ -16599,64 +16945,64 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="10" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="D38" s="11" t="n">
         <f aca="false">D29+D36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="E38" s="11" t="n">
         <f aca="false">E29+E36</f>
-        <v>-5897499.28333332</v>
+        <v>6248334.05</v>
       </c>
       <c r="F38" s="11" t="n">
         <f aca="false">F29+F36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="G38" s="11" t="n">
         <f aca="false">G29+G36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="H38" s="11" t="n">
         <f aca="false">H29+H36</f>
-        <v>-3893512.45833333</v>
+        <v>8252320.875</v>
       </c>
       <c r="I38" s="11" t="n">
         <f aca="false">I29+I36</f>
-        <v>31120114.8166667</v>
+        <v>43265948.15</v>
       </c>
       <c r="J38" s="11" t="n">
         <f aca="false">J29+J36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="K38" s="11" t="n">
         <f aca="false">K29+K36</f>
-        <v>-3893512.45833333</v>
+        <v>8252320.875</v>
       </c>
       <c r="L38" s="11" t="n">
         <f aca="false">L29+L36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="M38" s="11" t="n">
         <f aca="false">M29+M36</f>
-        <v>-1879885.18333333</v>
+        <v>10265948.15</v>
       </c>
       <c r="N38" s="11" t="n">
         <f aca="false">N29+N36</f>
-        <v>-3893512.45833333</v>
+        <v>8252320.875</v>
       </c>
       <c r="O38" s="11" t="n">
         <f aca="false">O29+O36</f>
-        <v>9120114.81666667</v>
+        <v>21265948.15</v>
       </c>
       <c r="P38" s="11" t="n">
         <f aca="false">SUM(D38:O38)</f>
-        <v>11382881.8750001</v>
+        <v>157132881.875</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D39" s="8" t="n">
         <f aca="false">$C$5</f>
@@ -16664,109 +17010,109 @@
       </c>
       <c r="E39" s="8" t="n">
         <f aca="false">D40</f>
-        <v>28120114.8166667</v>
+        <v>40265948.15</v>
       </c>
       <c r="F39" s="8" t="n">
         <f aca="false">E40</f>
-        <v>22222615.5333333</v>
+        <v>46514282.2</v>
       </c>
       <c r="G39" s="8" t="n">
         <f aca="false">F40</f>
-        <v>20342730.35</v>
+        <v>56780230.35</v>
       </c>
       <c r="H39" s="8" t="n">
         <f aca="false">G40</f>
-        <v>18462845.1666667</v>
+        <v>67046178.5</v>
       </c>
       <c r="I39" s="8" t="n">
         <f aca="false">H40</f>
-        <v>14569332.7083334</v>
+        <v>75298499.375</v>
       </c>
       <c r="J39" s="8" t="n">
         <f aca="false">I40</f>
-        <v>45689447.525</v>
+        <v>118564447.525</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">J40</f>
-        <v>43809562.3416667</v>
+        <v>128830395.675</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">K40</f>
-        <v>39916049.8833334</v>
+        <v>137082716.55</v>
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">L40</f>
-        <v>38036164.7</v>
+        <v>147348664.7</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">M40</f>
-        <v>36156279.5166667</v>
+        <v>157614612.85</v>
       </c>
       <c r="O39" s="8" t="n">
         <f aca="false">N40</f>
-        <v>32262767.0583334</v>
+        <v>165866933.725</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="13" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">D39+D38</f>
-        <v>28120114.8166667</v>
+        <v>40265948.15</v>
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">E39+E38</f>
-        <v>22222615.5333333</v>
+        <v>46514282.2</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">F39+F38</f>
-        <v>20342730.35</v>
+        <v>56780230.35</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">G39+G38</f>
-        <v>18462845.1666667</v>
+        <v>67046178.5</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">H39+H38</f>
-        <v>14569332.7083334</v>
+        <v>75298499.375</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">I39+I38</f>
-        <v>45689447.525</v>
+        <v>118564447.525</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">J39+J38</f>
-        <v>43809562.3416667</v>
+        <v>128830395.675</v>
       </c>
       <c r="K40" s="14" t="n">
         <f aca="false">K39+K38</f>
-        <v>39916049.8833334</v>
+        <v>137082716.55</v>
       </c>
       <c r="L40" s="14" t="n">
         <f aca="false">L39+L38</f>
-        <v>38036164.7</v>
+        <v>147348664.7</v>
       </c>
       <c r="M40" s="14" t="n">
         <f aca="false">M39+M38</f>
-        <v>36156279.5166667</v>
+        <v>157614612.85</v>
       </c>
       <c r="N40" s="14" t="n">
         <f aca="false">N39+N38</f>
-        <v>32262767.0583334</v>
+        <v>165866933.725</v>
       </c>
       <c r="O40" s="14" t="n">
         <f aca="false">O39+O38</f>
-        <v>41382881.8750001</v>
+        <v>187132881.875</v>
       </c>
       <c r="P40" s="47" t="n">
         <f aca="false">O40</f>
-        <v>41382881.8750001</v>
+        <v>187132881.875</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="65" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D41" s="66" t="n">
         <f aca="false">IF(D40&lt;0,D40,0)</f>
@@ -16821,37 +17167,37 @@
         <v>0</v>
       </c>
       <c r="Q41" s="26" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="26" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="26" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="35" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C49" s="36"/>
       <c r="D49" s="36"/>
@@ -16871,126 +17217,126 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="51" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C51" s="30" t="n">
         <f aca="false">O40</f>
-        <v>41382881.8750001</v>
+        <v>187132881.875</v>
       </c>
       <c r="D51" s="30" t="n">
         <f aca="false">MIN(D40:O40)</f>
-        <v>14569332.7083334</v>
+        <v>40265948.15</v>
       </c>
       <c r="E51" s="20" t="n">
         <f aca="false">IF(C51&lt;0,-MIN(C51,D51)+$C$55,MAX(0,-D51+$C$55))</f>
-        <v>40250575.2916667</v>
+        <v>26699793.1833333</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="19" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C52" s="66" t="n">
         <f aca="false">C51+(②前提!$C$32-③FY2027月次推移!$P$9)*(1+$C$6)</f>
-        <v>134114377.435</v>
+        <v>177839377.435</v>
       </c>
       <c r="D52" s="66" t="n">
         <f aca="false">D51+(②前提!$C$32-③FY2027月次推移!$P$9)*(1+$C$6)</f>
-        <v>107300828.268333</v>
+        <v>30972443.71</v>
       </c>
       <c r="E52" s="20" t="n">
         <f aca="false">IF(C52&lt;0,-MIN(C52,D52)+$C$55,MAX(0,-D52+$C$55))</f>
-        <v>0</v>
+        <v>35993297.6233333</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="19" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C53" s="66" t="n">
         <f aca="false">C51-(P16+P18)</f>
-        <v>-2617118.12499995</v>
+        <v>143132881.875</v>
       </c>
       <c r="D53" s="66" t="n">
         <f aca="false">D51-(P16+P18)</f>
-        <v>-29430667.2916666</v>
+        <v>-3734051.85</v>
       </c>
       <c r="E53" s="20" t="n">
         <f aca="false">IF(C53&lt;0,-MIN(C53,D53)+$C$55,MAX(0,-D53+$C$55))</f>
-        <v>84250575.2916667</v>
+        <v>70699793.1833333</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="19" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C54" s="66" t="n">
         <f aca="false">C51-①サマリー!$C$24*(1+$C$6)</f>
-        <v>41382881.8750001</v>
+        <v>-188401169.325</v>
       </c>
       <c r="D54" s="66" t="n">
         <f aca="false">D51-①サマリー!$C$24*(1+$C$6)</f>
-        <v>14569332.7083334</v>
+        <v>-335268103.05</v>
       </c>
       <c r="E54" s="20" t="n">
         <f aca="false">IF(C54&lt;0,-MIN(C54,D54)+$C$55,MAX(0,-D54+$C$55))</f>
-        <v>40250575.2916667</v>
+        <v>402233844.383333</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="6" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C55" s="50" t="n">
         <f aca="false">③FY2027月次推移!$C$8*(1+$C$6)</f>
-        <v>54819908</v>
+        <v>66965741.3333333</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="26" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="26" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="35" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C79" s="36"/>
       <c r="D79" s="36"/>
@@ -17010,30 +17356,30 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="6" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C80" s="41" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="6" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C81" s="30" t="n">
         <f aca="false">②前提!$C$6*(1+$C$6)+SUM(②前提!$C$13:$C$15)/12*(1+$C$6)-②前提!$C$32/12*(1+$C$6)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(((②前提!$C$8-AVERAGE(④FY2026月次実績!I32:K32)-(AVERAGE(④FY2026月次実績!I11:K11)+AVERAGE(④FY2026月次実績!I12:K12)+AVERAGE(④FY2026月次実績!I13:K13)+AVERAGE(④FY2026月次実績!I14:K14))-(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))*(1+$C$6))+(AVERAGE(④FY2026月次実績!I30:K30)+AVERAGE(④FY2026月次実績!I22:K22)))-②前提!$C$24/12-$C$9</f>
         <v>-21028556.1166667</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="17" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="D83" s="37" t="n">
         <v>1</v>
@@ -17074,45 +17420,45 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D84" s="67" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E84" s="67" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F84" s="67" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G84" s="67" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H84" s="67" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I84" s="67" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J84" s="67" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="K84" s="67" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L84" s="67" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M84" s="67" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N84" s="67" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O84" s="67" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="6" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D85" s="8" t="n">
         <f aca="false">$C$5+D$83*$C$81+(SUM($D$16:D16)+SUM($D$18:D18))-(SUM($D$26:D26)+SUM($D$27:D27))</f>
@@ -17165,7 +17511,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="6" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D86" s="8" t="n">
         <f aca="false">MAX(0,($C$80-D85)*12/((1+$C$6)*D$83))</f>
@@ -17218,7 +17564,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="42" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C88" s="20" t="n">
         <f aca="false">MAX(D86:O86)</f>
@@ -17227,7 +17573,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="42" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C89" s="20" t="n">
         <f aca="false">②前提!$C$6*12+C88</f>
@@ -17236,29 +17582,29 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="6" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C90" s="42" t="str">
         <f aca="false">INDEX(D84:O84,MATCH(C88,D86:O86,0))</f>
         <v>2027/02</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="26" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="26" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="26" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
